--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -96,6 +96,50 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+根据活动结束要清除数据，单独字段配置</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写道具Item资源文件夹中的道具名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 类型_地点ID
 类型：
 1. 游戏界面：例 类型_游戏ID\0(大厅)
@@ -105,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -133,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
   <si>
     <t>任务ID</t>
   </si>
@@ -144,7 +188,13 @@
     <t>任务条件</t>
   </si>
   <si>
-    <t>奖励</t>
+    <t>道具奖励</t>
+  </si>
+  <si>
+    <t>积分奖励</t>
+  </si>
+  <si>
+    <t>积分ICON</t>
   </si>
   <si>
     <t>按钮跳转类型</t>
@@ -180,6 +230,12 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>integralNum</t>
+  </si>
+  <si>
+    <t>integralIcon</t>
+  </si>
+  <si>
     <t>jumpType</t>
   </si>
   <si>
@@ -192,7 +248,7 @@
     <t>11001_1000_2_0</t>
   </si>
   <si>
-    <t>1022504_100</t>
+    <t>itemicon_1022504.png</t>
   </si>
   <si>
     <t>3_1</t>
@@ -207,18 +263,12 @@
     <t>11002_10000_0</t>
   </si>
   <si>
-    <t>1022504_200</t>
-  </si>
-  <si>
     <t>累积充值达到10000以上</t>
   </si>
   <si>
     <t>12001_100100_1000000</t>
   </si>
   <si>
-    <t>1022504_20</t>
-  </si>
-  <si>
     <t>1_100100</t>
   </si>
   <si>
@@ -228,9 +278,6 @@
     <t>12001_0_2000000</t>
   </si>
   <si>
-    <t>1022504_50</t>
-  </si>
-  <si>
     <t>1_0</t>
   </si>
   <si>
@@ -240,27 +287,18 @@
     <t>10003_100100_1_1000000_1990000</t>
   </si>
   <si>
-    <t>1022504_150</t>
-  </si>
-  <si>
     <t>在100100游戏中，金币累积赢奖达到1000000</t>
   </si>
   <si>
     <t>10003_0_1_2000000_1990000</t>
   </si>
   <si>
-    <t>1022504_180</t>
-  </si>
-  <si>
     <t>在任意游戏中，金币累积赢奖达到2000000</t>
   </si>
   <si>
     <t>10003_0_1_1000_1980000</t>
   </si>
   <si>
-    <t>1022504_500</t>
-  </si>
-  <si>
     <t>3_2</t>
   </si>
   <si>
@@ -270,9 +308,6 @@
     <t>12102_1022501_10</t>
   </si>
   <si>
-    <t>1022504_300</t>
-  </si>
-  <si>
     <t>2_3</t>
   </si>
   <si>
@@ -286,9 +321,6 @@
   </si>
   <si>
     <t>10001_0_1_500</t>
-  </si>
-  <si>
-    <t>1022504_90</t>
   </si>
   <si>
     <t>在任意电子游戏中，累积旋转500次</t>
@@ -1289,7 +1321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,6 +1359,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1341,47 +1376,65 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1722,761 +1775,901 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
     <col min="2" max="2" width="9.125" style="12" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="13" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="13" customWidth="1"/>
-    <col min="7" max="7" width="21.25" style="14" customWidth="1"/>
-    <col min="8" max="8" width="55.15" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="12" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="12"/>
+    <col min="4" max="4" width="12.625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="23.625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="14" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="14" customWidth="1"/>
+    <col min="9" max="9" width="21.25" style="15" customWidth="1"/>
+    <col min="10" max="10" width="55.15" style="12" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="15" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="H2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="I2" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="E3" s="22" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" s="11" customFormat="1" spans="1:8">
-      <c r="A5" s="22">
+      <c r="F3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="32"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:10">
+      <c r="A5" s="24">
         <v>10001</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="C5" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25">
+        <v>100</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:10">
+      <c r="A6" s="24">
+        <v>10002</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25">
+        <v>200</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:10">
+      <c r="A7" s="24">
+        <v>10003</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25">
         <v>20</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="11" t="s">
+      <c r="F7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:10">
+      <c r="A8" s="24">
+        <v>10004</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25">
+        <v>50</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="34"/>
+      <c r="J8" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:11">
+      <c r="A9" s="24">
+        <v>10005</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25">
+        <v>150</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="35"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:11">
+      <c r="A10" s="24">
+        <v>10006</v>
+      </c>
+      <c r="B10" s="24">
+        <v>1</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25">
+        <v>180</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="34"/>
+      <c r="J10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="35"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="24">
+        <v>10007</v>
+      </c>
+      <c r="B11" s="24">
+        <v>1</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25">
+        <v>200</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="34"/>
+      <c r="J11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:11">
+      <c r="A12" s="24">
+        <v>10008</v>
+      </c>
+      <c r="B12" s="24">
+        <v>1</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25">
+        <v>300</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="35"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:11">
+      <c r="A13" s="24">
+        <v>10009</v>
+      </c>
+      <c r="B13" s="24">
+        <v>1</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25">
+        <v>20</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="34"/>
+      <c r="J13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="35"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:10">
+      <c r="A14" s="24">
+        <v>10010</v>
+      </c>
+      <c r="B14" s="24">
+        <v>1</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25">
+        <v>90</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="34"/>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:10">
+      <c r="A15" s="27">
+        <v>10021</v>
+      </c>
+      <c r="B15" s="27">
+        <v>1</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:8">
-      <c r="A6" s="22">
-        <v>10002</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="D15" s="27"/>
+      <c r="E15" s="28">
+        <v>500</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:10">
+      <c r="A16" s="27">
+        <v>10022</v>
+      </c>
+      <c r="B16" s="27">
         <v>1</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C16" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28">
+        <v>200</v>
+      </c>
+      <c r="F16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="G16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="H16" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:10">
+      <c r="A17" s="27">
+        <v>10023</v>
+      </c>
+      <c r="B17" s="27">
+        <v>1</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28">
         <v>20</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="11" t="s">
+      <c r="F17" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="29" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:8">
-      <c r="A7" s="22">
-        <v>10003</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="I17" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:10">
+      <c r="A18" s="27">
+        <v>10024</v>
+      </c>
+      <c r="B18" s="27">
         <v>1</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="1" spans="1:8">
-      <c r="A8" s="22">
-        <v>10004</v>
-      </c>
-      <c r="B8" s="22">
+      <c r="C18" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28">
+        <v>50</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:11">
+      <c r="A19" s="27">
+        <v>10025</v>
+      </c>
+      <c r="B19" s="27">
         <v>1</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C19" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28">
+        <v>150</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="11" t="s">
+      <c r="H19" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" s="35"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:11">
+      <c r="A20" s="27">
+        <v>10026</v>
+      </c>
+      <c r="B20" s="27">
+        <v>1</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28">
+        <v>180</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="29" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:9">
-      <c r="A9" s="22">
-        <v>10005</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="H20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="35"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="27">
+        <v>10027</v>
+      </c>
+      <c r="B21" s="27">
         <v>1</v>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="30"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:9">
-      <c r="A10" s="22">
-        <v>10006</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="C21" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28">
+        <v>500</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:11">
+      <c r="A22" s="27">
+        <v>10028</v>
+      </c>
+      <c r="B22" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="30"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="22">
-        <v>10007</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="C22" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28">
+        <v>300</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="35"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:11">
+      <c r="A23" s="27">
+        <v>10029</v>
+      </c>
+      <c r="B23" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:9">
-      <c r="A12" s="22">
-        <v>10008</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="C23" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="27"/>
+      <c r="E23" s="28">
+        <v>20</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:10">
+      <c r="A24" s="27">
+        <v>10030</v>
+      </c>
+      <c r="B24" s="27">
         <v>1</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="24"/>
-      <c r="H12" s="11" t="s">
+      <c r="C24" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:9">
-      <c r="A13" s="22">
-        <v>10009</v>
-      </c>
-      <c r="B13" s="22">
-        <v>1</v>
-      </c>
-      <c r="C13" s="22" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="28">
+        <v>500</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:8">
-      <c r="A14" s="22">
-        <v>10010</v>
-      </c>
-      <c r="B14" s="22">
-        <v>1</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" s="11" customFormat="1" spans="1:8">
-      <c r="A15" s="25">
-        <v>10021</v>
-      </c>
-      <c r="B15" s="25">
-        <v>1</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:8">
-      <c r="A16" s="25">
-        <v>10022</v>
-      </c>
-      <c r="B16" s="25">
-        <v>1</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:8">
-      <c r="A17" s="25">
-        <v>10023</v>
-      </c>
-      <c r="B17" s="25">
-        <v>1</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:8">
-      <c r="A18" s="25">
-        <v>10024</v>
-      </c>
-      <c r="B18" s="25">
-        <v>1</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:9">
-      <c r="A19" s="25">
-        <v>10025</v>
-      </c>
-      <c r="B19" s="25">
-        <v>1</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="30"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:9">
-      <c r="A20" s="25">
-        <v>10026</v>
-      </c>
-      <c r="B20" s="25">
-        <v>1</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="30"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="25">
-        <v>10027</v>
-      </c>
-      <c r="B21" s="25">
-        <v>1</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="22" s="11" customFormat="1" spans="1:9">
-      <c r="A22" s="25">
-        <v>10028</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="30"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:9">
-      <c r="A23" s="25">
-        <v>10029</v>
-      </c>
-      <c r="B23" s="25">
-        <v>1</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="30"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:8">
-      <c r="A24" s="25">
-        <v>10030</v>
-      </c>
-      <c r="B24" s="25">
-        <v>1</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="E25" s="11"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="E26" s="11"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="E27" s="11"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="E28" s="11"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="E29" s="11"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="E30" s="11"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="E31" s="11"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="E32" s="11"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="E33" s="11"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="E34" s="11"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="E35" s="11"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="E36" s="11"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="E37" s="11"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="11"/>
       <c r="D38" s="11"/>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="E38" s="11"/>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="11"/>
       <c r="D39" s="11"/>
-    </row>
-    <row r="40" spans="4:4">
+      <c r="E39" s="11"/>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="4:6">
       <c r="D40" s="11"/>
-    </row>
-    <row r="41" spans="4:4">
+      <c r="E40" s="11"/>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="4:6">
       <c r="D41" s="11"/>
-    </row>
-    <row r="42" spans="4:4">
+      <c r="E41" s="11"/>
+      <c r="F41" s="30"/>
+    </row>
+    <row r="42" spans="4:6">
       <c r="D42" s="11"/>
-    </row>
-    <row r="43" spans="4:4">
+      <c r="E42" s="11"/>
+      <c r="F42" s="30"/>
+    </row>
+    <row r="43" spans="4:6">
       <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2512,16 +2705,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2529,35 +2722,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="P6" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2565,37 +2758,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2603,37 +2796,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2641,37 +2834,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2679,37 +2872,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2717,37 +2910,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -2755,37 +2948,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -2793,19 +2986,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -2814,10 +3007,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -2825,19 +3018,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -2846,10 +3039,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -2857,28 +3050,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -2886,28 +3079,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -2915,19 +3108,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -2935,19 +3128,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -2955,22 +3148,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -2978,28 +3171,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3007,28 +3200,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3036,28 +3229,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3065,19 +3258,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3085,10 +3278,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3096,10 +3289,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3107,10 +3300,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3118,10 +3311,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3129,10 +3322,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3140,10 +3333,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3151,10 +3344,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3162,10 +3355,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3173,10 +3366,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3184,10 +3377,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -140,12 +140,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-类型_地点ID
-类型：
-1. 游戏界面：例 类型_游戏ID\0(大厅)
-2. 活动界面：例 类型_活动ID\0(大厅)
-3. 功能界面：例 类型_功能ID\0(大厅)
-*注意：在跳转时，要判断其对应功能是否存在，如果不存在默认跳到大厅即可</t>
+读取jumpData.xlsx表中的ID</t>
         </r>
       </text>
     </comment>
@@ -177,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="139">
   <si>
     <t>任务ID</t>
   </si>
@@ -206,6 +201,9 @@
     <t>开启时间</t>
   </si>
   <si>
+    <t>任务描述</t>
+  </si>
+  <si>
     <t>#任务描述</t>
   </si>
   <si>
@@ -245,15 +243,15 @@
     <t>time</t>
   </si>
   <si>
+    <t>language</t>
+  </si>
+  <si>
     <t>11001_1000_2_0</t>
   </si>
   <si>
     <t>itemicon_1022504.png</t>
   </si>
   <si>
-    <t>3_1</t>
-  </si>
-  <si>
     <t>icon.png</t>
   </si>
   <si>
@@ -269,25 +267,19 @@
     <t>12001_100100_1000000</t>
   </si>
   <si>
-    <t>1_100100</t>
-  </si>
-  <si>
-    <t>在100100游戏中，有效下注细积达到1000000</t>
+    <t>在[金矿大亨]电子游戏中，有效下注累积达到1000000</t>
   </si>
   <si>
     <t>12001_0_2000000</t>
   </si>
   <si>
-    <t>1_0</t>
-  </si>
-  <si>
     <t>在任意游戏中，有效下注累积达到2000000</t>
   </si>
   <si>
     <t>10003_100100_1_1000000_1990000</t>
   </si>
   <si>
-    <t>在100100游戏中，金币累积赢奖达到1000000</t>
+    <t>在[金矿大亨]电子游戏中，金币累积赢奖达到1000000</t>
   </si>
   <si>
     <t>10003_0_1_2000000_1990000</t>
@@ -299,25 +291,19 @@
     <t>10003_0_1_1000_1980000</t>
   </si>
   <si>
-    <t>3_2</t>
-  </si>
-  <si>
     <t>在私人房间中钻石累积赢奖达到1000</t>
   </si>
   <si>
     <t>12102_1022501_10</t>
   </si>
   <si>
-    <t>2_3</t>
-  </si>
-  <si>
-    <t>累积使用10个1022501</t>
+    <t>在[摇钱树]活动中累积使用10个[祈福卡]</t>
   </si>
   <si>
     <t>10001_100100_1_100</t>
   </si>
   <si>
-    <t>在100100电子游戏中，累积旋转100次</t>
+    <t>在[金矿大亨]电子游戏中，累积旋转100次</t>
   </si>
   <si>
     <t>10001_0_1_500</t>
@@ -339,9 +325,6 @@
   </si>
   <si>
     <t>401、402 任务类型 专用，以下道具可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>任务描述</t>
   </si>
   <si>
     <t>达成条件</t>
@@ -1775,7 +1758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
@@ -1786,13 +1769,13 @@
     <col min="6" max="6" width="23.625" style="13" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="14" customWidth="1"/>
     <col min="8" max="8" width="15.25" style="14" customWidth="1"/>
-    <col min="9" max="9" width="21.25" style="15" customWidth="1"/>
-    <col min="10" max="10" width="55.15" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="12"/>
+    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
+    <col min="11" max="11" width="55.15" style="12" customWidth="1"/>
+    <col min="12" max="12" width="14.5" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1820,69 +1803,78 @@
       <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>13</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>22</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1892,8 +1884,9 @@
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="32"/>
-    </row>
-    <row r="5" s="11" customFormat="1" spans="1:10">
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:11">
       <c r="A5" s="24">
         <v>10001</v>
       </c>
@@ -1901,27 +1894,30 @@
         <v>1</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="25">
         <v>100</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G5" s="26">
+        <v>1</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="34"/>
-      <c r="J5" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:10">
+      <c r="J5" s="34">
+        <v>70001</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:11">
       <c r="A6" s="24">
         <v>10002</v>
       </c>
@@ -1929,27 +1925,30 @@
         <v>1</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="25">
         <v>200</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G6" s="26">
+        <v>2</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="34"/>
-      <c r="J6" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:10">
+      <c r="J6" s="34">
+        <v>70002</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:11">
       <c r="A7" s="24">
         <v>10003</v>
       </c>
@@ -1957,27 +1956,30 @@
         <v>1</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="25">
         <v>20</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G7" s="26">
+        <v>3</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" s="34"/>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="34">
+        <v>70003</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" s="11" customFormat="1" spans="1:10">
+    <row r="8" s="11" customFormat="1" spans="1:11">
       <c r="A8" s="24">
         <v>10004</v>
       </c>
@@ -1992,20 +1994,23 @@
         <v>50</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="26">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34">
+        <v>70004</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:11">
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:12">
       <c r="A9" s="24">
         <v>10005</v>
       </c>
@@ -2013,28 +2018,31 @@
         <v>1</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="25">
         <v>150</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9" s="34"/>
-      <c r="J9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="35"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:11">
+      <c r="J9" s="34">
+        <v>70005</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="35"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:12">
       <c r="A10" s="24">
         <v>10006</v>
       </c>
@@ -2042,28 +2050,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="25">
         <v>180</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="G10" s="26">
+        <v>3</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I10" s="34"/>
-      <c r="J10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="35"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="J10" s="34">
+        <v>70006</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="35"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="24">
         <v>10007</v>
       </c>
@@ -2071,28 +2082,31 @@
         <v>1</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25">
         <v>200</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="G11" s="26">
+        <v>1</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" s="34"/>
-      <c r="J11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:11">
+      <c r="J11" s="34">
+        <v>70007</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:12">
       <c r="A12" s="24">
         <v>10008</v>
       </c>
@@ -2100,28 +2114,31 @@
         <v>1</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="25">
         <v>300</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="G12" s="26">
+        <v>2</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" s="34"/>
-      <c r="J12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="35"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:11">
+      <c r="J12" s="34">
+        <v>70008</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="35"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:12">
       <c r="A13" s="24">
         <v>10009</v>
       </c>
@@ -2129,28 +2146,31 @@
         <v>1</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="25">
         <v>20</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G13" s="26">
+        <v>3</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13" s="34"/>
-      <c r="J13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="35"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:10">
+      <c r="J13" s="34">
+        <v>70009</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="35"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:11">
       <c r="A14" s="24">
         <v>10010</v>
       </c>
@@ -2158,27 +2178,30 @@
         <v>1</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="25">
         <v>90</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="G14" s="26">
+        <v>1</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14" s="34"/>
-      <c r="J14" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" s="11" customFormat="1" spans="1:10">
+      <c r="J14" s="34">
+        <v>70010</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:11">
       <c r="A15" s="27">
         <v>10021</v>
       </c>
@@ -2186,29 +2209,32 @@
         <v>1</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="28">
         <v>500</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G15" s="29">
+        <v>1</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:10">
+        <v>46</v>
+      </c>
+      <c r="J15" s="36">
+        <v>70001</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:11">
       <c r="A16" s="27">
         <v>10022</v>
       </c>
@@ -2216,29 +2242,32 @@
         <v>1</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="28">
         <v>200</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G16" s="29">
+        <v>2</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:10">
+        <v>46</v>
+      </c>
+      <c r="J16" s="36">
+        <v>70002</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:11">
       <c r="A17" s="27">
         <v>10023</v>
       </c>
@@ -2246,29 +2275,32 @@
         <v>1</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="28">
         <v>20</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G17" s="29">
+        <v>3</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="36">
+        <v>70003</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" s="11" customFormat="1" spans="1:10">
+    <row r="18" s="11" customFormat="1" spans="1:11">
       <c r="A18" s="27">
         <v>10024</v>
       </c>
@@ -2283,22 +2315,25 @@
         <v>50</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="29">
+        <v>1</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="36">
+        <v>70004</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:11">
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:12">
       <c r="A19" s="27">
         <v>10025</v>
       </c>
@@ -2306,30 +2341,33 @@
         <v>1</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="28">
         <v>150</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G19" s="29">
+        <v>2</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K19" s="35"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:11">
+        <v>46</v>
+      </c>
+      <c r="J19" s="36">
+        <v>70005</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="35"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:12">
       <c r="A20" s="27">
         <v>10026</v>
       </c>
@@ -2337,30 +2375,33 @@
         <v>1</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="28">
         <v>180</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="G20" s="29">
+        <v>3</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="35"/>
-    </row>
-    <row r="21" spans="1:13">
+        <v>46</v>
+      </c>
+      <c r="J20" s="36">
+        <v>70006</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="35"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="27">
         <v>10027</v>
       </c>
@@ -2368,30 +2409,33 @@
         <v>1</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="28">
         <v>500</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="G21" s="29">
+        <v>1</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="11"/>
-    </row>
-    <row r="22" s="11" customFormat="1" spans="1:11">
+        <v>46</v>
+      </c>
+      <c r="J21" s="36">
+        <v>70007</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:12">
       <c r="A22" s="27">
         <v>10028</v>
       </c>
@@ -2399,30 +2443,33 @@
         <v>1</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D22" s="27"/>
       <c r="E22" s="28">
         <v>300</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="G22" s="29">
+        <v>2</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="35"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:11">
+        <v>46</v>
+      </c>
+      <c r="J22" s="36">
+        <v>70008</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" s="35"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:12">
       <c r="A23" s="27">
         <v>10029</v>
       </c>
@@ -2430,30 +2477,33 @@
         <v>1</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="28">
         <v>20</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G23" s="29">
+        <v>3</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="35"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:10">
+      <c r="J23" s="36">
+        <v>70009</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="35"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:11">
       <c r="A24" s="27">
         <v>10030</v>
       </c>
@@ -2461,29 +2511,32 @@
         <v>1</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="28">
         <v>500</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="G24" s="29">
+        <v>1</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>46</v>
+      </c>
+      <c r="J24" s="36">
+        <v>70010</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2493,9 +2546,10 @@
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="37"/>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="37"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2505,9 +2559,10 @@
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="37"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26" s="37"/>
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2517,9 +2572,10 @@
       <c r="G27" s="31"/>
       <c r="H27" s="31"/>
       <c r="I27" s="37"/>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27" s="37"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2529,9 +2585,10 @@
       <c r="G28" s="31"/>
       <c r="H28" s="31"/>
       <c r="I28" s="37"/>
-      <c r="J28" s="11"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="J28" s="37"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2541,9 +2598,10 @@
       <c r="G29" s="31"/>
       <c r="H29" s="31"/>
       <c r="I29" s="37"/>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="J29" s="37"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2553,9 +2611,10 @@
       <c r="G30" s="31"/>
       <c r="H30" s="31"/>
       <c r="I30" s="37"/>
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="J30" s="37"/>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2565,9 +2624,10 @@
       <c r="G31" s="31"/>
       <c r="H31" s="31"/>
       <c r="I31" s="37"/>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="37"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2577,9 +2637,10 @@
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
       <c r="I32" s="37"/>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="J32" s="37"/>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2589,9 +2650,10 @@
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
       <c r="I33" s="37"/>
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="J33" s="37"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2601,9 +2663,10 @@
       <c r="G34" s="31"/>
       <c r="H34" s="31"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="J34" s="37"/>
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2613,9 +2676,10 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="37"/>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="J35" s="37"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2625,9 +2689,10 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="37"/>
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="J36" s="37"/>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2637,7 +2702,8 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="37"/>
-      <c r="J37" s="11"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="11"/>
@@ -2705,16 +2771,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2722,35 +2788,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="P6" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2758,37 +2824,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2796,37 +2862,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2834,37 +2900,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2872,37 +2938,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2910,37 +2976,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -2948,37 +3014,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -2986,19 +3052,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3007,10 +3073,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -3018,19 +3084,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -3039,10 +3105,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3050,28 +3116,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3079,28 +3145,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -3108,19 +3174,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -3128,19 +3194,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -3148,22 +3214,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -3171,28 +3237,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3200,28 +3266,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3229,28 +3295,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3258,19 +3324,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3278,10 +3344,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3289,10 +3355,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3300,10 +3366,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3311,10 +3377,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3322,10 +3388,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3333,10 +3399,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3344,10 +3410,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3355,10 +3421,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3366,10 +3432,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3377,10 +3443,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -96,16 +96,55 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-类型_地点ID
-类型：
-1. 游戏界面：例 类型_游戏ID\0(大厅)
-2. 活动界面：例 类型_活动ID\0(大厅)
-3. 功能界面：例 类型_功能ID\0(大厅)
-*注意：在跳转时，要判断其对应功能是否存在，如果不存在默认跳到大厅即可</t>
+根据活动结束要清除数据，单独字段配置</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写道具Item资源文件夹中的道具名称</t>
         </r>
       </text>
     </comment>
     <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+读取jumpData.xlsx表中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -133,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="139">
   <si>
     <t>任务ID</t>
   </si>
@@ -144,7 +183,13 @@
     <t>任务条件</t>
   </si>
   <si>
-    <t>奖励</t>
+    <t>道具奖励</t>
+  </si>
+  <si>
+    <t>积分奖励</t>
+  </si>
+  <si>
+    <t>积分ICON</t>
   </si>
   <si>
     <t>按钮跳转类型</t>
@@ -156,6 +201,9 @@
     <t>开启时间</t>
   </si>
   <si>
+    <t>任务描述</t>
+  </si>
+  <si>
     <t>#任务描述</t>
   </si>
   <si>
@@ -180,6 +228,12 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>integralNum</t>
+  </si>
+  <si>
+    <t>integralIcon</t>
+  </si>
+  <si>
     <t>jumpType</t>
   </si>
   <si>
@@ -189,13 +243,13 @@
     <t>time</t>
   </si>
   <si>
+    <t>language</t>
+  </si>
+  <si>
     <t>11001_1000_2_0</t>
   </si>
   <si>
-    <t>1022504_100</t>
-  </si>
-  <si>
-    <t>3_1</t>
+    <t>itemicon_1022504.png</t>
   </si>
   <si>
     <t>icon.png</t>
@@ -207,90 +261,54 @@
     <t>11002_10000_0</t>
   </si>
   <si>
-    <t>1022504_200</t>
-  </si>
-  <si>
     <t>累积充值达到10000以上</t>
   </si>
   <si>
     <t>12001_100100_1000000</t>
   </si>
   <si>
-    <t>1022504_20</t>
-  </si>
-  <si>
-    <t>1_100100</t>
-  </si>
-  <si>
-    <t>在100100游戏中，有效下注细积达到1000000</t>
+    <t>在[金矿大亨]电子游戏中，有效下注累积达到1000000</t>
   </si>
   <si>
     <t>12001_0_2000000</t>
   </si>
   <si>
-    <t>1022504_50</t>
-  </si>
-  <si>
-    <t>1_0</t>
-  </si>
-  <si>
     <t>在任意游戏中，有效下注累积达到2000000</t>
   </si>
   <si>
     <t>10003_100100_1_1000000_1990000</t>
   </si>
   <si>
-    <t>1022504_150</t>
-  </si>
-  <si>
-    <t>在100100游戏中，金币累积赢奖达到1000000</t>
+    <t>在[金矿大亨]电子游戏中，金币累积赢奖达到1000000</t>
   </si>
   <si>
     <t>10003_0_1_2000000_1990000</t>
   </si>
   <si>
-    <t>1022504_180</t>
-  </si>
-  <si>
     <t>在任意游戏中，金币累积赢奖达到2000000</t>
   </si>
   <si>
     <t>10003_0_1_1000_1980000</t>
   </si>
   <si>
-    <t>1022504_500</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
     <t>在私人房间中钻石累积赢奖达到1000</t>
   </si>
   <si>
     <t>12102_1022501_10</t>
   </si>
   <si>
-    <t>1022504_300</t>
-  </si>
-  <si>
-    <t>2_3</t>
-  </si>
-  <si>
-    <t>累积使用10个1022501</t>
+    <t>在[摇钱树]活动中累积使用10个[祈福卡]</t>
   </si>
   <si>
     <t>10001_100100_1_100</t>
   </si>
   <si>
-    <t>在100100电子游戏中，累积旋转100次</t>
+    <t>在[金矿大亨]电子游戏中，累积旋转100次</t>
   </si>
   <si>
     <t>10001_0_1_500</t>
   </si>
   <si>
-    <t>1022504_90</t>
-  </si>
-  <si>
     <t>在任意电子游戏中，累积旋转500次</t>
   </si>
   <si>
@@ -307,9 +325,6 @@
   </si>
   <si>
     <t>401、402 任务类型 专用，以下道具可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>任务描述</t>
   </si>
   <si>
     <t>达成条件</t>
@@ -1289,7 +1304,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,6 +1342,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1341,47 +1359,65 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1722,761 +1758,984 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
     <col min="2" max="2" width="9.125" style="12" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="13" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="13" customWidth="1"/>
-    <col min="7" max="7" width="21.25" style="14" customWidth="1"/>
-    <col min="8" max="8" width="55.15" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="12" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="12"/>
+    <col min="4" max="4" width="12.625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="23.625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="14" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="14" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
+    <col min="11" max="11" width="55.15" style="12" customWidth="1"/>
+    <col min="12" max="12" width="14.5" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="15" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>9</v>
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>12</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="H2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="I2" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="D3" s="20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" s="11" customFormat="1" spans="1:8">
-      <c r="A5" s="22">
+      <c r="E3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:11">
+      <c r="A5" s="24">
         <v>10001</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="C5" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25">
+        <v>100</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="26">
+        <v>1</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34">
+        <v>70001</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:11">
+      <c r="A6" s="24">
+        <v>10002</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25">
+        <v>200</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="26">
+        <v>2</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34">
+        <v>70002</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:11">
+      <c r="A7" s="24">
+        <v>10003</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25">
         <v>20</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:8">
-      <c r="A6" s="22">
-        <v>10002</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="F7" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="26">
+        <v>3</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34">
+        <v>70003</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:11">
+      <c r="A8" s="24">
+        <v>10004</v>
+      </c>
+      <c r="B8" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="22" t="s">
+      <c r="C8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25">
+        <v>50</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="26">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34">
+        <v>70004</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:12">
+      <c r="A9" s="24">
+        <v>10005</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25">
+        <v>150</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34">
+        <v>70005</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="35"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:12">
+      <c r="A10" s="24">
+        <v>10006</v>
+      </c>
+      <c r="B10" s="24">
+        <v>1</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25">
+        <v>180</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="26">
+        <v>3</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34">
+        <v>70006</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="35"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="24">
+        <v>10007</v>
+      </c>
+      <c r="B11" s="24">
+        <v>1</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25">
+        <v>200</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="26">
+        <v>1</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34">
+        <v>70007</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:12">
+      <c r="A12" s="24">
+        <v>10008</v>
+      </c>
+      <c r="B12" s="24">
+        <v>1</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25">
+        <v>300</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="26">
+        <v>2</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34">
+        <v>70008</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="35"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:12">
+      <c r="A13" s="24">
+        <v>10009</v>
+      </c>
+      <c r="B13" s="24">
+        <v>1</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25">
+        <v>20</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="26">
+        <v>3</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34">
+        <v>70009</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="35"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:11">
+      <c r="A14" s="24">
+        <v>10010</v>
+      </c>
+      <c r="B14" s="24">
+        <v>1</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25">
+        <v>90</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="26">
+        <v>1</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34">
+        <v>70010</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:11">
+      <c r="A15" s="27">
+        <v>10021</v>
+      </c>
+      <c r="B15" s="27">
+        <v>1</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="D15" s="27"/>
+      <c r="E15" s="28">
+        <v>500</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="29">
+        <v>1</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="36">
+        <v>70001</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:11">
+      <c r="A16" s="27">
+        <v>10022</v>
+      </c>
+      <c r="B16" s="27">
+        <v>1</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28">
+        <v>200</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="29">
+        <v>2</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="36">
+        <v>70002</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:11">
+      <c r="A17" s="27">
+        <v>10023</v>
+      </c>
+      <c r="B17" s="27">
+        <v>1</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28">
         <v>20</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="11" t="s">
+      <c r="F17" s="28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:8">
-      <c r="A7" s="22">
-        <v>10003</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="G17" s="29">
+        <v>3</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="36">
+        <v>70003</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:11">
+      <c r="A18" s="27">
+        <v>10024</v>
+      </c>
+      <c r="B18" s="27">
         <v>1</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C18" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28">
+        <v>50</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="29">
+        <v>1</v>
+      </c>
+      <c r="H18" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="1" spans="1:8">
-      <c r="A8" s="22">
-        <v>10004</v>
-      </c>
-      <c r="B8" s="22">
+      <c r="I18" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="36">
+        <v>70004</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:12">
+      <c r="A19" s="27">
+        <v>10025</v>
+      </c>
+      <c r="B19" s="27">
         <v>1</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:9">
-      <c r="A9" s="22">
-        <v>10005</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="C19" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28">
+        <v>150</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="29">
+        <v>2</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="36">
+        <v>70005</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="35"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:12">
+      <c r="A20" s="27">
+        <v>10026</v>
+      </c>
+      <c r="B20" s="27">
         <v>1</v>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="11" t="s">
+      <c r="C20" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="30"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:9">
-      <c r="A10" s="22">
-        <v>10006</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="D20" s="27"/>
+      <c r="E20" s="28">
+        <v>180</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="29">
+        <v>3</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20" s="36">
+        <v>70006</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="35"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="27">
+        <v>10027</v>
+      </c>
+      <c r="B21" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="22" t="s">
+      <c r="C21" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="11" t="s">
+      <c r="D21" s="27"/>
+      <c r="E21" s="28">
+        <v>500</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="29">
+        <v>1</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="36">
+        <v>70007</v>
+      </c>
+      <c r="K21" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="30"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="22">
-        <v>10007</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:12">
+      <c r="A22" s="27">
+        <v>10028</v>
+      </c>
+      <c r="B22" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="22" t="s">
+      <c r="C22" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28">
+        <v>300</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="29">
+        <v>2</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="36">
+        <v>70008</v>
+      </c>
+      <c r="K22" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="L22" s="35"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:12">
+      <c r="A23" s="27">
+        <v>10029</v>
+      </c>
+      <c r="B23" s="27">
+        <v>1</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="11" t="s">
+      <c r="D23" s="27"/>
+      <c r="E23" s="28">
+        <v>20</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="29">
+        <v>3</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="36">
+        <v>70009</v>
+      </c>
+      <c r="K23" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:9">
-      <c r="A12" s="22">
-        <v>10008</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="L23" s="35"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:11">
+      <c r="A24" s="27">
+        <v>10030</v>
+      </c>
+      <c r="B24" s="27">
         <v>1</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C24" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="28">
+        <v>500</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="29">
+        <v>1</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="36">
+        <v>70010</v>
+      </c>
+      <c r="K24" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="24"/>
-      <c r="H12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:9">
-      <c r="A13" s="22">
-        <v>10009</v>
-      </c>
-      <c r="B13" s="22">
-        <v>1</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:8">
-      <c r="A14" s="22">
-        <v>10010</v>
-      </c>
-      <c r="B14" s="22">
-        <v>1</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" s="11" customFormat="1" spans="1:8">
-      <c r="A15" s="25">
-        <v>10021</v>
-      </c>
-      <c r="B15" s="25">
-        <v>1</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:8">
-      <c r="A16" s="25">
-        <v>10022</v>
-      </c>
-      <c r="B16" s="25">
-        <v>1</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:8">
-      <c r="A17" s="25">
-        <v>10023</v>
-      </c>
-      <c r="B17" s="25">
-        <v>1</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:8">
-      <c r="A18" s="25">
-        <v>10024</v>
-      </c>
-      <c r="B18" s="25">
-        <v>1</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:9">
-      <c r="A19" s="25">
-        <v>10025</v>
-      </c>
-      <c r="B19" s="25">
-        <v>1</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="30"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:9">
-      <c r="A20" s="25">
-        <v>10026</v>
-      </c>
-      <c r="B20" s="25">
-        <v>1</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="30"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="25">
-        <v>10027</v>
-      </c>
-      <c r="B21" s="25">
-        <v>1</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="22" s="11" customFormat="1" spans="1:9">
-      <c r="A22" s="25">
-        <v>10028</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="30"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:9">
-      <c r="A23" s="25">
-        <v>10029</v>
-      </c>
-      <c r="B23" s="25">
-        <v>1</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="30"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:8">
-      <c r="A24" s="25">
-        <v>10030</v>
-      </c>
-      <c r="B24" s="25">
-        <v>1</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="E25" s="11"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="E26" s="11"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="E27" s="11"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="E28" s="11"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="E29" s="11"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="E30" s="11"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="E31" s="11"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="E32" s="11"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="E33" s="11"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="E34" s="11"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="E35" s="11"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="E36" s="11"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="E37" s="11"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="11"/>
       <c r="D38" s="11"/>
-    </row>
-    <row r="39" spans="2:4">
+      <c r="E38" s="11"/>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="11"/>
       <c r="D39" s="11"/>
-    </row>
-    <row r="40" spans="4:4">
+      <c r="E39" s="11"/>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="4:6">
       <c r="D40" s="11"/>
-    </row>
-    <row r="41" spans="4:4">
+      <c r="E40" s="11"/>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="4:6">
       <c r="D41" s="11"/>
-    </row>
-    <row r="42" spans="4:4">
+      <c r="E41" s="11"/>
+      <c r="F41" s="30"/>
+    </row>
+    <row r="42" spans="4:6">
       <c r="D42" s="11"/>
-    </row>
-    <row r="43" spans="4:4">
+      <c r="E42" s="11"/>
+      <c r="F42" s="30"/>
+    </row>
+    <row r="43" spans="4:6">
       <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2512,16 +2771,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2529,35 +2788,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2565,37 +2824,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2603,37 +2862,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2641,37 +2900,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2679,37 +2938,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2717,37 +2976,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -2755,37 +3014,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -2793,19 +3052,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -2814,10 +3073,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -2825,19 +3084,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -2846,10 +3105,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -2857,28 +3116,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -2886,28 +3145,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -2915,19 +3174,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -2935,19 +3194,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -2955,22 +3214,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -2978,28 +3237,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3007,28 +3266,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3036,28 +3295,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3065,19 +3324,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3085,10 +3344,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3096,10 +3355,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3107,10 +3366,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3118,10 +3377,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3129,10 +3388,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3140,10 +3399,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3151,10 +3410,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3162,10 +3421,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3173,10 +3432,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3184,10 +3443,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -252,7 +252,7 @@
     <t>itemicon_1022504.png</t>
   </si>
   <si>
-    <t>icon.png</t>
+    <t>task_Baccarat</t>
   </si>
   <si>
     <t>进行2次单笔1000以上的充值</t>
@@ -1904,7 +1904,7 @@
         <v>25</v>
       </c>
       <c r="G5" s="26">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>26</v>
@@ -1935,7 +1935,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="26">
-        <v>2</v>
+        <v>2001</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>26</v>
@@ -1966,7 +1966,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="26">
-        <v>3</v>
+        <v>2002</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>26</v>
@@ -1997,7 +1997,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="26">
-        <v>1</v>
+        <v>2003</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>26</v>
@@ -2028,7 +2028,7 @@
         <v>25</v>
       </c>
       <c r="G9" s="26">
-        <v>2</v>
+        <v>1001</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>26</v>
@@ -2060,7 +2060,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="26">
-        <v>3</v>
+        <v>2001</v>
       </c>
       <c r="H10" s="26" t="s">
         <v>26</v>
@@ -2092,7 +2092,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="26">
-        <v>1</v>
+        <v>2002</v>
       </c>
       <c r="H11" s="26" t="s">
         <v>26</v>
@@ -2124,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="G12" s="26">
-        <v>2</v>
+        <v>2003</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>26</v>
@@ -2156,7 +2156,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="26">
-        <v>3</v>
+        <v>1001</v>
       </c>
       <c r="H13" s="26" t="s">
         <v>26</v>
@@ -2188,7 +2188,7 @@
         <v>25</v>
       </c>
       <c r="G14" s="26">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="H14" s="26" t="s">
         <v>26</v>
@@ -2219,7 +2219,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="29">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="H15" s="29" t="s">
         <v>26</v>
@@ -2252,7 +2252,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="29">
-        <v>2</v>
+        <v>2001</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>26</v>
@@ -2285,7 +2285,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="29">
-        <v>3</v>
+        <v>2002</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>26</v>
@@ -2318,7 +2318,7 @@
         <v>25</v>
       </c>
       <c r="G18" s="29">
-        <v>1</v>
+        <v>2003</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>26</v>
@@ -2351,7 +2351,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="29">
-        <v>2</v>
+        <v>1001</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>26</v>
@@ -2385,7 +2385,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="29">
-        <v>3</v>
+        <v>2001</v>
       </c>
       <c r="H20" s="29" t="s">
         <v>26</v>
@@ -2419,7 +2419,7 @@
         <v>25</v>
       </c>
       <c r="G21" s="29">
-        <v>1</v>
+        <v>2002</v>
       </c>
       <c r="H21" s="29" t="s">
         <v>26</v>
@@ -2453,7 +2453,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="29">
-        <v>2</v>
+        <v>2003</v>
       </c>
       <c r="H22" s="29" t="s">
         <v>26</v>
@@ -2487,7 +2487,7 @@
         <v>25</v>
       </c>
       <c r="G23" s="29">
-        <v>3</v>
+        <v>1001</v>
       </c>
       <c r="H23" s="29" t="s">
         <v>26</v>
@@ -2521,7 +2521,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="29">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="H24" s="29" t="s">
         <v>26</v>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="138">
   <si>
     <t>任务ID</t>
   </si>
@@ -294,7 +294,7 @@
     <t>在私人房间中钻石累积赢奖达到1000</t>
   </si>
   <si>
-    <t>12102_1022501_10</t>
+    <t>12101_1022501_10</t>
   </si>
   <si>
     <t>在[摇钱树]活动中累积使用10个[祈福卡]</t>
@@ -313,9 +313,6 @@
   </si>
   <si>
     <t>2025/10/01 00:00:00</t>
-  </si>
-  <si>
-    <t>12101_1022501_10</t>
   </si>
   <si>
     <t>以下游戏可用来配置,【策划看】</t>
@@ -2443,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D22" s="27"/>
       <c r="E22" s="28">
@@ -2771,16 +2768,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2791,32 +2788,32 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="P6" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2824,37 +2821,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2862,37 +2859,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2900,37 +2897,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2938,37 +2935,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2976,37 +2973,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -3014,37 +3011,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -3052,19 +3049,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3073,10 +3070,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -3084,19 +3081,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -3105,10 +3102,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3116,28 +3113,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3145,28 +3142,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -3174,19 +3171,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -3194,19 +3191,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -3214,22 +3211,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -3237,28 +3234,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="P20" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3266,28 +3263,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3295,28 +3292,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3324,19 +3321,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3344,10 +3341,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3355,10 +3352,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3366,10 +3363,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3377,10 +3374,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3388,10 +3385,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3399,10 +3396,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3410,10 +3407,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3421,10 +3418,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3432,10 +3429,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3443,10 +3440,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -74,11 +74,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+相同任务类型，在当前时间下，任务组ID只会读取一个进行显示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 配置 condition.xlsx 文件中的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -144,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="141">
   <si>
     <t>任务ID</t>
   </si>
@@ -180,6 +202,9 @@
     <t>任务类型</t>
   </si>
   <si>
+    <t>任务组</t>
+  </si>
+  <si>
     <t>任务条件</t>
   </si>
   <si>
@@ -222,6 +247,9 @@
     <t>taskType</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>taskConditionId</t>
   </si>
   <si>
@@ -310,6 +338,9 @@
   </si>
   <si>
     <t>在任意电子游戏中，累积旋转500次</t>
+  </si>
+  <si>
+    <t>2026/1/01 00:00:00</t>
   </si>
   <si>
     <t>2025/10/01 00:00:00</t>
@@ -798,12 +829,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1301,7 +1332,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,12 +1423,6 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1412,9 +1437,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1755,24 +1777,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="36.875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="14" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="14" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
-    <col min="11" max="11" width="55.15" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="12"/>
+    <col min="2" max="3" width="9.125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="36.875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="14" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="14" customWidth="1"/>
+    <col min="10" max="11" width="21.25" style="15" customWidth="1"/>
+    <col min="12" max="12" width="55.15" style="12" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="12" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1782,957 +1804,826 @@
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="L1" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>11</v>
+      <c r="G2" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E3" s="20" t="s">
+        <v>19</v>
+      </c>
       <c r="F3" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="19" t="s">
         <v>20</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="I3" s="19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="19"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="19"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" s="11" customFormat="1" spans="1:11">
+      <c r="I4" s="19"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:12">
       <c r="A5" s="24">
         <v>10001</v>
       </c>
       <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25">
+      <c r="C5" s="24">
+        <v>1</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25">
         <v>100</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="26">
         <v>1001</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34">
+      <c r="I5" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32">
         <v>70001</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:11">
+      <c r="L5" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:12">
       <c r="A6" s="24">
         <v>10002</v>
       </c>
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="24">
+        <v>2</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25">
+        <v>200</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="26">
+        <v>2001</v>
+      </c>
+      <c r="I6" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25">
-        <v>200</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="26">
-        <v>2001</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34">
+      <c r="J6" s="32"/>
+      <c r="K6" s="32">
         <v>70002</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:11">
+      <c r="L6" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:12">
       <c r="A7" s="24">
         <v>10003</v>
       </c>
       <c r="B7" s="24">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25">
+      <c r="C7" s="24">
+        <v>3</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25">
         <v>20</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="G7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="26">
         <v>2002</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34">
+      <c r="I7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32">
         <v>70003</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="1" spans="1:11">
+      <c r="L7" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:12">
       <c r="A8" s="24">
         <v>10004</v>
       </c>
       <c r="B8" s="24">
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25">
+      <c r="C8" s="24">
+        <v>4</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25">
         <v>50</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="26">
         <v>2003</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34">
+      <c r="I8" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32">
         <v>70004</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:12">
+      <c r="L8" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:13">
       <c r="A9" s="24">
         <v>10005</v>
       </c>
       <c r="B9" s="24">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25">
+      <c r="C9" s="24">
+        <v>5</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25">
         <v>150</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="26">
         <v>1001</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34">
+      <c r="I9" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32">
         <v>70005</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="35"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:12">
+      <c r="L9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="33"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:13">
       <c r="A10" s="24">
         <v>10006</v>
       </c>
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25">
+      <c r="C10" s="24">
+        <v>6</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25">
         <v>180</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="26">
         <v>2001</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34">
+      <c r="I10" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32">
         <v>70006</v>
       </c>
-      <c r="K10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="35"/>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="33"/>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="24">
         <v>10007</v>
       </c>
       <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25">
+      <c r="C11" s="24">
+        <v>7</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="25">
         <v>200</v>
       </c>
-      <c r="F11" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="26">
+      <c r="G11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="26">
         <v>2002</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34">
+      <c r="I11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32">
         <v>70007</v>
       </c>
-      <c r="K11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:12">
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:13">
       <c r="A12" s="24">
         <v>10008</v>
       </c>
       <c r="B12" s="24">
         <v>1</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25">
+      <c r="C12" s="24">
+        <v>8</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25">
         <v>300</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="26">
+      <c r="G12" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="26">
         <v>2003</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34">
+      <c r="I12" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32">
         <v>70008</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="35"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:12">
+      <c r="L12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="33"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:13">
       <c r="A13" s="24">
         <v>10009</v>
       </c>
       <c r="B13" s="24">
         <v>1</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25">
+      <c r="C13" s="24">
+        <v>9</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="25">
         <v>20</v>
       </c>
-      <c r="F13" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="26">
+      <c r="G13" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="26">
         <v>1001</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34">
+      <c r="I13" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32">
         <v>70009</v>
       </c>
-      <c r="K13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="35"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:11">
+      <c r="L13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="33"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:12">
       <c r="A14" s="24">
         <v>10010</v>
       </c>
       <c r="B14" s="24">
         <v>1</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25">
+      <c r="C14" s="24">
+        <v>10</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25">
         <v>90</v>
       </c>
-      <c r="F14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="26">
+      <c r="G14" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="26">
         <v>2001</v>
       </c>
-      <c r="H14" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34">
+      <c r="I14" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32">
         <v>70010</v>
       </c>
-      <c r="K14" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" s="11" customFormat="1" spans="1:11">
+      <c r="L14" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:12">
       <c r="A15" s="27">
         <v>10021</v>
       </c>
       <c r="B15" s="27">
         <v>1</v>
       </c>
-      <c r="C15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28">
+      <c r="C15" s="27">
+        <v>1</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28">
         <v>500</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="29">
         <v>1001</v>
       </c>
-      <c r="H15" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="36">
+      <c r="I15" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="34">
         <v>70001</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:11">
+      <c r="L15" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:12">
       <c r="A16" s="27">
         <v>10022</v>
       </c>
       <c r="B16" s="27">
         <v>1</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="27">
+        <v>2</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28">
+        <v>200</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="29">
+        <v>2001</v>
+      </c>
+      <c r="I16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28">
-        <v>200</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="29">
-        <v>2001</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="36">
+      <c r="J16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="34">
         <v>70002</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:11">
+      <c r="L16" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:12">
       <c r="A17" s="27">
         <v>10023</v>
       </c>
       <c r="B17" s="27">
         <v>1</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28">
+      <c r="C17" s="27">
+        <v>3</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28">
         <v>20</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="29">
         <v>2002</v>
       </c>
-      <c r="H17" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17" s="36">
+      <c r="I17" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="34">
         <v>70003</v>
       </c>
-      <c r="K17" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:11">
+      <c r="L17" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:12">
       <c r="A18" s="27">
         <v>10024</v>
       </c>
       <c r="B18" s="27">
         <v>1</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28">
+      <c r="C18" s="27">
+        <v>4</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28">
         <v>50</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="29">
         <v>2003</v>
       </c>
-      <c r="H18" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18" s="36">
+      <c r="I18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="34">
         <v>70004</v>
       </c>
-      <c r="K18" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:12">
+      <c r="L18" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:13">
       <c r="A19" s="27">
         <v>10025</v>
       </c>
       <c r="B19" s="27">
         <v>1</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28">
+      <c r="C19" s="27">
+        <v>5</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28">
         <v>150</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="29">
         <v>1001</v>
       </c>
-      <c r="H19" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="36">
+      <c r="I19" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="34">
         <v>70005</v>
       </c>
-      <c r="K19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L19" s="35"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:12">
+      <c r="L19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:13">
       <c r="A20" s="27">
         <v>10026</v>
       </c>
       <c r="B20" s="27">
         <v>1</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28">
+      <c r="C20" s="27">
+        <v>6</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="28">
         <v>180</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="29">
         <v>2001</v>
       </c>
-      <c r="H20" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20" s="36">
+      <c r="I20" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="34">
         <v>70006</v>
       </c>
-      <c r="K20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L20" s="35"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="27">
         <v>10027</v>
       </c>
       <c r="B21" s="27">
         <v>1</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28">
+      <c r="C21" s="27">
+        <v>7</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28">
         <v>500</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="29">
         <v>2002</v>
       </c>
-      <c r="H21" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="36">
+      <c r="I21" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="34">
         <v>70007</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" s="11" customFormat="1" spans="1:12">
+      <c r="L21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:13">
       <c r="A22" s="27">
         <v>10028</v>
       </c>
       <c r="B22" s="27">
         <v>1</v>
       </c>
-      <c r="C22" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28">
+      <c r="C22" s="27">
+        <v>8</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28">
         <v>300</v>
       </c>
-      <c r="F22" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="29">
+      <c r="G22" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="29">
         <v>2003</v>
       </c>
-      <c r="H22" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="36">
+      <c r="I22" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="34">
         <v>70008</v>
       </c>
-      <c r="K22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="35"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:12">
+      <c r="L22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:13">
       <c r="A23" s="27">
         <v>10029</v>
       </c>
       <c r="B23" s="27">
         <v>1</v>
       </c>
-      <c r="C23" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28">
+      <c r="C23" s="27">
+        <v>9</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28">
         <v>20</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="29">
         <v>1001</v>
       </c>
-      <c r="H23" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="36">
+      <c r="I23" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="34">
         <v>70009</v>
       </c>
-      <c r="K23" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="35"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:11">
+      <c r="L23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:12">
       <c r="A24" s="27">
         <v>10030</v>
       </c>
       <c r="B24" s="27">
         <v>1</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28">
+      <c r="C24" s="27">
+        <v>10</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28">
         <v>500</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="29">
+      <c r="G24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="29">
         <v>2001</v>
       </c>
-      <c r="H24" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="I24" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="34">
         <v>70010</v>
       </c>
-      <c r="K24" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="11"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="11"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="11"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="11"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="11"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="11"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="30"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="30"/>
-    </row>
-    <row r="40" spans="4:6">
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="30"/>
-    </row>
-    <row r="41" spans="4:6">
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="30"/>
-    </row>
-    <row r="42" spans="4:6">
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="30"/>
-    </row>
-    <row r="43" spans="4:6">
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="30"/>
+      <c r="L24" s="11" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2768,16 +2659,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2785,35 +2676,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="N6" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2821,37 +2712,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2859,37 +2750,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2897,37 +2788,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2935,37 +2826,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2973,37 +2864,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -3011,37 +2902,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -3049,19 +2940,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3070,10 +2961,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -3081,19 +2972,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -3102,10 +2993,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3113,28 +3004,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3142,28 +3033,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -3171,19 +3062,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -3191,19 +3082,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -3211,22 +3102,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -3234,28 +3125,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="P20" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3263,28 +3154,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3292,28 +3183,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3321,19 +3212,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3341,10 +3232,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3352,10 +3243,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3363,10 +3254,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3374,10 +3265,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3385,10 +3276,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3396,10 +3287,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3407,10 +3298,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3418,10 +3309,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3429,10 +3320,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3440,10 +3331,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -185,7 +185,8 @@
           </rPr>
           <t xml:space="preserve">
 空值：表示默认数据
-有日期：对应月份读取的数据</t>
+有日期：对应月份读取的数据，日期格式  “1号 - 9号”配置成“01 - 09” 2字符书写
+</t>
         </r>
       </text>
     </comment>
@@ -340,7 +341,7 @@
     <t>在任意电子游戏中，累积旋转500次</t>
   </si>
   <si>
-    <t>2026/1/01 00:00:00</t>
+    <t>2026/10/01 00:00:00</t>
   </si>
   <si>
     <t>2025/10/01 00:00:00</t>
@@ -829,12 +830,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -74,11 +74,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+相同任务类型，在当前时间下，任务组ID只会读取一个进行显示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 配置 condition.xlsx 文件中的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -144,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +185,8 @@
           </rPr>
           <t xml:space="preserve">
 空值：表示默认数据
-有日期：对应月份读取的数据</t>
+有日期：对应月份读取的数据，日期格式  “1号 - 9号”配置成“01 - 09” 2字符书写
+</t>
         </r>
       </text>
     </comment>
@@ -172,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="141">
   <si>
     <t>任务ID</t>
   </si>
@@ -180,6 +203,9 @@
     <t>任务类型</t>
   </si>
   <si>
+    <t>任务组</t>
+  </si>
+  <si>
     <t>任务条件</t>
   </si>
   <si>
@@ -222,6 +248,9 @@
     <t>taskType</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>taskConditionId</t>
   </si>
   <si>
@@ -310,6 +339,9 @@
   </si>
   <si>
     <t>在任意电子游戏中，累积旋转500次</t>
+  </si>
+  <si>
+    <t>2026/10/01 00:00:00</t>
   </si>
   <si>
     <t>2025/10/01 00:00:00</t>
@@ -1301,7 +1333,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,12 +1424,6 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1412,9 +1438,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1755,24 +1778,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="36.875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="14" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="14" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
-    <col min="11" max="11" width="55.15" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="12"/>
+    <col min="2" max="3" width="9.125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="36.875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="14" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="14" customWidth="1"/>
+    <col min="10" max="11" width="21.25" style="15" customWidth="1"/>
+    <col min="12" max="12" width="55.15" style="12" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="12" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1782,957 +1805,826 @@
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="L1" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>11</v>
+      <c r="G2" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E3" s="20" t="s">
+        <v>19</v>
+      </c>
       <c r="F3" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="19" t="s">
         <v>20</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="I3" s="19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="19"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="19"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" s="11" customFormat="1" spans="1:11">
+      <c r="I4" s="19"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:12">
       <c r="A5" s="24">
         <v>10001</v>
       </c>
       <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25">
+      <c r="C5" s="24">
+        <v>1</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25">
         <v>100</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="26">
         <v>1001</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34">
+      <c r="I5" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32">
         <v>70001</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:11">
+      <c r="L5" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:12">
       <c r="A6" s="24">
         <v>10002</v>
       </c>
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="24">
+        <v>2</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25">
+        <v>200</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="26">
+        <v>2001</v>
+      </c>
+      <c r="I6" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25">
-        <v>200</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="26">
-        <v>2001</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34">
+      <c r="J6" s="32"/>
+      <c r="K6" s="32">
         <v>70002</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:11">
+      <c r="L6" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:12">
       <c r="A7" s="24">
         <v>10003</v>
       </c>
       <c r="B7" s="24">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25">
+      <c r="C7" s="24">
+        <v>3</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25">
         <v>20</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="G7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="26">
         <v>2002</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34">
+      <c r="I7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32">
         <v>70003</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="1" spans="1:11">
+      <c r="L7" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:12">
       <c r="A8" s="24">
         <v>10004</v>
       </c>
       <c r="B8" s="24">
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25">
+      <c r="C8" s="24">
+        <v>4</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25">
         <v>50</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="26">
         <v>2003</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34">
+      <c r="I8" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32">
         <v>70004</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:12">
+      <c r="L8" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:13">
       <c r="A9" s="24">
         <v>10005</v>
       </c>
       <c r="B9" s="24">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25">
+      <c r="C9" s="24">
+        <v>5</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25">
         <v>150</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="26">
         <v>1001</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34">
+      <c r="I9" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32">
         <v>70005</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="35"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:12">
+      <c r="L9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="33"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:13">
       <c r="A10" s="24">
         <v>10006</v>
       </c>
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25">
+      <c r="C10" s="24">
+        <v>6</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25">
         <v>180</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="26">
         <v>2001</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34">
+      <c r="I10" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32">
         <v>70006</v>
       </c>
-      <c r="K10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="35"/>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="33"/>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="24">
         <v>10007</v>
       </c>
       <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25">
+      <c r="C11" s="24">
+        <v>7</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="25">
         <v>200</v>
       </c>
-      <c r="F11" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="26">
+      <c r="G11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="26">
         <v>2002</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34">
+      <c r="I11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32">
         <v>70007</v>
       </c>
-      <c r="K11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:12">
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:13">
       <c r="A12" s="24">
         <v>10008</v>
       </c>
       <c r="B12" s="24">
         <v>1</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25">
+      <c r="C12" s="24">
+        <v>8</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25">
         <v>300</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="26">
+      <c r="G12" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="26">
         <v>2003</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34">
+      <c r="I12" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32">
         <v>70008</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="35"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:12">
+      <c r="L12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="33"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:13">
       <c r="A13" s="24">
         <v>10009</v>
       </c>
       <c r="B13" s="24">
         <v>1</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25">
+      <c r="C13" s="24">
+        <v>9</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="25">
         <v>20</v>
       </c>
-      <c r="F13" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="26">
+      <c r="G13" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="26">
         <v>1001</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34">
+      <c r="I13" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32">
         <v>70009</v>
       </c>
-      <c r="K13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="35"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:11">
+      <c r="L13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="33"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:12">
       <c r="A14" s="24">
         <v>10010</v>
       </c>
       <c r="B14" s="24">
         <v>1</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25">
+      <c r="C14" s="24">
+        <v>10</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25">
         <v>90</v>
       </c>
-      <c r="F14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="26">
+      <c r="G14" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="26">
         <v>2001</v>
       </c>
-      <c r="H14" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34">
+      <c r="I14" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32">
         <v>70010</v>
       </c>
-      <c r="K14" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" s="11" customFormat="1" spans="1:11">
+      <c r="L14" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:12">
       <c r="A15" s="27">
         <v>10021</v>
       </c>
       <c r="B15" s="27">
         <v>1</v>
       </c>
-      <c r="C15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28">
+      <c r="C15" s="27">
+        <v>1</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28">
         <v>500</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="29">
         <v>1001</v>
       </c>
-      <c r="H15" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="36">
+      <c r="I15" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="34">
         <v>70001</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:11">
+      <c r="L15" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:12">
       <c r="A16" s="27">
         <v>10022</v>
       </c>
       <c r="B16" s="27">
         <v>1</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="27">
+        <v>2</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28">
+        <v>200</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="29">
+        <v>2001</v>
+      </c>
+      <c r="I16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28">
-        <v>200</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="29">
-        <v>2001</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="36">
+      <c r="J16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="34">
         <v>70002</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:11">
+      <c r="L16" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:12">
       <c r="A17" s="27">
         <v>10023</v>
       </c>
       <c r="B17" s="27">
         <v>1</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28">
+      <c r="C17" s="27">
+        <v>3</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28">
         <v>20</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="29">
         <v>2002</v>
       </c>
-      <c r="H17" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17" s="36">
+      <c r="I17" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="34">
         <v>70003</v>
       </c>
-      <c r="K17" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:11">
+      <c r="L17" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:12">
       <c r="A18" s="27">
         <v>10024</v>
       </c>
       <c r="B18" s="27">
         <v>1</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28">
+      <c r="C18" s="27">
+        <v>4</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28">
         <v>50</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="29">
         <v>2003</v>
       </c>
-      <c r="H18" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18" s="36">
+      <c r="I18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="34">
         <v>70004</v>
       </c>
-      <c r="K18" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:12">
+      <c r="L18" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:13">
       <c r="A19" s="27">
         <v>10025</v>
       </c>
       <c r="B19" s="27">
         <v>1</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28">
+      <c r="C19" s="27">
+        <v>5</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28">
         <v>150</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="29">
         <v>1001</v>
       </c>
-      <c r="H19" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="36">
+      <c r="I19" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="34">
         <v>70005</v>
       </c>
-      <c r="K19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L19" s="35"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:12">
+      <c r="L19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="33"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:13">
       <c r="A20" s="27">
         <v>10026</v>
       </c>
       <c r="B20" s="27">
         <v>1</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28">
+      <c r="C20" s="27">
+        <v>6</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="28">
         <v>180</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="29">
         <v>2001</v>
       </c>
-      <c r="H20" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20" s="36">
+      <c r="I20" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="34">
         <v>70006</v>
       </c>
-      <c r="K20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L20" s="35"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="33"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="27">
         <v>10027</v>
       </c>
       <c r="B21" s="27">
         <v>1</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28">
+      <c r="C21" s="27">
+        <v>7</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28">
         <v>500</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="29">
         <v>2002</v>
       </c>
-      <c r="H21" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="36">
+      <c r="I21" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="34">
         <v>70007</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" s="11" customFormat="1" spans="1:12">
+      <c r="L21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:13">
       <c r="A22" s="27">
         <v>10028</v>
       </c>
       <c r="B22" s="27">
         <v>1</v>
       </c>
-      <c r="C22" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28">
+      <c r="C22" s="27">
+        <v>8</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28">
         <v>300</v>
       </c>
-      <c r="F22" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="29">
+      <c r="G22" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="29">
         <v>2003</v>
       </c>
-      <c r="H22" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="36">
+      <c r="I22" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="34">
         <v>70008</v>
       </c>
-      <c r="K22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="35"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:12">
+      <c r="L22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:13">
       <c r="A23" s="27">
         <v>10029</v>
       </c>
       <c r="B23" s="27">
         <v>1</v>
       </c>
-      <c r="C23" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28">
+      <c r="C23" s="27">
+        <v>9</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28">
         <v>20</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="29">
         <v>1001</v>
       </c>
-      <c r="H23" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="36">
+      <c r="I23" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="34">
         <v>70009</v>
       </c>
-      <c r="K23" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="35"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:11">
+      <c r="L23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:12">
       <c r="A24" s="27">
         <v>10030</v>
       </c>
       <c r="B24" s="27">
         <v>1</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28">
+      <c r="C24" s="27">
+        <v>10</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28">
         <v>500</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="29">
+      <c r="G24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="29">
         <v>2001</v>
       </c>
-      <c r="H24" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="I24" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="34">
         <v>70010</v>
       </c>
-      <c r="K24" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="11"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="11"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="11"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="11"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="11"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="11"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="30"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="30"/>
-    </row>
-    <row r="40" spans="4:6">
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="30"/>
-    </row>
-    <row r="41" spans="4:6">
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="30"/>
-    </row>
-    <row r="42" spans="4:6">
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="30"/>
-    </row>
-    <row r="43" spans="4:6">
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="30"/>
+      <c r="L24" s="11" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2768,16 +2660,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2785,35 +2677,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="N6" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2821,37 +2713,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2859,37 +2751,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2897,37 +2789,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2935,37 +2827,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2973,37 +2865,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -3011,37 +2903,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -3049,19 +2941,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3070,10 +2962,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -3081,19 +2973,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -3102,10 +2994,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3113,28 +3005,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3142,28 +3034,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -3171,19 +3063,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -3191,19 +3083,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -3211,22 +3103,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -3234,28 +3126,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="P20" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3263,28 +3155,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3292,28 +3184,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3321,19 +3213,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3341,10 +3233,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3352,10 +3244,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3363,10 +3255,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3374,10 +3266,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3385,10 +3277,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3396,10 +3288,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3407,10 +3299,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3418,10 +3310,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3429,10 +3321,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3440,10 +3332,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="160">
   <si>
     <t>任务ID</t>
   </si>
@@ -233,6 +233,21 @@
     <t>#任务描述</t>
   </si>
   <si>
+    <t>价值转化</t>
+  </si>
+  <si>
+    <t>钻石价值</t>
+  </si>
+  <si>
+    <t>道具价值</t>
+  </si>
+  <si>
+    <t>金币价值</t>
+  </si>
+  <si>
+    <t>积分</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -275,13 +290,97 @@
     <t>language</t>
   </si>
   <si>
+    <t>11001_10_2_0</t>
+  </si>
+  <si>
+    <t>itemicon_1022504.png</t>
+  </si>
+  <si>
+    <t>task_Baccarat</t>
+  </si>
+  <si>
+    <t>进行2次单笔10以上的充值</t>
+  </si>
+  <si>
+    <t>充值</t>
+  </si>
+  <si>
+    <t>11002_100_0</t>
+  </si>
+  <si>
+    <t>累积充值达到100以上</t>
+  </si>
+  <si>
+    <t>12001_100100_1000000</t>
+  </si>
+  <si>
+    <t>在[金矿大亨]电子游戏中，有效下注累积达到1000000</t>
+  </si>
+  <si>
+    <t>有效下注</t>
+  </si>
+  <si>
+    <t>12001_0_4000000</t>
+  </si>
+  <si>
+    <t>在任意游戏中，有效下注累积达到4000000</t>
+  </si>
+  <si>
+    <t>10003_100100_1_1000000_1990000</t>
+  </si>
+  <si>
+    <t>在[金矿大亨]电子游戏中，金币累积赢奖达到1000000</t>
+  </si>
+  <si>
+    <t>赢奖金币</t>
+  </si>
+  <si>
+    <t>10003_0_1_2000000_1990000</t>
+  </si>
+  <si>
+    <t>在任意游戏中，金币累积赢奖达到2000000</t>
+  </si>
+  <si>
+    <t>10003_0_1_1000_1980000</t>
+  </si>
+  <si>
+    <t>在私人房间中钻石累积赢奖达到1000</t>
+  </si>
+  <si>
+    <t>赢奖钻石</t>
+  </si>
+  <si>
+    <t>12101_1022501_20</t>
+  </si>
+  <si>
+    <t>在[摇钱树]活动中累积使用20个[祈福卡]</t>
+  </si>
+  <si>
+    <t>使用祈福卡</t>
+  </si>
+  <si>
+    <t>祈福卡</t>
+  </si>
+  <si>
+    <t>10001_100100_1_100</t>
+  </si>
+  <si>
+    <t>在[金矿大亨]电子游戏中，累积旋转100次</t>
+  </si>
+  <si>
+    <t>旋转次数</t>
+  </si>
+  <si>
+    <t>10001_0_1_500</t>
+  </si>
+  <si>
+    <t>在任意电子游戏中，累积旋转500次</t>
+  </si>
+  <si>
     <t>11001_1000_2_0</t>
   </si>
   <si>
-    <t>itemicon_1022504.png</t>
-  </si>
-  <si>
-    <t>task_Baccarat</t>
+    <t>2026/10/01 00:00:00</t>
   </si>
   <si>
     <t>进行2次单笔1000以上的充值</t>
@@ -290,63 +389,24 @@
     <t>11002_10000_0</t>
   </si>
   <si>
+    <t>2025/10/01 00:00:00</t>
+  </si>
+  <si>
     <t>累积充值达到10000以上</t>
   </si>
   <si>
-    <t>12001_100100_1000000</t>
-  </si>
-  <si>
-    <t>在[金矿大亨]电子游戏中，有效下注累积达到1000000</t>
-  </si>
-  <si>
     <t>12001_0_2000000</t>
   </si>
   <si>
     <t>在任意游戏中，有效下注累积达到2000000</t>
   </si>
   <si>
-    <t>10003_100100_1_1000000_1990000</t>
-  </si>
-  <si>
-    <t>在[金矿大亨]电子游戏中，金币累积赢奖达到1000000</t>
-  </si>
-  <si>
-    <t>10003_0_1_2000000_1990000</t>
-  </si>
-  <si>
-    <t>在任意游戏中，金币累积赢奖达到2000000</t>
-  </si>
-  <si>
-    <t>10003_0_1_1000_1980000</t>
-  </si>
-  <si>
-    <t>在私人房间中钻石累积赢奖达到1000</t>
-  </si>
-  <si>
     <t>12101_1022501_10</t>
   </si>
   <si>
     <t>在[摇钱树]活动中累积使用10个[祈福卡]</t>
   </si>
   <si>
-    <t>10001_100100_1_100</t>
-  </si>
-  <si>
-    <t>在[金矿大亨]电子游戏中，累积旋转100次</t>
-  </si>
-  <si>
-    <t>10001_0_1_500</t>
-  </si>
-  <si>
-    <t>在任意电子游戏中，累积旋转500次</t>
-  </si>
-  <si>
-    <t>2026/10/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/10/01 00:00:00</t>
-  </si>
-  <si>
     <t>以下游戏可用来配置,【策划看】</t>
   </si>
   <si>
@@ -393,9 +453,6 @@
   </si>
   <si>
     <t>领取任意奖励</t>
-  </si>
-  <si>
-    <t>祈福卡</t>
   </si>
   <si>
     <t>游戏中产出 (不是礼包获得)</t>
@@ -1778,7 +1835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="12" customWidth="1"/>
@@ -1792,10 +1849,12 @@
     <col min="10" max="11" width="21.25" style="15" customWidth="1"/>
     <col min="12" max="12" width="55.15" style="12" customWidth="1"/>
     <col min="13" max="13" width="14.5" style="12" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="12"/>
+    <col min="14" max="16" width="9.25" style="12"/>
+    <col min="17" max="18" width="14.125" style="12"/>
+    <col min="19" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:21">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1832,75 +1891,90 @@
       <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="Q1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1916,7 +1990,7 @@
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
     </row>
-    <row r="5" s="11" customFormat="1" spans="1:12">
+    <row r="5" s="11" customFormat="1" spans="1:21">
       <c r="A5" s="24">
         <v>10001</v>
       </c>
@@ -1927,30 +2001,52 @@
         <v>1</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="25">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H5" s="26">
         <v>1001</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J5" s="32"/>
       <c r="K5" s="32">
         <v>70001</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" s="11" customFormat="1" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="11">
+        <v>2</v>
+      </c>
+      <c r="P5" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="11">
+        <f>P5*N5</f>
+        <v>20</v>
+      </c>
+      <c r="R5" s="27">
+        <f>Q5</f>
+        <v>20</v>
+      </c>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:21">
       <c r="A6" s="24">
         <v>10002</v>
       </c>
@@ -1961,30 +2057,52 @@
         <v>2</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="25">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H6" s="26">
         <v>2001</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="32">
         <v>70002</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" s="11" customFormat="1" spans="1:12">
+        <v>37</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1</v>
+      </c>
+      <c r="P6" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="11">
+        <f>P6*N6</f>
+        <v>100</v>
+      </c>
+      <c r="R6" s="27">
+        <f>Q6</f>
+        <v>100</v>
+      </c>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:21">
       <c r="A7" s="24">
         <v>10003</v>
       </c>
@@ -1995,30 +2113,49 @@
         <v>3</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H7" s="26">
         <v>2002</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J7" s="32"/>
       <c r="K7" s="32">
         <v>70003</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="1" spans="1:12">
+        <v>39</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="Q7" s="11">
+        <f>N7</f>
+        <v>1000000</v>
+      </c>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27">
+        <f>Q7/100000</f>
+        <v>10</v>
+      </c>
+      <c r="U7" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:21">
       <c r="A8" s="24">
         <v>10004</v>
       </c>
@@ -2029,30 +2166,49 @@
         <v>4</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="25">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H8" s="26">
         <v>2003</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J8" s="32"/>
       <c r="K8" s="32">
         <v>70004</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="1" spans="1:13">
+        <v>42</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="11">
+        <v>4000000</v>
+      </c>
+      <c r="Q8" s="11">
+        <f>N8</f>
+        <v>4000000</v>
+      </c>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27">
+        <f>Q8/100000</f>
+        <v>40</v>
+      </c>
+      <c r="U8" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:21">
       <c r="A9" s="24">
         <v>10005</v>
       </c>
@@ -2063,31 +2219,48 @@
         <v>5</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="25">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H9" s="26">
         <v>1001</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="32">
         <v>70005</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="33"/>
-    </row>
-    <row r="10" s="11" customFormat="1" spans="1:13">
+        <v>44</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27">
+        <f>Q9/100000</f>
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:21">
       <c r="A10" s="24">
         <v>10006</v>
       </c>
@@ -2098,31 +2271,48 @@
         <v>6</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="25">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H10" s="26">
         <v>2001</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="32">
         <v>70006</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="33"/>
-    </row>
-    <row r="11" spans="1:15">
+        <v>47</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27">
+        <f>Q10/100000</f>
+        <v>20</v>
+      </c>
+      <c r="U10" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="24">
         <v>10007</v>
       </c>
@@ -2133,31 +2323,52 @@
         <v>7</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="25">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H11" s="26">
         <v>2002</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J11" s="32"/>
       <c r="K11" s="32">
         <v>70007</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:13">
+        <v>49</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="12">
+        <v>1000</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0.97</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>N11/P11</f>
+        <v>1030.92783505155</v>
+      </c>
+      <c r="R11" s="27">
+        <f>Q11/100</f>
+        <v>10.3092783505155</v>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:21">
       <c r="A12" s="24">
         <v>10008</v>
       </c>
@@ -2168,31 +2379,55 @@
         <v>8</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="25">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H12" s="26">
         <v>2003</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32">
         <v>70008</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="33"/>
-    </row>
-    <row r="13" s="11" customFormat="1" spans="1:13">
+        <v>52</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="11">
+        <v>20</v>
+      </c>
+      <c r="O12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12">
+        <v>0.25</v>
+      </c>
+      <c r="Q12" s="11">
+        <f>P12*N12</f>
+        <v>5</v>
+      </c>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27">
+        <f>Q12</f>
+        <v>5</v>
+      </c>
+      <c r="T12" s="27"/>
+      <c r="U12" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:21">
       <c r="A13" s="24">
         <v>10009</v>
       </c>
@@ -2203,31 +2438,49 @@
         <v>9</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="25">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H13" s="26">
         <v>1001</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J13" s="32"/>
       <c r="K13" s="32">
         <v>70009</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="33"/>
-    </row>
-    <row r="14" s="11" customFormat="1" spans="1:12">
+        <v>56</v>
+      </c>
+      <c r="M13" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="11">
+        <f>N13*100</f>
+        <v>10000</v>
+      </c>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27">
+        <f>Q13/100000</f>
+        <v>0.1</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:21">
       <c r="A14" s="24">
         <v>10010</v>
       </c>
@@ -2238,27 +2491,46 @@
         <v>10</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="25">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H14" s="26">
         <v>2001</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="32">
         <v>70010</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="11">
+        <v>500</v>
+      </c>
+      <c r="Q14" s="11">
+        <f>N14*100</f>
+        <v>50000</v>
+      </c>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27">
+        <f>Q14/100000</f>
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="15" s="11" customFormat="1" spans="1:12">
@@ -2272,29 +2544,29 @@
         <v>1</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="28">
         <v>500</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H15" s="29">
         <v>1001</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K15" s="34">
         <v>70001</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" s="11" customFormat="1" spans="1:12">
@@ -2308,29 +2580,29 @@
         <v>2</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="28">
         <v>200</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H16" s="29">
         <v>2001</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K16" s="34">
         <v>70002</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" s="11" customFormat="1" spans="1:12">
@@ -2344,29 +2616,29 @@
         <v>3</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28">
         <v>20</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H17" s="29">
         <v>2002</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J17" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K17" s="34">
         <v>70003</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:12">
@@ -2380,29 +2652,29 @@
         <v>4</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="28">
         <v>50</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H18" s="29">
         <v>2003</v>
       </c>
       <c r="I18" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J18" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K18" s="34">
         <v>70004</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" s="11" customFormat="1" spans="1:13">
@@ -2416,29 +2688,29 @@
         <v>5</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="28">
         <v>150</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H19" s="29">
         <v>1001</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K19" s="34">
         <v>70005</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M19" s="33"/>
     </row>
@@ -2453,29 +2725,29 @@
         <v>6</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="28">
         <v>180</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H20" s="29">
         <v>2001</v>
       </c>
       <c r="I20" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K20" s="34">
         <v>70006</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M20" s="33"/>
     </row>
@@ -2490,29 +2762,29 @@
         <v>7</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="28">
         <v>500</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H21" s="29">
         <v>2002</v>
       </c>
       <c r="I21" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K21" s="34">
         <v>70007</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O21" s="11"/>
     </row>
@@ -2527,29 +2799,29 @@
         <v>8</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28">
         <v>300</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H22" s="29">
         <v>2003</v>
       </c>
       <c r="I22" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J22" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K22" s="34">
         <v>70008</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M22" s="33"/>
     </row>
@@ -2564,29 +2836,29 @@
         <v>9</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28">
         <v>20</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H23" s="29">
         <v>1001</v>
       </c>
       <c r="I23" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K23" s="34">
         <v>70009</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M23" s="33"/>
     </row>
@@ -2601,29 +2873,29 @@
         <v>10</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="28">
         <v>500</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H24" s="29">
         <v>2001</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K24" s="34">
         <v>70010</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2660,16 +2932,16 @@
   <sheetData>
     <row r="5" spans="6:14">
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J5" s="6">
         <v>502</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -2680,32 +2952,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2713,37 +2985,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2751,37 +3023,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -2789,37 +3061,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -2827,37 +3099,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -2865,37 +3137,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -2903,37 +3175,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -2941,19 +3213,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -2962,10 +3234,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -2973,19 +3245,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -2994,10 +3266,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3005,28 +3277,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3034,28 +3306,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -3063,19 +3335,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -3083,19 +3355,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -3103,22 +3375,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -3126,28 +3398,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3155,28 +3427,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3184,28 +3456,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="6:16">
@@ -3213,19 +3485,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="6:8">
@@ -3233,10 +3505,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="6:8">
@@ -3244,10 +3516,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="6:8">
@@ -3255,10 +3527,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="6:8">
@@ -3266,10 +3538,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="6:8">
@@ -3277,10 +3549,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="6:8">
@@ -3288,10 +3560,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="6:8">
@@ -3299,10 +3571,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="6:8">
@@ -3310,10 +3582,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="6:8">
@@ -3321,10 +3593,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3332,10 +3604,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -190,12 +190,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+如果是单笔充值类型，则值 = 金额*100  
+例 值 = 9.99 *100 = 999 </t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="159">
   <si>
     <t>任务ID</t>
   </si>
@@ -290,16 +313,19 @@
     <t>language</t>
   </si>
   <si>
-    <t>11001_10_2_0</t>
+    <t>11001_999_2_0</t>
   </si>
   <si>
     <t>itemicon_1022504.png</t>
   </si>
   <si>
-    <t>task_Baccarat</t>
-  </si>
-  <si>
-    <t>进行2次单笔10以上的充值</t>
+    <t>task_Recharge</t>
+  </si>
+  <si>
+    <t>70001</t>
+  </si>
+  <si>
+    <t>進行2次單筆充值$9.99</t>
   </si>
   <si>
     <t>充值</t>
@@ -308,13 +334,16 @@
     <t>11002_100_0</t>
   </si>
   <si>
-    <t>累积充值达到100以上</t>
+    <t>累積充值達到$100.00</t>
   </si>
   <si>
     <t>12001_100100_1000000</t>
   </si>
   <si>
-    <t>在[金矿大亨]电子游戏中，有效下注累积达到1000000</t>
+    <t>task_GoldMineTycoon</t>
+  </si>
+  <si>
+    <t>在[金礦大亨]電子遊戲中，金币有效下注累積達到1,000,000</t>
   </si>
   <si>
     <t>有效下注</t>
@@ -323,13 +352,16 @@
     <t>12001_0_4000000</t>
   </si>
   <si>
-    <t>在任意游戏中，有效下注累积达到4000000</t>
+    <t>task_Anygame</t>
+  </si>
+  <si>
+    <t>在任意遊戲中，金币有效下注累積達到4,000,000</t>
   </si>
   <si>
     <t>10003_100100_1_1000000_1990000</t>
   </si>
   <si>
-    <t>在[金矿大亨]电子游戏中，金币累积赢奖达到1000000</t>
+    <t>在[金礦大亨]電子遊戲中，金币累積贏獎達到1,000,000</t>
   </si>
   <si>
     <t>赢奖金币</t>
@@ -338,22 +370,28 @@
     <t>10003_0_1_2000000_1990000</t>
   </si>
   <si>
-    <t>在任意游戏中，金币累积赢奖达到2000000</t>
+    <t>在任意遊戲中，金币累積贏獎達到2,000,000</t>
   </si>
   <si>
     <t>10003_0_1_1000_1980000</t>
   </si>
   <si>
-    <t>在私人房间中钻石累积赢奖达到1000</t>
+    <t>task_win diamonds</t>
+  </si>
+  <si>
+    <t>在私人房間中鑽石累積贏獎達到1,000</t>
   </si>
   <si>
     <t>赢奖钻石</t>
   </si>
   <si>
-    <t>12101_1022501_20</t>
-  </si>
-  <si>
-    <t>在[摇钱树]活动中累积使用20个[祈福卡]</t>
+    <t>12101_1022501_10</t>
+  </si>
+  <si>
+    <t>task_MoneyTree</t>
+  </si>
+  <si>
+    <t>在[搖錢樹]活動中累積使用10個[祈福卡]</t>
   </si>
   <si>
     <t>使用祈福卡</t>
@@ -365,7 +403,10 @@
     <t>10001_100100_1_100</t>
   </si>
   <si>
-    <t>在[金矿大亨]电子游戏中，累积旋转100次</t>
+    <t>task_rotation times</t>
+  </si>
+  <si>
+    <t>在[金礦大亨]電子遊戲中，累積旋轉100次</t>
   </si>
   <si>
     <t>旋转次数</t>
@@ -374,37 +415,16 @@
     <t>10001_0_1_500</t>
   </si>
   <si>
-    <t>在任意电子游戏中，累积旋转500次</t>
-  </si>
-  <si>
-    <t>11001_1000_2_0</t>
+    <t>在任意電子遊戲中，累積旋轉500次</t>
+  </si>
+  <si>
+    <t>11001_9_2_0</t>
   </si>
   <si>
     <t>2026/10/01 00:00:00</t>
   </si>
   <si>
-    <t>进行2次单笔1000以上的充值</t>
-  </si>
-  <si>
-    <t>11002_10000_0</t>
-  </si>
-  <si>
     <t>2025/10/01 00:00:00</t>
-  </si>
-  <si>
-    <t>累积充值达到10000以上</t>
-  </si>
-  <si>
-    <t>12001_0_2000000</t>
-  </si>
-  <si>
-    <t>在任意游戏中，有效下注累积达到2000000</t>
-  </si>
-  <si>
-    <t>12101_1022501_10</t>
-  </si>
-  <si>
-    <t>在[摇钱树]活动中累积使用10个[祈福卡]</t>
   </si>
   <si>
     <t>以下游戏可用来配置,【策划看】</t>
@@ -703,19 +723,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -728,6 +742,12 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1397,25 +1417,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1451,12 +1471,18 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1472,7 +1498,13 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -1480,18 +1512,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1845,7 +1865,7 @@
     <col min="6" max="6" width="13.125" style="12" customWidth="1"/>
     <col min="7" max="7" width="23.625" style="13" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="14" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="14" customWidth="1"/>
+    <col min="9" max="9" width="22.875" style="14" customWidth="1"/>
     <col min="10" max="11" width="21.25" style="15" customWidth="1"/>
     <col min="12" max="12" width="55.15" style="12" customWidth="1"/>
     <col min="13" max="13" width="14.5" style="12" customWidth="1"/>
@@ -1882,10 +1902,10 @@
       <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="12" t="s">
@@ -1907,7 +1927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:21">
       <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
@@ -1920,29 +1940,29 @@
       <c r="D2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:21">
       <c r="A3" s="16" t="s">
         <v>20</v>
       </c>
@@ -1955,13 +1975,13 @@
       <c r="D3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="24" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="19" t="s">
@@ -1970,61 +1990,61 @@
       <c r="I3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:21">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="5" s="11" customFormat="1" spans="1:21">
-      <c r="A5" s="24">
+      <c r="A5" s="26">
         <v>10001</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>1</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="25">
+      <c r="E5" s="26"/>
+      <c r="F5" s="27">
         <v>20</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="28">
         <v>1001</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32">
-        <v>70001</v>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29" t="s">
+        <v>34</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N5" s="11">
         <v>2</v>
@@ -2036,51 +2056,51 @@
         <f>P5*N5</f>
         <v>20</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="30">
         <f>Q5</f>
         <v>20</v>
       </c>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
       <c r="U5" s="11">
         <v>20</v>
       </c>
     </row>
     <row r="6" s="11" customFormat="1" spans="1:21">
-      <c r="A6" s="24">
+      <c r="A6" s="26">
         <v>10002</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <v>1</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27">
+        <v>100</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="28">
+        <v>2001</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29">
+        <v>70002</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25">
-        <v>100</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2001</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32">
-        <v>70002</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="N6" s="11">
         <v>1</v>
@@ -2092,51 +2112,51 @@
         <f>P6*N6</f>
         <v>100</v>
       </c>
-      <c r="R6" s="27">
+      <c r="R6" s="30">
         <f>Q6</f>
         <v>100</v>
       </c>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
       <c r="U6" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="7" s="11" customFormat="1" spans="1:21">
-      <c r="A7" s="24">
+      <c r="A7" s="26">
         <v>10003</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <v>1</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <v>3</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="25">
+      <c r="D7" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27">
         <v>10</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="28">
         <v>2002</v>
       </c>
-      <c r="I7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32">
+      <c r="I7" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29">
         <v>70003</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N7" s="11">
         <v>1000000</v>
@@ -2145,9 +2165,9 @@
         <f>N7</f>
         <v>1000000</v>
       </c>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="27">
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30">
         <f>Q7/100000</f>
         <v>10</v>
       </c>
@@ -2156,40 +2176,40 @@
       </c>
     </row>
     <row r="8" s="11" customFormat="1" spans="1:21">
-      <c r="A8" s="24">
+      <c r="A8" s="26">
         <v>10004</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="26">
         <v>1</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>4</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25">
+      <c r="D8" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="27">
         <v>40</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="28">
         <v>2003</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32">
+      <c r="I8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29">
         <v>70004</v>
       </c>
       <c r="L8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>40</v>
       </c>
       <c r="N8" s="11">
         <v>4000000</v>
@@ -2198,9 +2218,9 @@
         <f>N8</f>
         <v>4000000</v>
       </c>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27">
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30">
         <f>Q8/100000</f>
         <v>40</v>
       </c>
@@ -2209,40 +2229,40 @@
       </c>
     </row>
     <row r="9" s="11" customFormat="1" spans="1:21">
-      <c r="A9" s="24">
+      <c r="A9" s="26">
         <v>10005</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <v>1</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>5</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="25">
+      <c r="D9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="27">
         <v>10</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="28">
         <v>1001</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32">
+      <c r="I9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29">
         <v>70005</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N9" s="11">
         <v>1000000</v>
@@ -2250,9 +2270,9 @@
       <c r="Q9" s="11">
         <v>1000000</v>
       </c>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27">
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30">
         <f>Q9/100000</f>
         <v>10</v>
       </c>
@@ -2261,40 +2281,40 @@
       </c>
     </row>
     <row r="10" s="11" customFormat="1" spans="1:21">
-      <c r="A10" s="24">
+      <c r="A10" s="26">
         <v>10006</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="26">
         <v>1</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="26">
         <v>6</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="25">
+      <c r="D10" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27">
         <v>20</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="28">
         <v>2001</v>
       </c>
-      <c r="I10" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32">
+      <c r="I10" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29">
         <v>70006</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N10" s="11">
         <v>2000000</v>
@@ -2302,9 +2322,9 @@
       <c r="Q10" s="11">
         <v>2000000</v>
       </c>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27">
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30">
         <f>Q10/100000</f>
         <v>20</v>
       </c>
@@ -2313,40 +2333,40 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="24">
+      <c r="A11" s="26">
         <v>10007</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <v>1</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>7</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25">
+      <c r="D11" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27">
         <v>10</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="28">
         <v>2002</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32">
+      <c r="I11" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29">
         <v>70007</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N11" s="12">
         <v>1000</v>
@@ -2358,57 +2378,57 @@
         <f>N11/P11</f>
         <v>1030.92783505155</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="30">
         <f>Q11/100</f>
         <v>10.3092783505155</v>
       </c>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
       <c r="U11" s="12">
         <v>10</v>
       </c>
     </row>
     <row r="12" s="11" customFormat="1" spans="1:21">
-      <c r="A12" s="24">
+      <c r="A12" s="26">
         <v>10008</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="26">
         <v>1</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="26">
         <v>8</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25">
+      <c r="D12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27">
         <v>5</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="28">
         <v>2003</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32">
+      <c r="I12" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29">
         <v>70008</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N12" s="11">
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P12">
         <v>0.25</v>
@@ -2417,51 +2437,51 @@
         <f>P12*N12</f>
         <v>5</v>
       </c>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27">
+      <c r="R12" s="30"/>
+      <c r="S12" s="30">
         <f>Q12</f>
         <v>5</v>
       </c>
-      <c r="T12" s="27"/>
+      <c r="T12" s="30"/>
       <c r="U12" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="13" s="11" customFormat="1" spans="1:21">
-      <c r="A13" s="24">
+      <c r="A13" s="26">
         <v>10009</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="26">
         <v>1</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="26">
         <v>9</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25">
+      <c r="D13" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27">
         <v>1</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="28">
         <v>1001</v>
       </c>
-      <c r="I13" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32">
+      <c r="I13" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29">
         <v>70009</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="33" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="M13" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="N13" s="11">
         <v>100</v>
@@ -2470,9 +2490,9 @@
         <f>N13*100</f>
         <v>10000</v>
       </c>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27">
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30">
         <f>Q13/100000</f>
         <v>0.1</v>
       </c>
@@ -2481,40 +2501,40 @@
       </c>
     </row>
     <row r="14" s="11" customFormat="1" spans="1:21">
-      <c r="A14" s="24">
+      <c r="A14" s="26">
         <v>10010</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="26">
         <v>1</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="26">
         <v>10</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25">
+      <c r="D14" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27">
         <v>5</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="28">
         <v>2001</v>
       </c>
-      <c r="I14" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32">
+      <c r="I14" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29">
         <v>70010</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N14" s="11">
         <v>500</v>
@@ -2523,9 +2543,9 @@
         <f>N14*100</f>
         <v>50000</v>
       </c>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27">
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30">
         <f>Q14/100000</f>
         <v>0.5</v>
       </c>
@@ -2533,369 +2553,369 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" s="11" customFormat="1" spans="1:12">
-      <c r="A15" s="27">
+    <row r="15" s="11" customFormat="1" spans="1:21">
+      <c r="A15" s="30">
         <v>10021</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="30">
         <v>1</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="30">
         <v>1</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28">
-        <v>500</v>
-      </c>
-      <c r="G15" s="28" t="s">
+      <c r="D15" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="32">
+        <v>20</v>
+      </c>
+      <c r="G15" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="33">
         <v>1001</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="33" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K15" s="34">
         <v>70001</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" spans="1:12">
-      <c r="A16" s="27">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:21">
+      <c r="A16" s="30">
         <v>10022</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="30">
         <v>1</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="30">
         <v>2</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28">
-        <v>200</v>
-      </c>
-      <c r="G16" s="28" t="s">
+      <c r="D16" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="30"/>
+      <c r="F16" s="32">
+        <v>100</v>
+      </c>
+      <c r="G16" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="33">
         <v>2001</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="33" t="s">
         <v>33</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K16" s="34">
         <v>70002</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" spans="1:12">
-      <c r="A17" s="27">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:15">
+      <c r="A17" s="30">
         <v>10023</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="30">
         <v>1</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="30">
         <v>3</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28">
-        <v>20</v>
-      </c>
-      <c r="G17" s="28" t="s">
+      <c r="D17" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="30"/>
+      <c r="F17" s="32">
+        <v>10</v>
+      </c>
+      <c r="G17" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="33">
         <v>2002</v>
       </c>
-      <c r="I17" s="29" t="s">
-        <v>33</v>
+      <c r="I17" s="33" t="s">
+        <v>40</v>
       </c>
       <c r="J17" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K17" s="34">
         <v>70003</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:12">
-      <c r="A18" s="27">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:15">
+      <c r="A18" s="30">
         <v>10024</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="30">
         <v>1</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="30">
         <v>4</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="28">
-        <v>50</v>
-      </c>
-      <c r="G18" s="28" t="s">
+      <c r="D18" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="32">
+        <v>40</v>
+      </c>
+      <c r="G18" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="33">
         <v>2003</v>
       </c>
-      <c r="I18" s="29" t="s">
-        <v>33</v>
+      <c r="I18" s="33" t="s">
+        <v>44</v>
       </c>
       <c r="J18" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K18" s="34">
         <v>70004</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" spans="1:13">
-      <c r="A19" s="27">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:15">
+      <c r="A19" s="30">
         <v>10025</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="30">
         <v>1</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="30">
         <v>5</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28">
-        <v>150</v>
-      </c>
-      <c r="G19" s="28" t="s">
+      <c r="D19" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="30"/>
+      <c r="F19" s="32">
+        <v>10</v>
+      </c>
+      <c r="G19" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="33">
         <v>1001</v>
       </c>
-      <c r="I19" s="29" t="s">
-        <v>33</v>
+      <c r="I19" s="33" t="s">
+        <v>40</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K19" s="34">
         <v>70005</v>
       </c>
       <c r="L19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="31"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:15">
+      <c r="A20" s="30">
+        <v>10026</v>
+      </c>
+      <c r="B20" s="30">
+        <v>1</v>
+      </c>
+      <c r="C20" s="30">
+        <v>6</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="32">
+        <v>20</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="33">
+        <v>2001</v>
+      </c>
+      <c r="I20" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="M19" s="33"/>
-    </row>
-    <row r="20" s="11" customFormat="1" spans="1:13">
-      <c r="A20" s="27">
-        <v>10026</v>
-      </c>
-      <c r="B20" s="27">
-        <v>1</v>
-      </c>
-      <c r="C20" s="27">
-        <v>6</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28">
-        <v>180</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="29">
-        <v>2001</v>
-      </c>
-      <c r="I20" s="29" t="s">
-        <v>33</v>
-      </c>
       <c r="J20" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K20" s="34">
         <v>70006</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M20" s="33"/>
+        <v>50</v>
+      </c>
+      <c r="M20" s="31"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="27">
+      <c r="A21" s="30">
         <v>10027</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="30">
         <v>1</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="30">
         <v>7</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="28">
-        <v>500</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="D21" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="32">
+        <v>10</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="33">
         <v>2002</v>
       </c>
-      <c r="I21" s="29" t="s">
-        <v>33</v>
+      <c r="I21" s="33" t="s">
+        <v>52</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K21" s="34">
         <v>70007</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O21" s="11"/>
     </row>
-    <row r="22" s="11" customFormat="1" spans="1:13">
-      <c r="A22" s="27">
+    <row r="22" s="11" customFormat="1" spans="1:15">
+      <c r="A22" s="30">
         <v>10028</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="30">
         <v>1</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="30">
         <v>8</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="30"/>
+      <c r="F22" s="32">
+        <v>5</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="33">
+        <v>2003</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="34" t="s">
         <v>68</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28">
-        <v>300</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="29">
-        <v>2003</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="34" t="s">
-        <v>64</v>
       </c>
       <c r="K22" s="34">
         <v>70008</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="M22" s="33"/>
-    </row>
-    <row r="23" s="11" customFormat="1" spans="1:13">
-      <c r="A23" s="27">
+        <v>57</v>
+      </c>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:15">
+      <c r="A23" s="30">
         <v>10029</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="30">
         <v>1</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="30">
         <v>9</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28">
-        <v>20</v>
-      </c>
-      <c r="G23" s="28" t="s">
+      <c r="D23" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="32">
+        <v>1</v>
+      </c>
+      <c r="G23" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="33">
         <v>1001</v>
       </c>
-      <c r="I23" s="29" t="s">
-        <v>33</v>
+      <c r="I23" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K23" s="34">
         <v>70009</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" s="33"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:12">
-      <c r="A24" s="27">
+        <v>62</v>
+      </c>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:15">
+      <c r="A24" s="30">
         <v>10030</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="30">
         <v>1</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="30">
         <v>10</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28">
-        <v>500</v>
-      </c>
-      <c r="G24" s="28" t="s">
+      <c r="D24" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="30"/>
+      <c r="F24" s="32">
+        <v>5</v>
+      </c>
+      <c r="G24" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="33">
         <v>2001</v>
       </c>
-      <c r="I24" s="29" t="s">
-        <v>33</v>
+      <c r="I24" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K24" s="34">
         <v>70010</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2930,54 +2950,54 @@
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="6:14">
+    <row r="5" spans="2:16">
       <c r="F5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="2">
+        <v>502</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="6">
-        <v>502</v>
-      </c>
-      <c r="K5" s="6" t="s">
+      <c r="N5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="4" t="s">
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="2:16">
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>73</v>
+      <c r="P6" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2985,37 +3005,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="F7" s="1">
         <v>100100</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="N7" s="1">
         <v>1022501</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -3023,37 +3043,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1">
         <v>100300</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8" s="1">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="N8" s="1">
         <v>1022502</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -3061,37 +3081,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="F9" s="1">
         <v>100700</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="1">
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="N9" s="1">
         <v>1010301</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -3099,37 +3119,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F10" s="1">
         <v>101200</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N10" s="1">
         <v>1010302</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -3137,37 +3157,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" s="1">
         <v>101400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="N11" s="1">
         <v>1010303</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -3175,37 +3195,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F12" s="1">
         <v>200100</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="8">
+        <v>12</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="9">
-        <v>12</v>
-      </c>
-      <c r="K12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="N12" s="1">
         <v>1010311</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -3213,31 +3233,31 @@
         <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F13" s="1">
         <v>200101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+        <v>114</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
       <c r="N13" s="1">
         <v>1010312</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -3245,31 +3265,31 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F14" s="1">
         <v>200300</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+        <v>118</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
       <c r="N14" s="1">
         <v>1010313</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3277,28 +3297,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F15" s="1">
         <v>200400</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N15" s="1">
         <v>1010314</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -3306,120 +3326,120 @@
         <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F16" s="1">
         <v>200500</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N16" s="1">
         <v>1010315</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16">
+      <c r="B17" s="3">
+        <v>401</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="4">
-        <v>401</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>93</v>
+      <c r="D17" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="F17" s="1">
         <v>200600</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16">
+      <c r="B18" s="3">
+        <v>402</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="4">
-        <v>402</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>99</v>
+      <c r="D18" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="F18" s="1">
         <v>200700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
+      <c r="B19" s="10">
+        <v>501</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="2:14">
-      <c r="B19" s="5">
-        <v>501</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="F19" s="1">
         <v>200800</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N19" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="N19" s="5" t="s">
+    </row>
+    <row r="20" spans="2:16">
+      <c r="B20" s="2">
+        <v>502</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="20" spans="2:16">
-      <c r="B20" s="6">
-        <v>502</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="F20" s="1">
         <v>200900</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>73</v>
+      <c r="P20" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3427,28 +3447,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="F21" s="1">
         <v>201000</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N21" s="1">
         <v>1022501</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -3456,147 +3476,147 @@
         <v>602</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="F22" s="1">
         <v>300100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N22" s="1">
         <v>1022502</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="6:16">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16">
       <c r="F23" s="1">
         <v>300200</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N23" s="1">
         <v>1980000</v>
       </c>
       <c r="O23" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="6:8">
+    </row>
+    <row r="24" spans="2:16">
       <c r="F24" s="1">
         <v>200100</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="6:8">
+    </row>
+    <row r="25" spans="2:16">
       <c r="F25" s="1">
         <v>200101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="6:8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16">
       <c r="F26" s="1">
         <v>200300</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="6:8">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16">
       <c r="F27" s="1">
         <v>200400</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" spans="6:8">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16">
       <c r="F28" s="1">
         <v>200500</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="6:8">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16">
       <c r="F29" s="1">
         <v>200600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="6:8">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16">
       <c r="F30" s="1">
         <v>200700</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="6:8">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16">
       <c r="F31" s="1">
         <v>200800</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="6:8">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16">
       <c r="F32" s="1">
         <v>200900</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -3604,10 +3624,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -704,397 +704,397 @@
     <t>10001_100300_1_500</t>
   </si>
   <si>
+    <t>70101</t>
+  </si>
+  <si>
+    <t>在[超级明星]電子遊戲中，累積旋轉500次</t>
+  </si>
+  <si>
+    <t>10001_100700_1_500</t>
+  </si>
+  <si>
+    <t>70102</t>
+  </si>
+  <si>
+    <t>在[麻将胡了]電子遊戲中，累積旋轉500次</t>
+  </si>
+  <si>
+    <t>10001_101200_1_500</t>
+  </si>
+  <si>
+    <t>70103</t>
+  </si>
+  <si>
+    <t>在[财神]電子遊戲中，累積旋轉500次</t>
+  </si>
+  <si>
+    <t>10001_101400_1_500</t>
+  </si>
+  <si>
+    <t>70104</t>
+  </si>
+  <si>
+    <t>在[埃及艳后]電子遊戲中，累積旋轉500次</t>
+  </si>
+  <si>
+    <t>10001_0_1_2500</t>
+  </si>
+  <si>
+    <t>在任意電子遊戲中，累積旋轉2500次</t>
+  </si>
+  <si>
+    <t>以下游戏可用来配置,【策划看】</t>
+  </si>
+  <si>
+    <t>参与N次X活动 专用，以下活动可用来配置,【策划看】</t>
+  </si>
+  <si>
+    <t>401、402 任务类型 专用，以下道具可用来配置,【策划看】</t>
+  </si>
+  <si>
+    <t>达成条件</t>
+  </si>
+  <si>
+    <t>游戏ID</t>
+  </si>
+  <si>
+    <t>游戏名称</t>
+  </si>
+  <si>
+    <t>活动ID</t>
+  </si>
+  <si>
+    <t>活动名称</t>
+  </si>
+  <si>
+    <t>道具ID</t>
+  </si>
+  <si>
+    <t>道具名称</t>
+  </si>
+  <si>
+    <t>进行N次单笔X以上的充值</t>
+  </si>
+  <si>
+    <t>任意渠道充值</t>
+  </si>
+  <si>
+    <t>普通游戏</t>
+  </si>
+  <si>
+    <t>金礦大亨-普通</t>
+  </si>
+  <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
+    <t>领取任意奖励</t>
+  </si>
+  <si>
+    <t>游戏中产出 (不是礼包获得)</t>
+  </si>
+  <si>
+    <t>累积充值达到X以上</t>
+  </si>
+  <si>
+    <t>超级明星-普通</t>
+  </si>
+  <si>
+    <t>摇钱树</t>
+  </si>
+  <si>
+    <t>祈福任意摇钱树</t>
+  </si>
+  <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
+    <t>在N游戏中，金币有效下注累积达到X</t>
+  </si>
+  <si>
+    <t>指定游戏</t>
+  </si>
+  <si>
+    <t>麻将胡了-普通</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>领取任意罐子</t>
+  </si>
+  <si>
+    <t>赌场材料随机包(普通)</t>
+  </si>
+  <si>
+    <t>在任意游戏中，金币有效下注累积达到X</t>
+  </si>
+  <si>
+    <t>所有游戏</t>
+  </si>
+  <si>
+    <t>财神-普通</t>
+  </si>
+  <si>
+    <t>消耗任意道具数量</t>
+  </si>
+  <si>
+    <t>赌场材料随机包(豪华)</t>
+  </si>
+  <si>
+    <t>在N游戏中，金币累积赢奖达到X</t>
+  </si>
+  <si>
+    <t>埃及艳后-普通</t>
+  </si>
+  <si>
+    <t>推广分享</t>
+  </si>
+  <si>
+    <t>领取任意收益奖励</t>
+  </si>
+  <si>
+    <t>赌场材料随机包(尊贵)</t>
+  </si>
+  <si>
+    <t>在任意游戏中，金币累积赢奖达到X</t>
+  </si>
+  <si>
+    <t>紅黑大戰-普通</t>
+  </si>
+  <si>
+    <t>每日充值(未研发)</t>
+  </si>
+  <si>
+    <t>领取任意充值奖励</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(一星)</t>
+  </si>
+  <si>
+    <t>在N私人房间中钻石有效下注累积达到X</t>
+  </si>
+  <si>
+    <t>指定房间游戏</t>
+  </si>
+  <si>
+    <t>龍虎鬥-普通</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(二星)</t>
+  </si>
+  <si>
+    <t>在任意私人房间中钻石有效下注累积达到X</t>
+  </si>
+  <si>
+    <t>所有房间游戏</t>
+  </si>
+  <si>
+    <t>飛禽走獸-普通</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(三星)</t>
+  </si>
+  <si>
+    <t>在N私人房间中钻石累积赢奖达到X</t>
+  </si>
+  <si>
+    <t>豪車俱樂部-普通</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(四星)</t>
+  </si>
+  <si>
+    <t>在任意私人房间中钻石累积赢奖达到X</t>
+  </si>
+  <si>
+    <t>百家樂-普通</t>
+  </si>
+  <si>
+    <t>拼图随机礼包(五星)</t>
+  </si>
+  <si>
+    <t>在N游戏中，累积获得X个i</t>
+  </si>
+  <si>
+    <t>骰子-普通</t>
+  </si>
+  <si>
+    <t>在任意游戏中,累积获得X个i</t>
+  </si>
+  <si>
+    <t>越南色碟-普通</t>
+  </si>
+  <si>
+    <t>累积消耗X个i</t>
+  </si>
+  <si>
+    <t>查看501专用</t>
+  </si>
+  <si>
+    <t>大小骰子-普通</t>
+  </si>
+  <si>
+    <t>501 任务类型专用，以下道具可用来配置,【策划看】</t>
+  </si>
+  <si>
+    <t>参与N次X活动</t>
+  </si>
+  <si>
+    <t>查看502专用</t>
+  </si>
+  <si>
+    <t>魚蝦蟹-普通</t>
+  </si>
+  <si>
+    <t>在N电子游戏中，累积旋转X次</t>
+  </si>
+  <si>
+    <t>指定SLOT游戏</t>
+  </si>
+  <si>
+    <t>水果機-普通</t>
+  </si>
+  <si>
+    <t>摇钱树中使用即可</t>
+  </si>
+  <si>
+    <t>在任意电子游戏中，累积旋转X次</t>
+  </si>
+  <si>
+    <t>所有SLOT游戏</t>
+  </si>
+  <si>
+    <t>21點-普通</t>
+  </si>
+  <si>
+    <t>刮刮卡中使用即可</t>
+  </si>
+  <si>
+    <t>德州-普通</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>购买\兑换\赌场升级\房间消耗</t>
+  </si>
+  <si>
+    <t>私人游戏</t>
+  </si>
+  <si>
+    <t>紅黑大戰-房间</t>
+  </si>
+  <si>
+    <t>龍虎鬥-房间</t>
+  </si>
+  <si>
+    <t>飛禽走獸-房间</t>
+  </si>
+  <si>
+    <t>豪車俱樂部-房间</t>
+  </si>
+  <si>
+    <t>百家樂-房间</t>
+  </si>
+  <si>
+    <t>骰子-房间</t>
+  </si>
+  <si>
+    <t>越南色碟-房间</t>
+  </si>
+  <si>
+    <t>大小骰子-房间</t>
+  </si>
+  <si>
+    <t>魚蝦蟹-房间</t>
+  </si>
+  <si>
+    <t>德州-房间</t>
+  </si>
+  <si>
+    <t>充值商城</t>
+  </si>
+  <si>
+    <t>在私人房間中鑽石累積贏獎達到1,000</t>
+  </si>
+  <si>
+    <t>金矿大亨</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>在私人房間中鑽石累積贏獎達到7,000</t>
+  </si>
+  <si>
+    <t>在私人房間中鑽石累積贏獎達到70,000</t>
+  </si>
+  <si>
+    <t>在私人房間中鑽石累積贏獎達到700,000</t>
+  </si>
+  <si>
+    <t>创建房间</t>
+  </si>
+  <si>
+    <t>10003_0_1_1000_1980000</t>
+  </si>
+  <si>
+    <t>task_win diamonds</t>
+  </si>
+  <si>
+    <t>赢奖钻石</t>
+  </si>
+  <si>
+    <t>10003_0_1_7000_1980000</t>
+  </si>
+  <si>
+    <t>70381</t>
+  </si>
+  <si>
+    <t>10003_0_1_70000_1980000</t>
+  </si>
+  <si>
+    <t>70382</t>
+  </si>
+  <si>
+    <t>10003_0_1_700000_1980000</t>
+  </si>
+  <si>
+    <t>70383</t>
+  </si>
+  <si>
+    <t>2025/10/01 00:00:00</t>
+  </si>
+  <si>
+    <t>11001_9_2_0</t>
+  </si>
+  <si>
+    <t>2026/10/01 00:00:00</t>
+  </si>
+  <si>
+    <t>累積充值達到$100.00</t>
+  </si>
+  <si>
+    <t>12001_0_4000000</t>
+  </si>
+  <si>
+    <t>10003_0_1_2000000_1990000</t>
+  </si>
+  <si>
+    <t>在任意遊戲中，金币累積贏獎達到2,000,000</t>
+  </si>
+  <si>
     <t>task_rotation times</t>
-  </si>
-  <si>
-    <t>70101</t>
-  </si>
-  <si>
-    <t>在[超级明星]電子遊戲中，累積旋轉500次</t>
-  </si>
-  <si>
-    <t>10001_100700_1_500</t>
-  </si>
-  <si>
-    <t>70102</t>
-  </si>
-  <si>
-    <t>在[麻将胡了]電子遊戲中，累積旋轉500次</t>
-  </si>
-  <si>
-    <t>10001_101200_1_500</t>
-  </si>
-  <si>
-    <t>70103</t>
-  </si>
-  <si>
-    <t>在[财神]電子遊戲中，累積旋轉500次</t>
-  </si>
-  <si>
-    <t>10001_101400_1_500</t>
-  </si>
-  <si>
-    <t>70104</t>
-  </si>
-  <si>
-    <t>在[埃及艳后]電子遊戲中，累積旋轉500次</t>
-  </si>
-  <si>
-    <t>10001_0_1_2500</t>
-  </si>
-  <si>
-    <t>在任意電子遊戲中，累積旋轉2500次</t>
-  </si>
-  <si>
-    <t>以下游戏可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>参与N次X活动 专用，以下活动可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>401、402 任务类型 专用，以下道具可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>达成条件</t>
-  </si>
-  <si>
-    <t>游戏ID</t>
-  </si>
-  <si>
-    <t>游戏名称</t>
-  </si>
-  <si>
-    <t>活动ID</t>
-  </si>
-  <si>
-    <t>活动名称</t>
-  </si>
-  <si>
-    <t>道具ID</t>
-  </si>
-  <si>
-    <t>道具名称</t>
-  </si>
-  <si>
-    <t>进行N次单笔X以上的充值</t>
-  </si>
-  <si>
-    <t>任意渠道充值</t>
-  </si>
-  <si>
-    <t>普通游戏</t>
-  </si>
-  <si>
-    <t>金礦大亨-普通</t>
-  </si>
-  <si>
-    <t>每日奖金</t>
-  </si>
-  <si>
-    <t>领取任意奖励</t>
-  </si>
-  <si>
-    <t>游戏中产出 (不是礼包获得)</t>
-  </si>
-  <si>
-    <t>累积充值达到X以上</t>
-  </si>
-  <si>
-    <t>超级明星-普通</t>
-  </si>
-  <si>
-    <t>摇钱树</t>
-  </si>
-  <si>
-    <t>祈福任意摇钱树</t>
-  </si>
-  <si>
-    <t>刮刮卡</t>
-  </si>
-  <si>
-    <t>在N游戏中，金币有效下注累积达到X</t>
-  </si>
-  <si>
-    <t>指定游戏</t>
-  </si>
-  <si>
-    <t>麻将胡了-普通</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>领取任意罐子</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(普通)</t>
-  </si>
-  <si>
-    <t>在任意游戏中，金币有效下注累积达到X</t>
-  </si>
-  <si>
-    <t>所有游戏</t>
-  </si>
-  <si>
-    <t>财神-普通</t>
-  </si>
-  <si>
-    <t>消耗任意道具数量</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(豪华)</t>
-  </si>
-  <si>
-    <t>在N游戏中，金币累积赢奖达到X</t>
-  </si>
-  <si>
-    <t>埃及艳后-普通</t>
-  </si>
-  <si>
-    <t>推广分享</t>
-  </si>
-  <si>
-    <t>领取任意收益奖励</t>
-  </si>
-  <si>
-    <t>赌场材料随机包(尊贵)</t>
-  </si>
-  <si>
-    <t>在任意游戏中，金币累积赢奖达到X</t>
-  </si>
-  <si>
-    <t>紅黑大戰-普通</t>
-  </si>
-  <si>
-    <t>每日充值(未研发)</t>
-  </si>
-  <si>
-    <t>领取任意充值奖励</t>
-  </si>
-  <si>
-    <t>拼图随机礼包(一星)</t>
-  </si>
-  <si>
-    <t>在N私人房间中钻石有效下注累积达到X</t>
-  </si>
-  <si>
-    <t>指定房间游戏</t>
-  </si>
-  <si>
-    <t>龍虎鬥-普通</t>
-  </si>
-  <si>
-    <t>拼图随机礼包(二星)</t>
-  </si>
-  <si>
-    <t>在任意私人房间中钻石有效下注累积达到X</t>
-  </si>
-  <si>
-    <t>所有房间游戏</t>
-  </si>
-  <si>
-    <t>飛禽走獸-普通</t>
-  </si>
-  <si>
-    <t>拼图随机礼包(三星)</t>
-  </si>
-  <si>
-    <t>在N私人房间中钻石累积赢奖达到X</t>
-  </si>
-  <si>
-    <t>豪車俱樂部-普通</t>
-  </si>
-  <si>
-    <t>拼图随机礼包(四星)</t>
-  </si>
-  <si>
-    <t>在任意私人房间中钻石累积赢奖达到X</t>
-  </si>
-  <si>
-    <t>百家樂-普通</t>
-  </si>
-  <si>
-    <t>拼图随机礼包(五星)</t>
-  </si>
-  <si>
-    <t>在N游戏中，累积获得X个i</t>
-  </si>
-  <si>
-    <t>骰子-普通</t>
-  </si>
-  <si>
-    <t>在任意游戏中,累积获得X个i</t>
-  </si>
-  <si>
-    <t>越南色碟-普通</t>
-  </si>
-  <si>
-    <t>累积消耗X个i</t>
-  </si>
-  <si>
-    <t>查看501专用</t>
-  </si>
-  <si>
-    <t>大小骰子-普通</t>
-  </si>
-  <si>
-    <t>501 任务类型专用，以下道具可用来配置,【策划看】</t>
-  </si>
-  <si>
-    <t>参与N次X活动</t>
-  </si>
-  <si>
-    <t>查看502专用</t>
-  </si>
-  <si>
-    <t>魚蝦蟹-普通</t>
-  </si>
-  <si>
-    <t>在N电子游戏中，累积旋转X次</t>
-  </si>
-  <si>
-    <t>指定SLOT游戏</t>
-  </si>
-  <si>
-    <t>水果機-普通</t>
-  </si>
-  <si>
-    <t>摇钱树中使用即可</t>
-  </si>
-  <si>
-    <t>在任意电子游戏中，累积旋转X次</t>
-  </si>
-  <si>
-    <t>所有SLOT游戏</t>
-  </si>
-  <si>
-    <t>21點-普通</t>
-  </si>
-  <si>
-    <t>刮刮卡中使用即可</t>
-  </si>
-  <si>
-    <t>德州-普通</t>
-  </si>
-  <si>
-    <t>钻石</t>
-  </si>
-  <si>
-    <t>购买\兑换\赌场升级\房间消耗</t>
-  </si>
-  <si>
-    <t>私人游戏</t>
-  </si>
-  <si>
-    <t>紅黑大戰-房间</t>
-  </si>
-  <si>
-    <t>龍虎鬥-房间</t>
-  </si>
-  <si>
-    <t>飛禽走獸-房间</t>
-  </si>
-  <si>
-    <t>豪車俱樂部-房间</t>
-  </si>
-  <si>
-    <t>百家樂-房间</t>
-  </si>
-  <si>
-    <t>骰子-房间</t>
-  </si>
-  <si>
-    <t>越南色碟-房间</t>
-  </si>
-  <si>
-    <t>大小骰子-房间</t>
-  </si>
-  <si>
-    <t>魚蝦蟹-房间</t>
-  </si>
-  <si>
-    <t>德州-房间</t>
-  </si>
-  <si>
-    <t>充值商城</t>
-  </si>
-  <si>
-    <t>在私人房間中鑽石累積贏獎達到1,000</t>
-  </si>
-  <si>
-    <t>金矿大亨</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>财神</t>
-  </si>
-  <si>
-    <t>埃及艳后</t>
-  </si>
-  <si>
-    <t>在私人房間中鑽石累積贏獎達到7,000</t>
-  </si>
-  <si>
-    <t>在私人房間中鑽石累積贏獎達到70,000</t>
-  </si>
-  <si>
-    <t>在私人房間中鑽石累積贏獎達到700,000</t>
-  </si>
-  <si>
-    <t>创建房间</t>
-  </si>
-  <si>
-    <t>10003_0_1_1000_1980000</t>
-  </si>
-  <si>
-    <t>task_win diamonds</t>
-  </si>
-  <si>
-    <t>赢奖钻石</t>
-  </si>
-  <si>
-    <t>10003_0_1_7000_1980000</t>
-  </si>
-  <si>
-    <t>70381</t>
-  </si>
-  <si>
-    <t>10003_0_1_70000_1980000</t>
-  </si>
-  <si>
-    <t>70382</t>
-  </si>
-  <si>
-    <t>10003_0_1_700000_1980000</t>
-  </si>
-  <si>
-    <t>70383</t>
-  </si>
-  <si>
-    <t>2025/10/01 00:00:00</t>
-  </si>
-  <si>
-    <t>11001_9_2_0</t>
-  </si>
-  <si>
-    <t>2026/10/01 00:00:00</t>
-  </si>
-  <si>
-    <t>累積充值達到$100.00</t>
-  </si>
-  <si>
-    <t>12001_0_4000000</t>
-  </si>
-  <si>
-    <t>10003_0_1_2000000_1990000</t>
-  </si>
-  <si>
-    <t>在任意遊戲中，金币累積贏獎達到2,000,000</t>
   </si>
   <si>
     <t>10001_0_1_500</t>
@@ -2634,7 +2634,7 @@
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="2">
-        <f t="shared" ref="V5:V12" si="2">ROUND(MAX(S5/100,T5/100,U5),0)</f>
+        <f t="shared" ref="V5:V41" si="2">ROUND(MAX(S5/100,T5/100,U5),0)</f>
         <v>20</v>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
         <v>1000000</v>
       </c>
       <c r="R12" s="2">
-        <f t="shared" ref="R12:R15" si="6">O12</f>
+        <f t="shared" ref="R12:R32" si="6">O12</f>
         <v>1000000</v>
       </c>
       <c r="S12" s="12"/>
@@ -3122,7 +3122,7 @@
         <v>5</v>
       </c>
       <c r="V13" s="2">
-        <f>ROUND(MAX(S13/100,T13/100,U13),0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
         <v>50</v>
       </c>
       <c r="V14" s="2">
-        <f>ROUND(MAX(S14/100,T14/100,U14),0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
         <v>0.285714285714286</v>
       </c>
       <c r="V15" s="2">
-        <f>ROUND(MAX(S15/100,T15/100,U15),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
         <v>1000000</v>
       </c>
       <c r="R16" s="2">
-        <f>O16</f>
+        <f t="shared" si="6"/>
         <v>1000000</v>
       </c>
       <c r="S16" s="12"/>
@@ -3297,7 +3297,7 @@
         <v>0.142857142857143</v>
       </c>
       <c r="V16" s="2">
-        <f>ROUND(MAX(S16/100,T16/100,U16),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
         <v>35000000</v>
       </c>
       <c r="R17" s="2">
-        <f>O17</f>
+        <f t="shared" si="6"/>
         <v>35000000</v>
       </c>
       <c r="S17" s="12"/>
@@ -3356,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="V17" s="2">
-        <f>ROUND(MAX(S17/100,T17/100,U17),0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
         <v>350000000</v>
       </c>
       <c r="R18" s="2">
-        <f>O18</f>
+        <f t="shared" si="6"/>
         <v>350000000</v>
       </c>
       <c r="S18" s="12"/>
@@ -3415,7 +3415,7 @@
         <v>50</v>
       </c>
       <c r="V18" s="2">
-        <f>ROUND(MAX(S18/100,T18/100,U18),0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>1400000000</v>
       </c>
       <c r="R19" s="2">
-        <f>O19</f>
+        <f t="shared" si="6"/>
         <v>1400000000</v>
       </c>
       <c r="S19" s="12"/>
@@ -3474,7 +3474,7 @@
         <v>200</v>
       </c>
       <c r="V19" s="2">
-        <f>ROUND(MAX(S19/100,T19/100,U19),0)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
         <v>35000000</v>
       </c>
       <c r="R20" s="2">
-        <f>O20</f>
+        <f t="shared" si="6"/>
         <v>35000000</v>
       </c>
       <c r="S20" s="12"/>
@@ -3533,7 +3533,7 @@
         <v>5</v>
       </c>
       <c r="V20" s="2">
-        <f>ROUND(MAX(S20/100,T20/100,U20),0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
         <v>350000000</v>
       </c>
       <c r="R21" s="2">
-        <f>O21</f>
+        <f t="shared" si="6"/>
         <v>350000000</v>
       </c>
       <c r="S21" s="12"/>
@@ -3592,7 +3592,7 @@
         <v>50</v>
       </c>
       <c r="V21" s="2">
-        <f>ROUND(MAX(S21/100,T21/100,U21),0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
         <v>1400000000</v>
       </c>
       <c r="R22" s="2">
-        <f>O22</f>
+        <f t="shared" si="6"/>
         <v>1400000000</v>
       </c>
       <c r="S22" s="12"/>
@@ -3651,7 +3651,7 @@
         <v>200</v>
       </c>
       <c r="V22" s="2">
-        <f>ROUND(MAX(S22/100,T22/100,U22),0)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>35000000</v>
       </c>
       <c r="R23" s="2">
-        <f>O23</f>
+        <f t="shared" si="6"/>
         <v>35000000</v>
       </c>
       <c r="S23" s="12"/>
@@ -3710,7 +3710,7 @@
         <v>5</v>
       </c>
       <c r="V23" s="2">
-        <f>ROUND(MAX(S23/100,T23/100,U23),0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
         <v>350000000</v>
       </c>
       <c r="R24" s="2">
-        <f>O24</f>
+        <f t="shared" si="6"/>
         <v>350000000</v>
       </c>
       <c r="S24" s="12"/>
@@ -3769,7 +3769,7 @@
         <v>50</v>
       </c>
       <c r="V24" s="2">
-        <f>ROUND(MAX(S24/100,T24/100,U24),0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
         <v>1400000000</v>
       </c>
       <c r="R25" s="2">
-        <f>O25</f>
+        <f t="shared" si="6"/>
         <v>1400000000</v>
       </c>
       <c r="S25" s="12"/>
@@ -3828,7 +3828,7 @@
         <v>200</v>
       </c>
       <c r="V25" s="2">
-        <f>ROUND(MAX(S25/100,T25/100,U25),0)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
         <v>35000000</v>
       </c>
       <c r="R26" s="2">
-        <f>O26</f>
+        <f t="shared" si="6"/>
         <v>35000000</v>
       </c>
       <c r="S26" s="12"/>
@@ -3887,7 +3887,7 @@
         <v>5</v>
       </c>
       <c r="V26" s="2">
-        <f>ROUND(MAX(S26/100,T26/100,U26),0)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
         <v>350000000</v>
       </c>
       <c r="R27" s="2">
-        <f>O27</f>
+        <f t="shared" si="6"/>
         <v>350000000</v>
       </c>
       <c r="S27" s="12"/>
@@ -3946,7 +3946,7 @@
         <v>50</v>
       </c>
       <c r="V27" s="2">
-        <f>ROUND(MAX(S27/100,T27/100,U27),0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
         <v>1400000000</v>
       </c>
       <c r="R28" s="2">
-        <f>O28</f>
+        <f t="shared" si="6"/>
         <v>1400000000</v>
       </c>
       <c r="S28" s="12"/>
@@ -4005,7 +4005,7 @@
         <v>200</v>
       </c>
       <c r="V28" s="2">
-        <f>ROUND(MAX(S28/100,T28/100,U28),0)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         <v>2000000</v>
       </c>
       <c r="R29" s="2">
-        <f>O29</f>
+        <f t="shared" si="6"/>
         <v>2000000</v>
       </c>
       <c r="S29" s="12"/>
@@ -4063,7 +4063,7 @@
         <v>0.285714285714286</v>
       </c>
       <c r="V29" s="2">
-        <f>ROUND(MAX(S29/100,T29/100,U29),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
         <v>210000000</v>
       </c>
       <c r="R30" s="2">
-        <f>O30</f>
+        <f t="shared" si="6"/>
         <v>210000000</v>
       </c>
       <c r="S30" s="12"/>
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="V30" s="2">
-        <f>ROUND(MAX(S30/100,T30/100,U30),0)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>2100000000</v>
       </c>
       <c r="R31" s="2">
-        <f>O31</f>
+        <f t="shared" si="6"/>
         <v>2100000000</v>
       </c>
       <c r="S31" s="12"/>
@@ -4181,7 +4181,7 @@
         <v>300</v>
       </c>
       <c r="V31" s="2">
-        <f>ROUND(MAX(S31/100,T31/100,U31),0)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
         <v>4200000000</v>
       </c>
       <c r="R32" s="2">
-        <f>O32</f>
+        <f t="shared" si="6"/>
         <v>4200000000</v>
       </c>
       <c r="S32" s="12"/>
@@ -4240,7 +4240,7 @@
         <v>600</v>
       </c>
       <c r="V32" s="2">
-        <f>ROUND(MAX(S32/100,T32/100,U32),0)</f>
+        <f t="shared" si="2"/>
         <v>600</v>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="2">
-        <f>ROUND(MAX(S33/100,T33/100,U33),0)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="2">
-        <f>ROUND(MAX(S34/100,T34/100,U34),0)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="2">
-        <f>ROUND(MAX(S35/100,T35/100,U35),0)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="V36" s="2">
-        <f>ROUND(MAX(S36/100,T36/100,U36),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4525,14 +4525,14 @@
         <v>11003</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="N37" s="15" t="s">
         <v>135</v>
@@ -4551,7 +4551,7 @@
         <v>3.57142857142857</v>
       </c>
       <c r="V37" s="2">
-        <f>ROUND(MAX(S37/100,T37/100,U37),0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="11">
@@ -4588,10 +4588,10 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="N38" s="15" t="s">
         <v>135</v>
@@ -4610,7 +4610,7 @@
         <v>3.57142857142857</v>
       </c>
       <c r="V38" s="2">
-        <f>ROUND(MAX(S38/100,T38/100,U38),0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="11">
@@ -4647,10 +4647,10 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="N39" s="15" t="s">
         <v>135</v>
@@ -4669,7 +4669,7 @@
         <v>3.57142857142857</v>
       </c>
       <c r="V39" s="2">
-        <f>ROUND(MAX(S39/100,T39/100,U39),0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="11">
@@ -4706,10 +4706,10 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="N40" s="15" t="s">
         <v>135</v>
@@ -4728,7 +4728,7 @@
         <v>3.57142857142857</v>
       </c>
       <c r="V40" s="2">
-        <f>ROUND(MAX(S40/100,T40/100,U40),0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="11">
@@ -4767,7 +4767,7 @@
         <v>70010</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>135</v>
@@ -4786,7 +4786,7 @@
         <v>17.8571428571429</v>
       </c>
       <c r="V41" s="2">
-        <f>ROUND(MAX(S41/100,T41/100,U41),0)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
@@ -4833,16 +4833,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J5" s="17">
         <v>502</v>
       </c>
       <c r="K5" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="N5" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="N5" s="18" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -4853,32 +4853,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>154</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>155</v>
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="K6" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="L6" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N6" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="L6" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="N6" s="22" t="s">
+      <c r="O6" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="O6" s="22" t="s">
-        <v>160</v>
-      </c>
       <c r="P6" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -4886,28 +4886,28 @@
         <v>101</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>161</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>162</v>
       </c>
       <c r="F7" s="16">
         <v>100100</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>163</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="J7" s="16">
         <v>2</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>165</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>166</v>
       </c>
       <c r="N7" s="16">
         <v>1022501</v>
@@ -4916,7 +4916,7 @@
         <v>125</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -4924,37 +4924,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F8" s="16">
         <v>100300</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J8" s="16">
         <v>3</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>170</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>171</v>
       </c>
       <c r="N8" s="16">
         <v>1022502</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -4962,37 +4962,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>173</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>174</v>
       </c>
       <c r="F9" s="16">
         <v>100700</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J9" s="16">
         <v>4</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>177</v>
       </c>
       <c r="N9" s="16">
         <v>1010301</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -5000,37 +5000,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="F10" s="16">
         <v>101200</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J10" s="16">
         <v>5</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N10" s="16">
         <v>1010302</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -5038,37 +5038,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F11" s="16">
         <v>101400</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J11" s="16">
         <v>6</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="N11" s="16">
         <v>1010303</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -5076,37 +5076,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" s="16">
         <v>200100</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J12" s="23">
         <v>12</v>
       </c>
       <c r="K12" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="L12" s="23" t="s">
         <v>191</v>
-      </c>
-      <c r="L12" s="23" t="s">
-        <v>192</v>
       </c>
       <c r="N12" s="16">
         <v>1010311</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -5114,19 +5114,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>194</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>195</v>
       </c>
       <c r="F13" s="16">
         <v>200101</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="24"/>
@@ -5135,10 +5135,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -5146,19 +5146,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>198</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>199</v>
       </c>
       <c r="F14" s="16">
         <v>200300</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
@@ -5167,10 +5167,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -5178,28 +5178,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F15" s="16">
         <v>200400</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N15" s="16">
         <v>1010314</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -5207,28 +5207,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F16" s="16">
         <v>200500</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N16" s="16">
         <v>1010315</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -5236,19 +5236,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F17" s="16">
         <v>200600</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -5256,19 +5256,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F18" s="16">
         <v>200700</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -5276,22 +5276,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>212</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>213</v>
       </c>
       <c r="F19" s="16">
         <v>200800</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H19" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="N19" s="25" t="s">
         <v>214</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -5299,28 +5299,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>216</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>217</v>
       </c>
       <c r="F20" s="16">
         <v>200900</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N20" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="O20" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="O20" s="22" t="s">
-        <v>160</v>
-      </c>
       <c r="P20" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -5328,19 +5328,19 @@
         <v>601</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>219</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>220</v>
       </c>
       <c r="F21" s="16">
         <v>201000</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N21" s="16">
         <v>1022501</v>
@@ -5349,7 +5349,7 @@
         <v>125</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -5357,28 +5357,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>223</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>224</v>
       </c>
       <c r="F22" s="16">
         <v>300100</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N22" s="16">
         <v>1022502</v>
       </c>
       <c r="O22" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -5386,19 +5386,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N23" s="16">
         <v>1980000</v>
       </c>
       <c r="O23" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="P23" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="P23" s="16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -5406,10 +5406,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -5417,10 +5417,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -5428,10 +5428,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -5439,10 +5439,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -5450,10 +5450,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -5461,10 +5461,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -5472,10 +5472,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -5483,10 +5483,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -5494,10 +5494,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="6:8">
@@ -5505,10 +5505,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -5574,7 +5574,7 @@
         <v>69</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L5" s="8">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5589,7 +5589,7 @@
         <v>111</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L6" s="8">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5601,10 +5601,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L7" s="8">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5619,7 +5619,7 @@
         <v>123</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L8" s="8">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5634,7 +5634,7 @@
         <v>134</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L9" s="8">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5646,10 +5646,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L10" s="8">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5661,10 +5661,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L11" s="8">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5676,10 +5676,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L12" s="8">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5691,10 +5691,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L13" s="8">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5706,10 +5706,10 @@
         <v>70104</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L14" s="8">
         <f>_xlfn.XLOOKUP(K14,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5724,7 +5724,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L15" s="8">
         <f>_xlfn.XLOOKUP(K15,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5739,7 +5739,7 @@
         <v>77</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L16" s="8">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5754,7 +5754,7 @@
         <v>80</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L17" s="8">
         <f>_xlfn.XLOOKUP(K17,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5769,7 +5769,7 @@
         <v>83</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L18" s="8">
         <f>_xlfn.XLOOKUP(K18,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5784,7 +5784,7 @@
         <v>86</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L19" s="8">
         <f>_xlfn.XLOOKUP(K19,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5799,7 +5799,7 @@
         <v>89</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L20" s="8">
         <f>_xlfn.XLOOKUP(K20,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5814,7 +5814,7 @@
         <v>93</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L21" s="8">
         <f>_xlfn.XLOOKUP(K21,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5829,7 +5829,7 @@
         <v>96</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L22" s="8">
         <f>_xlfn.XLOOKUP(K22,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5844,7 +5844,7 @@
         <v>99</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L23" s="8">
         <f>_xlfn.XLOOKUP(K23,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5859,7 +5859,7 @@
         <v>103</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L24" s="8">
         <f>_xlfn.XLOOKUP(K24,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5874,7 +5874,7 @@
         <v>106</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L25" s="8">
         <f>_xlfn.XLOOKUP(K25,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5889,7 +5889,7 @@
         <v>109</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L26" s="8">
         <f>_xlfn.XLOOKUP(K26,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5901,10 +5901,10 @@
         <v>70381</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L27" s="8">
         <f>_xlfn.XLOOKUP(K27,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5916,10 +5916,10 @@
         <v>70382</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L28" s="8">
         <f>_xlfn.XLOOKUP(K28,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5931,10 +5931,10 @@
         <v>70383</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L29" s="8">
         <f>_xlfn.XLOOKUP(K29,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5949,7 +5949,7 @@
         <v>114</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L30" s="8">
         <f>_xlfn.XLOOKUP(K30,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5964,7 +5964,7 @@
         <v>117</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L31" s="8">
         <f>_xlfn.XLOOKUP(K31,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5979,7 +5979,7 @@
         <v>120</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L32" s="8">
         <f>_xlfn.XLOOKUP(K32,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -5994,7 +5994,7 @@
         <v>39</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L33" s="8">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6009,7 +6009,7 @@
         <v>42</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L34" s="8">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6024,7 +6024,7 @@
         <v>45</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L35" s="8">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6039,7 +6039,7 @@
         <v>50</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L36" s="8">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6054,7 +6054,7 @@
         <v>53</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L37" s="8">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6069,7 +6069,7 @@
         <v>60</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L38" s="8">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6084,7 +6084,7 @@
         <v>64</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L39" s="8">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6099,7 +6099,7 @@
         <v>128</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L40" s="8">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6114,7 +6114,7 @@
         <v>131</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L41" s="8">
         <f>_xlfn.XLOOKUP(K41,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6123,7 +6123,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="K42" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L42" s="8">
         <f>_xlfn.XLOOKUP(K42,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6132,7 +6132,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="K43" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L43" s="8">
         <f>_xlfn.XLOOKUP(K43,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="K44" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L44" s="8">
         <f>_xlfn.XLOOKUP(K44,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6150,7 +6150,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="K45" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L45" s="8">
         <f>_xlfn.XLOOKUP(K45,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -6242,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="11">
@@ -6255,17 +6255,17 @@
         <v>2001</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="6">
         <v>70007</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O59" s="1">
         <v>1000</v>
@@ -6301,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F60" s="10"/>
       <c r="G60" s="11">
@@ -6314,17 +6314,17 @@
         <v>2001</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O60" s="1">
         <v>7000</v>
@@ -6362,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F61" s="10"/>
       <c r="G61" s="11">
@@ -6375,17 +6375,17 @@
         <v>2001</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O61" s="1">
         <v>70000</v>
@@ -6423,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F62" s="10"/>
       <c r="G62" s="11">
@@ -6436,17 +6436,17 @@
         <v>2001</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O62" s="1">
         <v>700000</v>
@@ -6483,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="13">
@@ -6496,16 +6496,16 @@
         <v>2002</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L63" s="14">
         <v>70007</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P63" s="2"/>
     </row>
@@ -6524,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="13">
@@ -6540,7 +6540,7 @@
         <v>33</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L65" s="14">
         <v>70001</v>
@@ -6584,13 +6584,13 @@
         <v>33</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L66" s="14">
         <v>70002</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" spans="1:22">
@@ -6624,7 +6624,7 @@
         <v>55</v>
       </c>
       <c r="K67" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L67" s="14">
         <v>70003</v>
@@ -6648,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="13">
@@ -6664,7 +6664,7 @@
         <v>66</v>
       </c>
       <c r="K68" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L68" s="14">
         <v>70004</v>
@@ -6704,7 +6704,7 @@
         <v>55</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L69" s="14">
         <v>70005</v>
@@ -6729,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F70" s="12"/>
       <c r="G70" s="13">
@@ -6745,13 +6745,13 @@
         <v>66</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L70" s="14">
         <v>70006</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N70" s="15"/>
     </row>
@@ -6786,7 +6786,7 @@
         <v>122</v>
       </c>
       <c r="K71" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L71" s="14">
         <v>70008</v>
@@ -6824,10 +6824,10 @@
         <v>1001</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>137</v>
+        <v>267</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L72" s="14">
         <v>70009</v>
@@ -6865,10 +6865,10 @@
         <v>2001</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>137</v>
+        <v>267</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L73" s="14">
         <v>70010</v>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -3185,7 +3185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB86"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -8146,7 +8146,6 @@
         <v>No jogo [any game], foram acumuladas 500 rodadas.</v>
       </c>
     </row>
-    <row r="86" ht="14.25"/>
   </sheetData>
   <conditionalFormatting sqref="L$1:L$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>28</v>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>28</v>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -101,7 +101,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置 condition.xlsx 文件中的ID</t>
+配置 condition.xlsx 文件中的ID
+充值类型的单位是分，比如要求充值9.99美元，需要填 999</t>
         </r>
       </text>
     </comment>
@@ -459,7 +460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="425">
   <si>
     <t>任务ID</t>
   </si>
@@ -470,7 +471,7 @@
     <t>任务组</t>
   </si>
   <si>
-    <t>任务条件</t>
+    <t>任务条件（充值货币单位是分，服务端会除以100）</t>
   </si>
   <si>
     <t>道具奖励</t>
@@ -503,6 +504,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
@@ -542,7 +546,7 @@
     <t>language</t>
   </si>
   <si>
-    <t>11002_300000_0</t>
+    <t>11002_30000000_0</t>
   </si>
   <si>
     <t>itemicon_1022504.png</t>
@@ -563,7 +567,7 @@
     <t>300000</t>
   </si>
   <si>
-    <t>11002_1400000_0</t>
+    <t>11002_140000000_0</t>
   </si>
   <si>
     <t>70002</t>
@@ -575,7 +579,7 @@
     <t>1400000</t>
   </si>
   <si>
-    <t>11002_8300000_0</t>
+    <t>11002_830000000_0</t>
   </si>
   <si>
     <t>70003</t>
@@ -587,7 +591,7 @@
     <t>8300000</t>
   </si>
   <si>
-    <t>11002_32000000_0</t>
+    <t>11002_3200000000_0</t>
   </si>
   <si>
     <t>70004</t>
@@ -599,7 +603,7 @@
     <t>32000000</t>
   </si>
   <si>
-    <t>11002_132000000_0</t>
+    <t>11002_13200000000_0</t>
   </si>
   <si>
     <t>70005</t>
@@ -611,7 +615,7 @@
     <t>132000000</t>
   </si>
   <si>
-    <t>11002_200000000_0</t>
+    <t>11002_20000000000_0</t>
   </si>
   <si>
     <t>70006</t>
@@ -1349,6 +1353,9 @@
   </si>
   <si>
     <t>德州-房间</t>
+  </si>
+  <si>
+    <t>任务条件</t>
   </si>
   <si>
     <t>价值转化</t>
@@ -1980,7 +1987,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2056,6 +2063,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2378,7 +2391,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2402,16 +2415,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2420,89 +2433,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2632,6 +2645,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2680,7 +2696,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -3269,22 +3285,22 @@
         <v>14</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>13</v>
@@ -3292,38 +3308,38 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="28"/>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -3353,32 +3369,32 @@
       <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>27</v>
+      <c r="E5" s="43" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13">
         <v>1</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="10">
         <v>2003</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="4" t="str">
         <f t="shared" ref="M5:M10" si="0">"累積充值達到 "&amp;S5&amp;" ₫"</f>
         <v>累積充值達到 300,000 ₫</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1">
         <v>11002</v>
@@ -3388,13 +3404,13 @@
       <c r="R5" s="1">
         <v>2003</v>
       </c>
-      <c r="S5" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="T5" s="43" t="s">
+      <c r="S5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="44">
+      <c r="T5" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="45">
         <f t="shared" ref="U5:U10" si="1">S5/29000*7*3%</f>
         <v>2.17241379310345</v>
       </c>
@@ -3430,32 +3446,32 @@
       <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>34</v>
+      <c r="E6" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13">
         <v>10</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="10">
         <v>2003</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 1,400,000 ₫</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="1">
         <v>11002</v>
@@ -3465,13 +3481,13 @@
       <c r="R6" s="1">
         <v>2003</v>
       </c>
-      <c r="S6" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="43" t="s">
+      <c r="S6" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="44">
+      <c r="T6" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="U6" s="45">
         <f t="shared" si="1"/>
         <v>10.1379310344828</v>
       </c>
@@ -3507,32 +3523,32 @@
       <c r="D7" s="12">
         <v>1</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>38</v>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
         <v>60</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10">
         <v>2003</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 8,300,000 ₫</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" s="1">
         <v>11002</v>
@@ -3542,13 +3558,13 @@
       <c r="R7" s="1">
         <v>2003</v>
       </c>
-      <c r="S7" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T7" s="43" t="s">
+      <c r="S7" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="44">
+      <c r="T7" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" s="45">
         <f t="shared" si="1"/>
         <v>60.1034482758621</v>
       </c>
@@ -3584,32 +3600,32 @@
       <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>42</v>
+      <c r="E8" s="43" t="s">
+        <v>43</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="13">
         <v>230</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="10">
         <v>2003</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 32,000,000 ₫</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O8" s="1">
         <v>11002</v>
@@ -3619,13 +3635,13 @@
       <c r="R8" s="1">
         <v>2003</v>
       </c>
-      <c r="S8" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="43" t="s">
+      <c r="S8" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="44">
+      <c r="T8" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="45">
         <f t="shared" si="1"/>
         <v>231.724137931035</v>
       </c>
@@ -3661,48 +3677,48 @@
       <c r="D9" s="36">
         <v>1</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>46</v>
+      <c r="E9" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="13">
         <v>950</v>
       </c>
-      <c r="H9" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="46">
+      <c r="H9" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="47">
         <v>2003</v>
       </c>
-      <c r="J9" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="47"/>
+      <c r="J9" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="48"/>
       <c r="L9" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" s="36" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 132,000,000 ₫</v>
       </c>
-      <c r="N9" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="48">
+      <c r="N9" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="49">
         <v>11002</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48">
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49">
         <v>2003</v>
       </c>
-      <c r="S9" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="49" t="s">
+      <c r="S9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="50">
+      <c r="T9" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="51">
         <f t="shared" si="1"/>
         <v>955.862068965517</v>
       </c>
@@ -3736,48 +3752,48 @@
       <c r="D10" s="37">
         <v>1</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>50</v>
+      <c r="E10" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="13">
         <v>1440</v>
       </c>
-      <c r="H10" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="52">
+      <c r="H10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="53">
         <v>2003</v>
       </c>
-      <c r="J10" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="53"/>
+      <c r="J10" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="54"/>
       <c r="L10" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M10" s="37" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 200,000,000 ₫</v>
       </c>
-      <c r="N10" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="54">
+      <c r="N10" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="55">
         <v>11002</v>
       </c>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54">
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55">
         <v>2003</v>
       </c>
-      <c r="S10" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="T10" s="55" t="s">
+      <c r="S10" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="U10" s="56">
+      <c r="T10" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="U10" s="57">
         <f t="shared" si="1"/>
         <v>1448.27586206897</v>
       </c>
@@ -3812,37 +3828,37 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="13">
         <v>20</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I11" s="10">
         <v>11007</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M11" s="4" t="str">
         <f t="shared" ref="M11:M14" si="5">"在["&amp;P11&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S11</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O11" s="4">
         <v>12001</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="1">
         <v>100700</v>
@@ -3850,13 +3866,13 @@
       <c r="R11" s="1">
         <v>11007</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T11" s="43" t="s">
+      <c r="S11" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U11" s="57">
+      <c r="T11" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11" s="58">
         <f t="shared" ref="U11:U35" si="6">S11*3%/29000*7</f>
         <v>24.6206896551724</v>
       </c>
@@ -3864,21 +3880,21 @@
         <v>1</v>
       </c>
       <c r="W11" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X11" s="4" t="str">
         <f>"In the ["&amp;W11&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S11</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y11" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z11" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y11&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S11</f>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA11" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB11" s="4" t="str">
         <f>"No videogame ["&amp;AA11&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S11</f>
@@ -3899,37 +3915,37 @@
         <v>2</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="13">
         <v>20</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="10">
         <v>11003</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M12" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O12" s="4">
         <v>12001</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q12" s="1">
         <v>100300</v>
@@ -3937,13 +3953,13 @@
       <c r="R12" s="1">
         <v>11003</v>
       </c>
-      <c r="S12" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T12" s="43" t="s">
+      <c r="S12" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U12" s="57">
+      <c r="T12" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -3951,21 +3967,21 @@
         <v>2</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X12" s="4" t="str">
         <f>"In the ["&amp;W12&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S12</f>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y12" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z12" s="4" t="str">
         <f t="shared" ref="Z12:Z35" si="7">"Trong trò chơi ["&amp;Y12&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S12</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB12" s="4" t="str">
         <f t="shared" ref="AB12:AB35" si="8">"No videogame ["&amp;AA12&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S12</f>
@@ -3986,37 +4002,37 @@
         <v>3</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13">
         <v>20</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="10">
         <v>11012</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M13" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O13" s="4">
         <v>12001</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q13" s="1">
         <v>101200</v>
@@ -4024,13 +4040,13 @@
       <c r="R13" s="1">
         <v>11012</v>
       </c>
-      <c r="S13" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T13" s="43" t="s">
+      <c r="S13" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U13" s="57">
+      <c r="T13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4038,21 +4054,21 @@
         <v>3</v>
       </c>
       <c r="W13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X13" s="4" t="str">
         <f>"In the ["&amp;W13&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S13</f>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y13" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB13" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4073,37 +4089,37 @@
         <v>4</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13">
         <v>20</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="10">
         <v>11014</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O14" s="4">
         <v>12001</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="1">
         <v>101400</v>
@@ -4111,13 +4127,13 @@
       <c r="R14" s="1">
         <v>11014</v>
       </c>
-      <c r="S14" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="43" t="s">
+      <c r="S14" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="57">
+      <c r="T14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U14" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4125,21 +4141,21 @@
         <v>4</v>
       </c>
       <c r="W14" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X14" s="4" t="str">
         <f>"In the ["&amp;W14&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S14</f>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y14" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z14" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB14" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4160,37 +4176,37 @@
         <v>5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13">
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="10">
         <v>11003</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S15</f>
         <v>在任意遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O15" s="4">
         <v>12001</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q15" s="1">
         <v>0</v>
@@ -4198,13 +4214,13 @@
       <c r="R15" s="1">
         <v>11003</v>
       </c>
-      <c r="S15" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T15" s="43" t="s">
+      <c r="S15" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U15" s="57">
+      <c r="T15" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U15" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4212,21 +4228,21 @@
         <v>5</v>
       </c>
       <c r="W15" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X15" s="4" t="str">
         <f>"In the ["&amp;W15&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S15</f>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y15" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4240,44 +4256,44 @@
       <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="59">
         <v>1200101</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13">
         <v>60</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="10">
         <v>11007</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" s="4" t="str">
         <f>"在["&amp;P16&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S16</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O16" s="4">
         <v>12001</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="1">
         <v>100700</v>
@@ -4285,13 +4301,13 @@
       <c r="R16" s="1">
         <v>11007</v>
       </c>
-      <c r="S16" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T16" s="43" t="s">
+      <c r="S16" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U16" s="57">
+      <c r="T16" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4299,21 +4315,21 @@
         <v>1</v>
       </c>
       <c r="W16" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X16" s="4" t="str">
         <f t="shared" ref="X16:X35" si="9">"In the ["&amp;W16&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S16</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y16" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z16" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA16" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB16" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4327,44 +4343,44 @@
       <c r="B17" s="12">
         <v>1</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="59">
         <v>1200101</v>
       </c>
       <c r="D17" s="12">
         <v>2</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13">
         <v>60</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I17" s="10">
         <v>11003</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M17" s="4" t="str">
         <f>"在["&amp;P17&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S17</f>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="4">
         <v>12001</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="1">
         <v>100300</v>
@@ -4372,13 +4388,13 @@
       <c r="R17" s="1">
         <v>11003</v>
       </c>
-      <c r="S17" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T17" s="43" t="s">
+      <c r="S17" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U17" s="57">
+      <c r="T17" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4386,21 +4402,21 @@
         <v>2</v>
       </c>
       <c r="W17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X17" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y17" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z17" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB17" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4414,44 +4430,44 @@
       <c r="B18" s="12">
         <v>1</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="59">
         <v>1200101</v>
       </c>
       <c r="D18" s="12">
         <v>3</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13">
         <v>60</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I18" s="10">
         <v>11012</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M18" s="4" t="str">
         <f>"在["&amp;P18&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S18</f>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O18" s="4">
         <v>12001</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="1">
         <v>101200</v>
@@ -4459,13 +4475,13 @@
       <c r="R18" s="1">
         <v>11012</v>
       </c>
-      <c r="S18" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T18" s="43" t="s">
+      <c r="S18" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U18" s="57">
+      <c r="T18" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4473,21 +4489,21 @@
         <v>3</v>
       </c>
       <c r="W18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X18" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y18" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z18" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB18" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4501,44 +4517,44 @@
       <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <v>1200101</v>
       </c>
       <c r="D19" s="12">
         <v>4</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13">
         <v>60</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="10">
         <v>11014</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M19" s="4" t="str">
         <f>"在["&amp;P19&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S19</f>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O19" s="4">
         <v>12001</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="1">
         <v>101400</v>
@@ -4546,13 +4562,13 @@
       <c r="R19" s="1">
         <v>11014</v>
       </c>
-      <c r="S19" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T19" s="43" t="s">
+      <c r="S19" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U19" s="57">
+      <c r="T19" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4560,21 +4576,21 @@
         <v>4</v>
       </c>
       <c r="W19" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X19" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y19" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z19" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB19" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4588,44 +4604,44 @@
       <c r="B20" s="12">
         <v>1</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="59">
         <v>1200101</v>
       </c>
       <c r="D20" s="12">
         <v>5</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13">
         <v>60</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="10">
         <v>11003</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M20" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S20</f>
         <v>在任意遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O20" s="4">
         <v>12001</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -4633,13 +4649,13 @@
       <c r="R20" s="1">
         <v>11003</v>
       </c>
-      <c r="S20" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T20" s="43" t="s">
+      <c r="S20" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U20" s="57">
+      <c r="T20" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U20" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4647,21 +4663,21 @@
         <v>5</v>
       </c>
       <c r="W20" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X20" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y20" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z20" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA20" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB20" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4675,44 +4691,44 @@
       <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="60">
         <v>1200102</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13">
         <v>130</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I21" s="10">
         <v>11007</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M21" s="4" t="str">
         <f t="shared" ref="M21:M29" si="10">"在["&amp;P21&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S21</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O21" s="4">
         <v>12001</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="1">
         <v>100700</v>
@@ -4720,13 +4736,13 @@
       <c r="R21" s="1">
         <v>11007</v>
       </c>
-      <c r="S21" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T21" s="43" t="s">
+      <c r="S21" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U21" s="57">
+      <c r="T21" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U21" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4734,21 +4750,21 @@
         <v>1</v>
       </c>
       <c r="W21" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X21" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y21" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z21" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA21" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB21" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4762,44 +4778,44 @@
       <c r="B22" s="12">
         <v>1</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="60">
         <v>1200102</v>
       </c>
       <c r="D22" s="12">
         <v>2</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13">
         <v>130</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I22" s="10">
         <v>11003</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M22" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O22" s="4">
         <v>12001</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q22" s="1">
         <v>100300</v>
@@ -4807,13 +4823,13 @@
       <c r="R22" s="1">
         <v>11003</v>
       </c>
-      <c r="S22" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T22" s="43" t="s">
+      <c r="S22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U22" s="57">
+      <c r="T22" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U22" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4821,21 +4837,21 @@
         <v>2</v>
       </c>
       <c r="W22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X22" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y22" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z22" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB22" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4849,44 +4865,44 @@
       <c r="B23" s="12">
         <v>1</v>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="60">
         <v>1200102</v>
       </c>
       <c r="D23" s="12">
         <v>3</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13">
         <v>130</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I23" s="10">
         <v>11012</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M23" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O23" s="4">
         <v>12001</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q23" s="1">
         <v>101200</v>
@@ -4894,13 +4910,13 @@
       <c r="R23" s="1">
         <v>11012</v>
       </c>
-      <c r="S23" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T23" s="43" t="s">
+      <c r="S23" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U23" s="57">
+      <c r="T23" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U23" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4908,21 +4924,21 @@
         <v>3</v>
       </c>
       <c r="W23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X23" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y23" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z23" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB23" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4936,44 +4952,44 @@
       <c r="B24" s="12">
         <v>1</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="60">
         <v>1200102</v>
       </c>
       <c r="D24" s="12">
         <v>4</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13">
         <v>130</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I24" s="10">
         <v>11014</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M24" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O24" s="4">
         <v>12001</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="1">
         <v>101400</v>
@@ -4981,13 +4997,13 @@
       <c r="R24" s="1">
         <v>11014</v>
       </c>
-      <c r="S24" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T24" s="43" t="s">
+      <c r="S24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U24" s="57">
+      <c r="T24" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U24" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4995,21 +5011,21 @@
         <v>4</v>
       </c>
       <c r="W24" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X24" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y24" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z24" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB24" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5023,44 +5039,44 @@
       <c r="B25" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25" s="60">
         <v>1200102</v>
       </c>
       <c r="D25" s="12">
         <v>5</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13">
         <v>130</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" s="10">
         <v>11003</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M25" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S25</f>
         <v>在任意遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O25" s="4">
         <v>12001</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
@@ -5068,13 +5084,13 @@
       <c r="R25" s="1">
         <v>11003</v>
       </c>
-      <c r="S25" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T25" s="43" t="s">
+      <c r="S25" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U25" s="57">
+      <c r="T25" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U25" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -5082,21 +5098,21 @@
         <v>5</v>
       </c>
       <c r="W25" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X25" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y25" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z25" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA25" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB25" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5117,51 +5133,51 @@
         <v>1</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F26" s="36"/>
       <c r="G26" s="13">
         <v>490</v>
       </c>
-      <c r="H26" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="46">
+      <c r="H26" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="47">
         <v>11007</v>
       </c>
-      <c r="J26" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47" t="s">
-        <v>114</v>
+      <c r="J26" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48" t="s">
+        <v>115</v>
       </c>
       <c r="M26" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N26" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O26" s="36">
         <v>12001</v>
       </c>
-      <c r="P26" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="48">
+      <c r="P26" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q26" s="49">
         <v>100700</v>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="49">
         <v>11007</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T26" s="49" t="s">
+      <c r="S26" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U26" s="50">
+      <c r="T26" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5169,21 +5185,21 @@
         <v>1</v>
       </c>
       <c r="W26" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X26" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y26" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z26" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA26" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB26" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5204,51 +5220,51 @@
         <v>2</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="13">
         <v>490</v>
       </c>
-      <c r="H27" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="46">
+      <c r="H27" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="47">
         <v>11003</v>
       </c>
-      <c r="J27" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47" t="s">
-        <v>118</v>
+      <c r="J27" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48" t="s">
+        <v>119</v>
       </c>
       <c r="M27" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N27" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O27" s="36">
         <v>12001</v>
       </c>
-      <c r="P27" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="48">
+      <c r="P27" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q27" s="49">
         <v>100300</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="49">
         <v>11003</v>
       </c>
-      <c r="S27" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T27" s="49" t="s">
+      <c r="S27" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U27" s="50">
+      <c r="T27" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U27" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5256,21 +5272,21 @@
         <v>2</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X27" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y27" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z27" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB27" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5291,51 +5307,51 @@
         <v>3</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="36"/>
       <c r="G28" s="13">
         <v>490</v>
       </c>
-      <c r="H28" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="46">
+      <c r="H28" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="47">
         <v>11012</v>
       </c>
-      <c r="J28" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47" t="s">
-        <v>120</v>
+      <c r="J28" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48" t="s">
+        <v>121</v>
       </c>
       <c r="M28" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N28" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O28" s="36">
         <v>12001</v>
       </c>
-      <c r="P28" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="48">
+      <c r="P28" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="49">
         <v>101200</v>
       </c>
-      <c r="R28" s="48">
+      <c r="R28" s="49">
         <v>11012</v>
       </c>
-      <c r="S28" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T28" s="49" t="s">
+      <c r="S28" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U28" s="50">
+      <c r="T28" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U28" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5343,21 +5359,21 @@
         <v>3</v>
       </c>
       <c r="W28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X28" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y28" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z28" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB28" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5378,51 +5394,51 @@
         <v>4</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="36"/>
       <c r="G29" s="13">
         <v>490</v>
       </c>
-      <c r="H29" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="46">
+      <c r="H29" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="47">
         <v>11014</v>
       </c>
-      <c r="J29" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47" t="s">
-        <v>122</v>
+      <c r="J29" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48" t="s">
+        <v>123</v>
       </c>
       <c r="M29" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N29" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O29" s="36">
         <v>12001</v>
       </c>
-      <c r="P29" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q29" s="48">
+      <c r="P29" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q29" s="49">
         <v>101400</v>
       </c>
-      <c r="R29" s="48">
+      <c r="R29" s="49">
         <v>11014</v>
       </c>
-      <c r="S29" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T29" s="49" t="s">
+      <c r="S29" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U29" s="50">
+      <c r="T29" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U29" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5430,21 +5446,21 @@
         <v>4</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X29" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y29" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA29" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB29" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5465,51 +5481,51 @@
         <v>5</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="36"/>
       <c r="G30" s="13">
         <v>490</v>
       </c>
-      <c r="H30" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="46">
+      <c r="H30" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="47">
         <v>11003</v>
       </c>
-      <c r="J30" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47" t="s">
-        <v>124</v>
+      <c r="J30" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48" t="s">
+        <v>125</v>
       </c>
       <c r="M30" s="36" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S30</f>
         <v>在任意遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N30" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O30" s="36">
         <v>12001</v>
       </c>
-      <c r="P30" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q30" s="48">
+      <c r="P30" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q30" s="49">
         <v>0</v>
       </c>
-      <c r="R30" s="48">
+      <c r="R30" s="49">
         <v>11003</v>
       </c>
-      <c r="S30" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T30" s="49" t="s">
+      <c r="S30" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U30" s="50">
+      <c r="T30" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U30" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5517,21 +5533,21 @@
         <v>5</v>
       </c>
       <c r="W30" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X30" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y30" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z30" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA30" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB30" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5551,52 +5567,52 @@
       <c r="D31" s="37">
         <v>1</v>
       </c>
-      <c r="E31" s="51" t="s">
-        <v>125</v>
+      <c r="E31" s="52" t="s">
+        <v>126</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="13">
         <v>1210</v>
       </c>
-      <c r="H31" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="52">
+      <c r="H31" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="53">
         <v>11007</v>
       </c>
-      <c r="J31" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53" t="s">
-        <v>126</v>
+      <c r="J31" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54" t="s">
+        <v>127</v>
       </c>
       <c r="M31" s="37" t="str">
         <f t="shared" ref="M31:M34" si="11">"在["&amp;P31&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S31</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O31" s="37">
         <v>12001</v>
       </c>
-      <c r="P31" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q31" s="54">
+      <c r="P31" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q31" s="55">
         <v>100700</v>
       </c>
-      <c r="R31" s="54">
+      <c r="R31" s="55">
         <v>11007</v>
       </c>
-      <c r="S31" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T31" s="55" t="s">
+      <c r="S31" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U31" s="56">
+      <c r="T31" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U31" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5604,21 +5620,21 @@
         <v>1</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X31" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z31" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA31" s="37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB31" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5638,52 +5654,52 @@
       <c r="D32" s="37">
         <v>2</v>
       </c>
-      <c r="E32" s="51" t="s">
-        <v>129</v>
+      <c r="E32" s="52" t="s">
+        <v>130</v>
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="13">
         <v>1210</v>
       </c>
-      <c r="H32" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="52">
+      <c r="H32" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="53">
         <v>11003</v>
       </c>
-      <c r="J32" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53" t="s">
-        <v>130</v>
+      <c r="J32" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54" t="s">
+        <v>131</v>
       </c>
       <c r="M32" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O32" s="37">
         <v>12001</v>
       </c>
-      <c r="P32" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q32" s="54">
+      <c r="P32" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q32" s="55">
         <v>100300</v>
       </c>
-      <c r="R32" s="54">
+      <c r="R32" s="55">
         <v>11003</v>
       </c>
-      <c r="S32" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T32" s="55" t="s">
+      <c r="S32" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U32" s="56">
+      <c r="T32" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U32" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5691,21 +5707,21 @@
         <v>2</v>
       </c>
       <c r="W32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X32" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y32" s="37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z32" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB32" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5725,52 +5741,52 @@
       <c r="D33" s="37">
         <v>3</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>131</v>
+      <c r="E33" s="52" t="s">
+        <v>132</v>
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="13">
         <v>1210</v>
       </c>
-      <c r="H33" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="52">
+      <c r="H33" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="53">
         <v>11012</v>
       </c>
-      <c r="J33" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53" t="s">
-        <v>132</v>
+      <c r="J33" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54" t="s">
+        <v>133</v>
       </c>
       <c r="M33" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O33" s="37">
         <v>12001</v>
       </c>
-      <c r="P33" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="54">
+      <c r="P33" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="55">
         <v>101200</v>
       </c>
-      <c r="R33" s="54">
+      <c r="R33" s="55">
         <v>11012</v>
       </c>
-      <c r="S33" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T33" s="55" t="s">
+      <c r="S33" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U33" s="56">
+      <c r="T33" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U33" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5778,21 +5794,21 @@
         <v>3</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X33" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z33" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB33" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5812,52 +5828,52 @@
       <c r="D34" s="37">
         <v>4</v>
       </c>
-      <c r="E34" s="51" t="s">
-        <v>133</v>
+      <c r="E34" s="52" t="s">
+        <v>134</v>
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="13">
         <v>1210</v>
       </c>
-      <c r="H34" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="52">
+      <c r="H34" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="53">
         <v>11014</v>
       </c>
-      <c r="J34" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53" t="s">
-        <v>134</v>
+      <c r="J34" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54" t="s">
+        <v>135</v>
       </c>
       <c r="M34" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N34" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O34" s="37">
         <v>12001</v>
       </c>
-      <c r="P34" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34" s="54">
+      <c r="P34" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q34" s="55">
         <v>101400</v>
       </c>
-      <c r="R34" s="54">
+      <c r="R34" s="55">
         <v>11014</v>
       </c>
-      <c r="S34" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T34" s="55" t="s">
+      <c r="S34" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U34" s="56">
+      <c r="T34" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U34" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5865,21 +5881,21 @@
         <v>4</v>
       </c>
       <c r="W34" s="37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X34" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y34" s="37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA34" s="37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB34" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5899,52 +5915,52 @@
       <c r="D35" s="37">
         <v>5</v>
       </c>
-      <c r="E35" s="51" t="s">
-        <v>135</v>
+      <c r="E35" s="52" t="s">
+        <v>136</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="13">
         <v>1210</v>
       </c>
-      <c r="H35" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="52">
+      <c r="H35" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="53">
         <v>11003</v>
       </c>
-      <c r="J35" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53" t="s">
-        <v>136</v>
+      <c r="J35" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54" t="s">
+        <v>137</v>
       </c>
       <c r="M35" s="37" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S35</f>
         <v>在任意遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N35" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O35" s="37">
         <v>12001</v>
       </c>
-      <c r="P35" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q35" s="54">
+      <c r="P35" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" s="55">
         <v>0</v>
       </c>
-      <c r="R35" s="54">
+      <c r="R35" s="55">
         <v>11003</v>
       </c>
-      <c r="S35" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T35" s="55" t="s">
+      <c r="S35" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U35" s="56">
+      <c r="T35" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U35" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5952,21 +5968,21 @@
         <v>5</v>
       </c>
       <c r="W35" s="37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X35" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y35" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z35" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA35" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB35" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5987,37 +6003,37 @@
         <v>1</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="13">
         <v>120</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I36" s="10">
         <v>11007</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M36" s="4" t="str">
         <f t="shared" ref="M36:M39" si="12">"在["&amp;P36&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S36</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O36" s="4">
         <v>10003</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q36" s="1">
         <v>100700</v>
@@ -6025,13 +6041,13 @@
       <c r="R36" s="1">
         <v>11007</v>
       </c>
-      <c r="S36" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T36" s="43" t="s">
+      <c r="S36" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U36" s="60">
+      <c r="T36" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U36" s="61">
         <f t="shared" ref="U36:U40" si="13">S36*3%/29000*7*2</f>
         <v>120.206896551724</v>
       </c>
@@ -6039,21 +6055,21 @@
         <v>1</v>
       </c>
       <c r="W36" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X36" s="4" t="str">
         <f>"In the ["&amp;W36&amp;"] , total gold coins won have reached  "&amp;S36</f>
         <v>In the [Mahjong Hu] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y36" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z36" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y36&amp;"], tổng số vàng thắng được đạt "&amp;S36</f>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA36" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB36" s="4" t="str">
         <f>"No jogo ["&amp;AA36&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S36</f>
@@ -6074,37 +6090,37 @@
         <v>2</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13">
         <v>120</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I37" s="10">
         <v>11003</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M37" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="4">
         <v>10003</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q37" s="1">
         <v>100300</v>
@@ -6112,13 +6128,13 @@
       <c r="R37" s="1">
         <v>11003</v>
       </c>
-      <c r="S37" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T37" s="43" t="s">
+      <c r="S37" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U37" s="60">
+      <c r="T37" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U37" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6126,21 +6142,21 @@
         <v>2</v>
       </c>
       <c r="W37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X37" s="4" t="str">
         <f t="shared" ref="X37:X55" si="14">"In the ["&amp;W37&amp;"] , total gold coins won have reached  "&amp;S37</f>
         <v>In the [Super Star] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y37" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z37" s="4" t="str">
         <f t="shared" ref="Z37:Z55" si="15">"Trong trò chơi ["&amp;Y37&amp;"], tổng số vàng thắng được đạt "&amp;S37</f>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB37" s="4" t="str">
         <f t="shared" ref="AB37:AB55" si="16">"No jogo ["&amp;AA37&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S37</f>
@@ -6161,37 +6177,37 @@
         <v>3</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="13">
         <v>120</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I38" s="10">
         <v>11012</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M38" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="4">
         <v>10003</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q38" s="1">
         <v>101200</v>
@@ -6199,13 +6215,13 @@
       <c r="R38" s="1">
         <v>11012</v>
       </c>
-      <c r="S38" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T38" s="43" t="s">
+      <c r="S38" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U38" s="60">
+      <c r="T38" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U38" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6213,21 +6229,21 @@
         <v>3</v>
       </c>
       <c r="W38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X38" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y38" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z38" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB38" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6248,37 +6264,37 @@
         <v>4</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="13">
         <v>120</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="10">
         <v>11014</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M39" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="4">
         <v>10003</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="1">
         <v>101400</v>
@@ -6286,13 +6302,13 @@
       <c r="R39" s="1">
         <v>11014</v>
       </c>
-      <c r="S39" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T39" s="43" t="s">
+      <c r="S39" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U39" s="60">
+      <c r="T39" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6300,21 +6316,21 @@
         <v>4</v>
       </c>
       <c r="W39" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X39" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y39" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z39" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA39" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB39" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6335,37 +6351,37 @@
         <v>5</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="13">
         <v>120</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I40" s="10">
         <v>11003</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M40" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S40</f>
         <v>在任意遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O40" s="4">
         <v>10003</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="1">
         <v>0</v>
@@ -6373,13 +6389,13 @@
       <c r="R40" s="1">
         <v>11003</v>
       </c>
-      <c r="S40" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T40" s="43" t="s">
+      <c r="S40" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U40" s="60">
+      <c r="T40" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U40" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6387,21 +6403,21 @@
         <v>5</v>
       </c>
       <c r="W40" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X40" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y40" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z40" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA40" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB40" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6422,37 +6438,37 @@
         <v>1</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="13">
         <v>260</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I41" s="10">
         <v>11007</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M41" s="4" t="str">
         <f t="shared" ref="M41:M44" si="17">"在["&amp;P41&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S41</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="4">
         <v>10003</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q41" s="1">
         <v>100700</v>
@@ -6460,13 +6476,13 @@
       <c r="R41" s="1">
         <v>11007</v>
       </c>
-      <c r="S41" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T41" s="43" t="s">
+      <c r="S41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U41" s="60">
+      <c r="T41" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U41" s="61">
         <f t="shared" ref="U41:U45" si="18">S41*3%/29000*7*2</f>
         <v>260.689655172414</v>
       </c>
@@ -6474,21 +6490,21 @@
         <v>1</v>
       </c>
       <c r="W41" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X41" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y41" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z41" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA41" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB41" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6509,37 +6525,37 @@
         <v>2</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
         <v>260</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>11003</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M42" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42" s="4">
         <v>10003</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q42" s="1">
         <v>100300</v>
@@ -6547,13 +6563,13 @@
       <c r="R42" s="1">
         <v>11003</v>
       </c>
-      <c r="S42" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T42" s="43" t="s">
+      <c r="S42" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U42" s="60">
+      <c r="T42" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U42" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6561,21 +6577,21 @@
         <v>2</v>
       </c>
       <c r="W42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X42" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y42" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z42" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB42" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6596,37 +6612,37 @@
         <v>3</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
         <v>260</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>11012</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M43" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O43" s="4">
         <v>10003</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q43" s="1">
         <v>101200</v>
@@ -6634,13 +6650,13 @@
       <c r="R43" s="1">
         <v>11012</v>
       </c>
-      <c r="S43" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T43" s="43" t="s">
+      <c r="S43" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U43" s="60">
+      <c r="T43" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U43" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6648,21 +6664,21 @@
         <v>3</v>
       </c>
       <c r="W43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X43" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y43" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z43" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB43" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6683,37 +6699,37 @@
         <v>4</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
         <v>260</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>11014</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M44" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44" s="4">
         <v>10003</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="1">
         <v>101400</v>
@@ -6721,13 +6737,13 @@
       <c r="R44" s="1">
         <v>11014</v>
       </c>
-      <c r="S44" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T44" s="43" t="s">
+      <c r="S44" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U44" s="60">
+      <c r="T44" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U44" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6735,21 +6751,21 @@
         <v>4</v>
       </c>
       <c r="W44" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X44" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y44" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z44" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA44" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB44" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6770,37 +6786,37 @@
         <v>5</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
         <v>260</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>11003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M45" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S45</f>
         <v>在任意遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O45" s="4">
         <v>10003</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="1">
         <v>0</v>
@@ -6808,13 +6824,13 @@
       <c r="R45" s="1">
         <v>11003</v>
       </c>
-      <c r="S45" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T45" s="43" t="s">
+      <c r="S45" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U45" s="60">
+      <c r="T45" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U45" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6822,21 +6838,21 @@
         <v>5</v>
       </c>
       <c r="W45" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X45" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y45" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z45" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA45" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB45" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6857,37 +6873,37 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
         <v>350</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>11007</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M46" s="4" t="str">
         <f t="shared" ref="M46:M49" si="19">"在["&amp;P46&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S46</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O46" s="4">
         <v>10003</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q46" s="1">
         <v>100700</v>
@@ -6895,13 +6911,13 @@
       <c r="R46" s="1">
         <v>11007</v>
       </c>
-      <c r="S46" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T46" s="43" t="s">
+      <c r="S46" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U46" s="60">
+      <c r="T46" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U46" s="61">
         <f t="shared" ref="U46:U55" si="20">S46*3%/29000*7*2</f>
         <v>350.48275862069</v>
       </c>
@@ -6909,21 +6925,21 @@
         <v>1</v>
       </c>
       <c r="W46" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X46" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z46" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA46" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB46" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6944,37 +6960,37 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
         <v>350</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>11003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M47" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O47" s="4">
         <v>10003</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q47" s="1">
         <v>100300</v>
@@ -6982,13 +6998,13 @@
       <c r="R47" s="1">
         <v>11003</v>
       </c>
-      <c r="S47" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" s="43" t="s">
+      <c r="S47" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U47" s="60">
+      <c r="T47" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U47" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -6996,21 +7012,21 @@
         <v>2</v>
       </c>
       <c r="W47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X47" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y47" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z47" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB47" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7031,37 +7047,37 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
         <v>350</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>11012</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M48" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O48" s="4">
         <v>10003</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q48" s="1">
         <v>101200</v>
@@ -7069,13 +7085,13 @@
       <c r="R48" s="1">
         <v>11012</v>
       </c>
-      <c r="S48" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T48" s="43" t="s">
+      <c r="S48" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U48" s="60">
+      <c r="T48" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U48" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7083,21 +7099,21 @@
         <v>3</v>
       </c>
       <c r="W48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X48" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y48" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z48" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB48" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7118,37 +7134,37 @@
         <v>4</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="13">
         <v>350</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I49" s="10">
         <v>11014</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M49" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O49" s="4">
         <v>10003</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="1">
         <v>101400</v>
@@ -7156,13 +7172,13 @@
       <c r="R49" s="1">
         <v>11014</v>
       </c>
-      <c r="S49" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T49" s="43" t="s">
+      <c r="S49" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U49" s="60">
+      <c r="T49" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U49" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7170,21 +7186,21 @@
         <v>4</v>
       </c>
       <c r="W49" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X49" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y49" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z49" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA49" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB49" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7205,37 +7221,37 @@
         <v>5</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13">
         <v>350</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I50" s="10">
         <v>11003</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M50" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S50</f>
         <v>在任意遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O50" s="4">
         <v>10003</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q50" s="1">
         <v>0</v>
@@ -7243,13 +7259,13 @@
       <c r="R50" s="1">
         <v>11003</v>
       </c>
-      <c r="S50" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T50" s="43" t="s">
+      <c r="S50" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U50" s="60">
+      <c r="T50" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U50" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7257,21 +7273,21 @@
         <v>5</v>
       </c>
       <c r="W50" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X50" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y50" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z50" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA50" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB50" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7292,51 +7308,51 @@
         <v>1</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F51" s="36"/>
       <c r="G51" s="13">
         <v>1200</v>
       </c>
-      <c r="H51" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="46">
+      <c r="H51" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="47">
         <v>11007</v>
       </c>
-      <c r="J51" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47" t="s">
-        <v>173</v>
+      <c r="J51" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48" t="s">
+        <v>174</v>
       </c>
       <c r="M51" s="36" t="str">
         <f t="shared" ref="M51:M54" si="21">"在["&amp;P51&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S51</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N51" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51" s="36">
         <v>10003</v>
       </c>
-      <c r="P51" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q51" s="48">
+      <c r="P51" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q51" s="49">
         <v>100700</v>
       </c>
-      <c r="R51" s="48">
+      <c r="R51" s="49">
         <v>11007</v>
       </c>
-      <c r="S51" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T51" s="49" t="s">
+      <c r="S51" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U51" s="50">
+      <c r="T51" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U51" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7344,21 +7360,21 @@
         <v>1</v>
       </c>
       <c r="W51" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X51" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y51" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z51" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA51" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB51" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7379,51 +7395,51 @@
         <v>2</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="13">
         <v>1200</v>
       </c>
-      <c r="H52" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="46">
+      <c r="H52" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="47">
         <v>11003</v>
       </c>
-      <c r="J52" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K52" s="47"/>
-      <c r="L52" s="47" t="s">
-        <v>177</v>
+      <c r="J52" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52" s="48"/>
+      <c r="L52" s="48" t="s">
+        <v>178</v>
       </c>
       <c r="M52" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N52" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O52" s="36">
         <v>10003</v>
       </c>
-      <c r="P52" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q52" s="48">
+      <c r="P52" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q52" s="49">
         <v>100300</v>
       </c>
-      <c r="R52" s="48">
+      <c r="R52" s="49">
         <v>11003</v>
       </c>
-      <c r="S52" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T52" s="49" t="s">
+      <c r="S52" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U52" s="50">
+      <c r="T52" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U52" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7431,21 +7447,21 @@
         <v>2</v>
       </c>
       <c r="W52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X52" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y52" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z52" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB52" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7466,51 +7482,51 @@
         <v>3</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F53" s="36"/>
       <c r="G53" s="13">
         <v>1200</v>
       </c>
-      <c r="H53" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="46">
+      <c r="H53" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="47">
         <v>11012</v>
       </c>
-      <c r="J53" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47" t="s">
-        <v>179</v>
+      <c r="J53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K53" s="48"/>
+      <c r="L53" s="48" t="s">
+        <v>180</v>
       </c>
       <c r="M53" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N53" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O53" s="36">
         <v>10003</v>
       </c>
-      <c r="P53" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q53" s="48">
+      <c r="P53" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="49">
         <v>101200</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="49">
         <v>11012</v>
       </c>
-      <c r="S53" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T53" s="49" t="s">
+      <c r="S53" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U53" s="50">
+      <c r="T53" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U53" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7518,21 +7534,21 @@
         <v>3</v>
       </c>
       <c r="W53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X53" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y53" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z53" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB53" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7553,51 +7569,51 @@
         <v>4</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="13">
         <v>1200</v>
       </c>
-      <c r="H54" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="46">
+      <c r="H54" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="47">
         <v>11014</v>
       </c>
-      <c r="J54" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47" t="s">
-        <v>181</v>
+      <c r="J54" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="48"/>
+      <c r="L54" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="M54" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N54" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O54" s="36">
         <v>10003</v>
       </c>
-      <c r="P54" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q54" s="48">
+      <c r="P54" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q54" s="49">
         <v>101400</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="49">
         <v>11014</v>
       </c>
-      <c r="S54" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T54" s="49" t="s">
+      <c r="S54" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U54" s="50">
+      <c r="T54" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U54" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7605,21 +7621,21 @@
         <v>4</v>
       </c>
       <c r="W54" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X54" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y54" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z54" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA54" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB54" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7640,51 +7656,51 @@
         <v>5</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="13">
         <v>1200</v>
       </c>
-      <c r="H55" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="46">
+      <c r="H55" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="47">
         <v>11003</v>
       </c>
-      <c r="J55" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="K55" s="47"/>
-      <c r="L55" s="47" t="s">
-        <v>183</v>
+      <c r="J55" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="48"/>
+      <c r="L55" s="48" t="s">
+        <v>184</v>
       </c>
       <c r="M55" s="36" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S55</f>
         <v>在任意遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N55" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O55" s="36">
         <v>10003</v>
       </c>
-      <c r="P55" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q55" s="48">
+      <c r="P55" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q55" s="49">
         <v>0</v>
       </c>
-      <c r="R55" s="48">
+      <c r="R55" s="49">
         <v>11003</v>
       </c>
-      <c r="S55" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T55" s="49" t="s">
+      <c r="S55" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U55" s="50">
+      <c r="T55" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U55" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7692,21 +7708,21 @@
         <v>5</v>
       </c>
       <c r="W55" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X55" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y55" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z55" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA55" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB55" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7727,37 +7743,37 @@
         <v>1</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="13">
         <v>5</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I56" s="10">
         <v>11007</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M56" s="4" t="str">
         <f>"在["&amp;P56&amp;"]電子遊戲中，累積旋轉 "&amp;S56&amp;"次"</f>
         <v>在[麻将胡了]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="4">
         <v>10001</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q56" s="1">
         <v>100700</v>
@@ -7765,11 +7781,11 @@
       <c r="R56" s="1">
         <v>11007</v>
       </c>
-      <c r="S56" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T56" s="43" t="s">
-        <v>187</v>
+      <c r="S56" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T56" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U56" s="4">
         <f t="shared" ref="U56:U60" si="22">S56/100</f>
@@ -7779,21 +7795,21 @@
         <v>1</v>
       </c>
       <c r="W56" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X56" s="4" t="str">
         <f>"In the game ["&amp;W56&amp;"] , "&amp;S56&amp;" spins have been accumulated."</f>
         <v>In the game [Mahjong Hu] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y56" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z56" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y56&amp;"], tích lũy quay "&amp;T56&amp;" lần."</f>
         <v>Trong trò chơi [Mạt chược], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA56" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB56" s="4" t="str">
         <f>"No jogo ["&amp;W56&amp;"], foram acumuladas "&amp;T56&amp;" rodadas."</f>
@@ -7814,37 +7830,37 @@
         <v>2</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="13">
         <v>5</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" s="10">
         <v>11003</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M57" s="4" t="str">
         <f>"在["&amp;P57&amp;"]電子遊戲中，累積旋轉 "&amp;S57&amp;"次"</f>
         <v>在[超级明星]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="4">
         <v>10001</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q57" s="1">
         <v>100300</v>
@@ -7852,11 +7868,11 @@
       <c r="R57" s="1">
         <v>11003</v>
       </c>
-      <c r="S57" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T57" s="43" t="s">
-        <v>187</v>
+      <c r="S57" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T57" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U57" s="4">
         <f t="shared" si="22"/>
@@ -7866,21 +7882,21 @@
         <v>2</v>
       </c>
       <c r="W57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X57" s="4" t="str">
         <f>"In the game ["&amp;W57&amp;"] , "&amp;S57&amp;" spins have been accumulated."</f>
         <v>In the game [Super Star] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y57" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z57" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y57&amp;"], tích lũy quay "&amp;T57&amp;" lần."</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB57" s="4" t="str">
         <f>"No jogo ["&amp;W57&amp;"], foram acumuladas "&amp;T57&amp;" rodadas."</f>
@@ -7901,37 +7917,37 @@
         <v>3</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="13">
         <v>5</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I58" s="10">
         <v>11012</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M58" s="4" t="str">
         <f>"在["&amp;P58&amp;"]電子遊戲中，累積旋轉 "&amp;S58&amp;"次"</f>
         <v>在[财神]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O58" s="4">
         <v>10001</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q58" s="1">
         <v>101200</v>
@@ -7939,11 +7955,11 @@
       <c r="R58" s="1">
         <v>11012</v>
       </c>
-      <c r="S58" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T58" s="43" t="s">
-        <v>187</v>
+      <c r="S58" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T58" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U58" s="4">
         <f t="shared" si="22"/>
@@ -7953,21 +7969,21 @@
         <v>3</v>
       </c>
       <c r="W58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X58" s="4" t="str">
         <f>"In the game ["&amp;W58&amp;"] , "&amp;S58&amp;" spins have been accumulated."</f>
         <v>In the game [God of Wealth] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y58" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z58" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y58&amp;"], tích lũy quay "&amp;T58&amp;" lần."</f>
         <v>Trong trò chơi [Thần Tài], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB58" s="4" t="str">
         <f>"No jogo ["&amp;W58&amp;"], foram acumuladas "&amp;T58&amp;" rodadas."</f>
@@ -7988,37 +8004,37 @@
         <v>4</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>11014</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M59" s="4" t="str">
         <f>"在["&amp;P59&amp;"]電子遊戲中，累積旋轉 "&amp;S59&amp;"次"</f>
         <v>在[埃及艳后]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O59" s="4">
         <v>10001</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q59" s="1">
         <v>101400</v>
@@ -8026,11 +8042,11 @@
       <c r="R59" s="1">
         <v>11014</v>
       </c>
-      <c r="S59" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T59" s="43" t="s">
-        <v>187</v>
+      <c r="S59" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T59" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U59" s="4">
         <f t="shared" si="22"/>
@@ -8040,21 +8056,21 @@
         <v>4</v>
       </c>
       <c r="W59" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X59" s="4" t="str">
         <f>"In the game ["&amp;W59&amp;"] , "&amp;S59&amp;" spins have been accumulated."</f>
         <v>In the game [Cleopatra] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y59" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z59" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y59&amp;"], tích lũy quay "&amp;T59&amp;" lần."</f>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA59" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB59" s="4" t="str">
         <f>"No jogo ["&amp;W59&amp;"], foram acumuladas "&amp;T59&amp;" rodadas."</f>
@@ -8075,31 +8091,31 @@
         <v>5</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>5</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>11003</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M60" s="4" t="str">
         <f>"在任意電子遊戲中，累積旋轉 "&amp;S60&amp;"次"</f>
         <v>在任意電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="4">
         <v>10001</v>
@@ -8111,11 +8127,11 @@
       <c r="R60" s="1">
         <v>11003</v>
       </c>
-      <c r="S60" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T60" s="43" t="s">
-        <v>187</v>
+      <c r="S60" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T60" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U60" s="4">
         <f t="shared" si="22"/>
@@ -8125,21 +8141,21 @@
         <v>5</v>
       </c>
       <c r="W60" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X60" s="4" t="str">
         <f>"In the game ["&amp;W60&amp;"] , "&amp;S60&amp;" spins have been accumulated."</f>
         <v>In the game [any game] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y60" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z60" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y60&amp;"], tích lũy quay "&amp;T60&amp;" lần."</f>
         <v>Trong trò chơi [bất kỳ], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA60" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB60" s="4" t="str">
         <f>"No jogo ["&amp;W60&amp;"], foram acumuladas "&amp;T60&amp;" rodadas."</f>
@@ -8181,16 +8197,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J5" s="19">
         <v>502</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -8201,32 +8217,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -8234,37 +8250,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F7" s="18">
         <v>100100</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J7" s="18">
         <v>2</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N7" s="18">
         <v>1022501</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -8272,37 +8288,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="18">
         <v>100300</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J8" s="18">
         <v>3</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N8" s="18">
         <v>1022502</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -8310,37 +8326,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" s="18">
         <v>100700</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J9" s="18">
         <v>4</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N9" s="18">
         <v>1010301</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -8348,37 +8364,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="18">
         <v>101200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="18">
         <v>5</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N10" s="18">
         <v>1010302</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -8386,37 +8402,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F11" s="18">
         <v>101400</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J11" s="18">
         <v>6</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N11" s="18">
         <v>1010303</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -8424,37 +8440,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="18">
         <v>200100</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="25">
         <v>12</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N12" s="18">
         <v>1010311</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -8462,19 +8478,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13" s="18">
         <v>200101</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -8483,10 +8499,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -8494,19 +8510,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F14" s="18">
         <v>200300</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -8515,10 +8531,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -8526,28 +8542,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" s="18">
         <v>200400</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N15" s="18">
         <v>1010314</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -8555,28 +8571,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F16" s="18">
         <v>200500</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N16" s="18">
         <v>1010315</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -8584,19 +8600,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F17" s="18">
         <v>200600</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -8604,19 +8620,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F18" s="18">
         <v>200700</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -8624,22 +8640,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="18">
         <v>200800</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -8647,28 +8663,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F20" s="18">
         <v>200900</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -8676,28 +8692,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F21" s="18">
         <v>201000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N21" s="18">
         <v>1022501</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -8705,28 +8721,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F22" s="18">
         <v>300100</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N22" s="18">
         <v>1022502</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -8734,19 +8750,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N23" s="18">
         <v>1980000</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -8754,10 +8770,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -8765,10 +8781,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -8776,10 +8792,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -8787,10 +8803,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -8798,10 +8814,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -8809,10 +8825,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -8820,10 +8836,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -8831,10 +8847,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -8842,10 +8858,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -8853,10 +8869,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:22">
@@ -8871,7 +8887,7 @@
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28" t="s">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>4</v>
@@ -8898,19 +8914,19 @@
         <v>11</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:22">
@@ -8925,25 +8941,25 @@
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L39" s="33" t="s">
         <v>13</v>
@@ -8951,38 +8967,38 @@
     </row>
     <row r="40" s="3" customFormat="1" spans="1:22">
       <c r="A40" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L40" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:22">
@@ -9014,36 +9030,36 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
         <v>3</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>3002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
         <v>70008</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O42" s="4">
         <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -9079,36 +9095,36 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
         <v>8</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>3002</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O43" s="4">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>0.25</v>
@@ -9144,36 +9160,36 @@
         <v>2</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
         <v>25</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>3002</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O44" s="4">
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>0.25</v>
@@ -9208,30 +9224,30 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
         <v>20</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>2003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O45" s="4">
         <v>2</v>
@@ -9270,30 +9286,30 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
         <v>1</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>2003</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -9332,30 +9348,30 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
         <v>5</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>2003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -9394,30 +9410,30 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
         <v>10</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>2003</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O48" s="4">
         <v>1</v>
@@ -9461,7 +9477,7 @@
         <v>70001</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -9471,7 +9487,7 @@
         <v>70002</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -9481,7 +9497,7 @@
         <v>70003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -9491,7 +9507,7 @@
         <v>70004</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -9501,10 +9517,10 @@
         <v>70005</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L5" s="10">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9516,10 +9532,10 @@
         <v>70006</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L6" s="10">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9531,10 +9547,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>317</v>
       </c>
       <c r="L7" s="10">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9546,10 +9562,10 @@
         <v>70008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L8" s="10">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9561,10 +9577,10 @@
         <v>70009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" s="10">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9576,10 +9592,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L10" s="10">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9591,10 +9607,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L11" s="10">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9606,10 +9622,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L12" s="10">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9621,10 +9637,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L13" s="10">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9636,10 +9652,10 @@
         <v>70104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" s="10">
         <f>_xlfn.XLOOKUP(K14,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9651,10 +9667,10 @@
         <v>70301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="10">
         <f>_xlfn.XLOOKUP(K15,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9666,10 +9682,10 @@
         <v>70302</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L16" s="10">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9681,10 +9697,10 @@
         <v>70303</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L17" s="10">
         <f>_xlfn.XLOOKUP(K17,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9696,10 +9712,10 @@
         <v>70304</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L18" s="10">
         <f>_xlfn.XLOOKUP(K18,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9711,10 +9727,10 @@
         <v>70305</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L19" s="10">
         <f>_xlfn.XLOOKUP(K19,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9726,10 +9742,10 @@
         <v>70306</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L20" s="10">
         <f>_xlfn.XLOOKUP(K20,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9741,10 +9757,10 @@
         <v>70307</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L21" s="10">
         <f>_xlfn.XLOOKUP(K21,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9756,10 +9772,10 @@
         <v>70308</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L22" s="10">
         <f>_xlfn.XLOOKUP(K22,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9771,10 +9787,10 @@
         <v>70309</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L23" s="10">
         <f>_xlfn.XLOOKUP(K23,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9786,10 +9802,10 @@
         <v>70310</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L24" s="10">
         <f>_xlfn.XLOOKUP(K24,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9801,10 +9817,10 @@
         <v>70311</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L25" s="10">
         <f>_xlfn.XLOOKUP(K25,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9816,10 +9832,10 @@
         <v>70312</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L26" s="10">
         <f>_xlfn.XLOOKUP(K26,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9831,10 +9847,10 @@
         <v>70381</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L27" s="10">
         <f>_xlfn.XLOOKUP(K27,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9846,10 +9862,10 @@
         <v>70382</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L28" s="10">
         <f>_xlfn.XLOOKUP(K28,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9861,10 +9877,10 @@
         <v>70383</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L29" s="10">
         <f>_xlfn.XLOOKUP(K29,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9876,10 +9892,10 @@
         <v>70391</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L30" s="10">
         <f>_xlfn.XLOOKUP(K30,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9891,10 +9907,10 @@
         <v>70392</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L31" s="10">
         <f>_xlfn.XLOOKUP(K31,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9906,10 +9922,10 @@
         <v>70393</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L32" s="10">
         <f>_xlfn.XLOOKUP(K32,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9921,10 +9937,10 @@
         <v>71101</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L33" s="10">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9936,10 +9952,10 @@
         <v>71102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L34" s="10">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9951,10 +9967,10 @@
         <v>71103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L35" s="10">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9966,10 +9982,10 @@
         <v>71201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L36" s="10">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9981,10 +9997,10 @@
         <v>71202</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L37" s="10">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9996,10 +10012,10 @@
         <v>72011</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L38" s="10">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10011,10 +10027,10 @@
         <v>72012</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L39" s="10">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10026,10 +10042,10 @@
         <v>72101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L40" s="10">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10041,10 +10057,10 @@
         <v>72102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L41" s="10">
         <f>_xlfn.XLOOKUP(K41,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10053,7 +10069,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="K42" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L42" s="10">
         <f>_xlfn.XLOOKUP(K42,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10062,7 +10078,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="K43" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L43" s="10">
         <f>_xlfn.XLOOKUP(K43,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10071,7 +10087,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="K44" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L44" s="10">
         <f>_xlfn.XLOOKUP(K44,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10080,7 +10096,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="K45" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L45" s="10">
         <f>_xlfn.XLOOKUP(K45,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10172,30 +10188,30 @@
         <v>1</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>2001</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8">
         <v>70007</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
@@ -10231,30 +10247,30 @@
         <v>1</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>10</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>2001</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="O60" s="3">
         <v>7000</v>
@@ -10292,30 +10308,30 @@
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13">
         <v>100</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I61" s="10">
         <v>2001</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O61" s="3">
         <v>70000</v>
@@ -10353,30 +10369,30 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="13">
         <v>1000</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I62" s="10">
         <v>2001</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O62" s="3">
         <v>700000</v>
@@ -10413,29 +10429,29 @@
         <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="15">
         <v>10</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I63" s="11">
         <v>2002</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L63" s="16">
         <v>70007</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P63" s="4"/>
     </row>
@@ -10454,29 +10470,29 @@
         <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F65" s="14"/>
       <c r="G65" s="15">
         <v>20</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I65" s="11">
         <v>1001</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L65" s="16">
         <v>70001</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V65" s="4">
         <f>ROUND(MAX(S65/100,T65/100,U65),0)</f>
@@ -10498,29 +10514,29 @@
         <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="15">
         <v>100</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I66" s="11">
         <v>2001</v>
       </c>
       <c r="J66" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="K66" s="16" t="s">
         <v>361</v>
-      </c>
-      <c r="K66" s="16" t="s">
-        <v>359</v>
       </c>
       <c r="L66" s="16">
         <v>70002</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:22">
@@ -10538,29 +10554,29 @@
         <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="15">
         <v>10</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I67" s="11">
         <v>2002</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L67" s="16">
         <v>70003</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:22">
@@ -10578,29 +10594,29 @@
         <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F68" s="14"/>
       <c r="G68" s="15">
         <v>40</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I68" s="11">
         <v>2003</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L68" s="16">
         <v>70004</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:22">
@@ -10618,29 +10634,29 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="15">
         <v>10</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I69" s="11">
         <v>1001</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L69" s="16">
         <v>70005</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N69" s="17"/>
     </row>
@@ -10659,29 +10675,29 @@
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="15">
         <v>20</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I70" s="11">
         <v>2001</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L70" s="16">
         <v>70006</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N70" s="17"/>
     </row>
@@ -10700,29 +10716,29 @@
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="15">
         <v>5</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I71" s="11">
         <v>2003</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L71" s="16">
         <v>70008</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N71" s="17"/>
     </row>
@@ -10741,29 +10757,29 @@
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="15">
         <v>1</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I72" s="11">
         <v>1001</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L72" s="16">
         <v>70009</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N72" s="17"/>
     </row>
@@ -10782,29 +10798,29 @@
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="15">
         <v>5</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I73" s="11">
         <v>2001</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L73" s="16">
         <v>70010</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -10831,384 +10847,384 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1">
         <v>100100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1">
         <v>100300</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>100700</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1">
         <v>101200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="1">
         <v>101400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B7" s="1">
         <v>101700</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B8" s="1">
         <v>102100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B9" s="1">
         <v>102200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1">
         <v>102300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1">
         <v>102400</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1">
         <v>102500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B13" s="1">
         <v>200100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B14" s="1">
         <v>200101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B15" s="1">
         <v>200300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B16" s="1">
         <v>200400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B17" s="1">
         <v>200500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B18" s="1">
         <v>200600</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B19" s="1">
         <v>200700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B20" s="1">
         <v>200800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B21" s="1">
         <v>200900</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B22" s="1">
         <v>300100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B23" s="1">
         <v>300200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B24" s="1">
         <v>500000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1">
         <v>500001</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B26" s="1">
         <v>500002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B27" s="1">
         <v>500003</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B28" s="1">
         <v>500004</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B29" s="1">
         <v>500005</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1">
         <v>500006</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1">
         <v>500007</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1">
         <v>600000</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="1">
         <v>600001</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B34" s="1">
         <v>600002</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1">
         <v>600003</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -101,7 +101,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置 condition.xlsx 文件中的ID</t>
+配置 condition.xlsx 文件中的ID
+充值类型的单位是分，比如要求充值9.99美元，需要填 999</t>
         </r>
       </text>
     </comment>
@@ -459,7 +460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="425">
   <si>
     <t>任务ID</t>
   </si>
@@ -470,7 +471,7 @@
     <t>任务组</t>
   </si>
   <si>
-    <t>任务条件</t>
+    <t>任务条件（充值货币单位是分，服务端会除以100）</t>
   </si>
   <si>
     <t>道具奖励</t>
@@ -503,6 +504,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
@@ -542,7 +546,7 @@
     <t>language</t>
   </si>
   <si>
-    <t>11002_300000_0</t>
+    <t>11002_30000000_0</t>
   </si>
   <si>
     <t>itemicon_1022504.png</t>
@@ -563,7 +567,7 @@
     <t>300000</t>
   </si>
   <si>
-    <t>11002_1400000_0</t>
+    <t>11002_140000000_0</t>
   </si>
   <si>
     <t>70002</t>
@@ -575,7 +579,7 @@
     <t>1400000</t>
   </si>
   <si>
-    <t>11002_8300000_0</t>
+    <t>11002_830000000_0</t>
   </si>
   <si>
     <t>70003</t>
@@ -587,7 +591,7 @@
     <t>8300000</t>
   </si>
   <si>
-    <t>11002_32000000_0</t>
+    <t>11002_3200000000_0</t>
   </si>
   <si>
     <t>70004</t>
@@ -599,7 +603,7 @@
     <t>32000000</t>
   </si>
   <si>
-    <t>11002_132000000_0</t>
+    <t>11002_13200000000_0</t>
   </si>
   <si>
     <t>70005</t>
@@ -611,7 +615,7 @@
     <t>132000000</t>
   </si>
   <si>
-    <t>11002_200000000_0</t>
+    <t>11002_20000000000_0</t>
   </si>
   <si>
     <t>70006</t>
@@ -1349,6 +1353,9 @@
   </si>
   <si>
     <t>德州-房间</t>
+  </si>
+  <si>
+    <t>任务条件</t>
   </si>
   <si>
     <t>价值转化</t>
@@ -1980,7 +1987,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2056,6 +2063,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2378,7 +2391,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2402,16 +2415,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2420,89 +2433,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2632,6 +2645,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2680,7 +2696,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -3269,22 +3285,22 @@
         <v>14</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>13</v>
@@ -3292,38 +3308,38 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="28"/>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -3353,32 +3369,32 @@
       <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>27</v>
+      <c r="E5" s="43" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="10">
         <v>2003</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="4" t="str">
         <f t="shared" ref="M5:M10" si="0">"累積充值達到 "&amp;S5&amp;" ₫"</f>
         <v>累積充值達到 300,000 ₫</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1">
         <v>11002</v>
@@ -3388,13 +3404,13 @@
       <c r="R5" s="1">
         <v>2003</v>
       </c>
-      <c r="S5" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="T5" s="43" t="s">
+      <c r="S5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="44">
+      <c r="T5" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="45">
         <f t="shared" ref="U5:U10" si="1">S5/29000*7*3%</f>
         <v>2.17241379310345</v>
       </c>
@@ -3430,32 +3446,32 @@
       <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>34</v>
+      <c r="E6" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13">
         <v>10</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="10">
         <v>2003</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 1,400,000 ₫</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="1">
         <v>11002</v>
@@ -3465,13 +3481,13 @@
       <c r="R6" s="1">
         <v>2003</v>
       </c>
-      <c r="S6" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="43" t="s">
+      <c r="S6" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="44">
+      <c r="T6" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="U6" s="45">
         <f t="shared" si="1"/>
         <v>10.1379310344828</v>
       </c>
@@ -3507,32 +3523,32 @@
       <c r="D7" s="12">
         <v>1</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>38</v>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
         <v>60</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10">
         <v>2003</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 8,300,000 ₫</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" s="1">
         <v>11002</v>
@@ -3542,13 +3558,13 @@
       <c r="R7" s="1">
         <v>2003</v>
       </c>
-      <c r="S7" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T7" s="43" t="s">
+      <c r="S7" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="44">
+      <c r="T7" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" s="45">
         <f t="shared" si="1"/>
         <v>60.1034482758621</v>
       </c>
@@ -3584,32 +3600,32 @@
       <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>42</v>
+      <c r="E8" s="43" t="s">
+        <v>43</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="13">
         <v>230</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="10">
         <v>2003</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 32,000,000 ₫</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O8" s="1">
         <v>11002</v>
@@ -3619,13 +3635,13 @@
       <c r="R8" s="1">
         <v>2003</v>
       </c>
-      <c r="S8" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="43" t="s">
+      <c r="S8" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="44">
+      <c r="T8" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="45">
         <f t="shared" si="1"/>
         <v>231.724137931035</v>
       </c>
@@ -3661,48 +3677,48 @@
       <c r="D9" s="36">
         <v>1</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>46</v>
+      <c r="E9" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="13">
         <v>950</v>
       </c>
-      <c r="H9" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="46">
+      <c r="H9" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="47">
         <v>2003</v>
       </c>
-      <c r="J9" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="47"/>
+      <c r="J9" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="48"/>
       <c r="L9" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" s="36" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 132,000,000 ₫</v>
       </c>
-      <c r="N9" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="48">
+      <c r="N9" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="49">
         <v>11002</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48">
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49">
         <v>2003</v>
       </c>
-      <c r="S9" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="49" t="s">
+      <c r="S9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="50">
+      <c r="T9" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="51">
         <f t="shared" si="1"/>
         <v>955.862068965517</v>
       </c>
@@ -3736,48 +3752,48 @@
       <c r="D10" s="37">
         <v>1</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>50</v>
+      <c r="E10" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="13">
         <v>1440</v>
       </c>
-      <c r="H10" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="52">
+      <c r="H10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="53">
         <v>2003</v>
       </c>
-      <c r="J10" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="53"/>
+      <c r="J10" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="54"/>
       <c r="L10" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M10" s="37" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 200,000,000 ₫</v>
       </c>
-      <c r="N10" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="54">
+      <c r="N10" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="55">
         <v>11002</v>
       </c>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54">
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55">
         <v>2003</v>
       </c>
-      <c r="S10" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="T10" s="55" t="s">
+      <c r="S10" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="U10" s="56">
+      <c r="T10" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="U10" s="57">
         <f t="shared" si="1"/>
         <v>1448.27586206897</v>
       </c>
@@ -3812,37 +3828,37 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="13">
         <v>20</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I11" s="10">
         <v>11007</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M11" s="4" t="str">
         <f t="shared" ref="M11:M14" si="5">"在["&amp;P11&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S11</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O11" s="4">
         <v>12001</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="1">
         <v>100700</v>
@@ -3850,13 +3866,13 @@
       <c r="R11" s="1">
         <v>11007</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T11" s="43" t="s">
+      <c r="S11" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U11" s="57">
+      <c r="T11" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11" s="58">
         <f t="shared" ref="U11:U35" si="6">S11*3%/29000*7</f>
         <v>24.6206896551724</v>
       </c>
@@ -3864,21 +3880,21 @@
         <v>1</v>
       </c>
       <c r="W11" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X11" s="4" t="str">
         <f>"In the ["&amp;W11&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S11</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y11" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z11" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y11&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S11</f>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA11" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB11" s="4" t="str">
         <f>"No videogame ["&amp;AA11&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S11</f>
@@ -3899,37 +3915,37 @@
         <v>2</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="13">
         <v>20</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="10">
         <v>11003</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M12" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O12" s="4">
         <v>12001</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q12" s="1">
         <v>100300</v>
@@ -3937,13 +3953,13 @@
       <c r="R12" s="1">
         <v>11003</v>
       </c>
-      <c r="S12" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T12" s="43" t="s">
+      <c r="S12" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U12" s="57">
+      <c r="T12" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -3951,21 +3967,21 @@
         <v>2</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X12" s="4" t="str">
         <f>"In the ["&amp;W12&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S12</f>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y12" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z12" s="4" t="str">
         <f t="shared" ref="Z12:Z35" si="7">"Trong trò chơi ["&amp;Y12&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S12</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB12" s="4" t="str">
         <f t="shared" ref="AB12:AB35" si="8">"No videogame ["&amp;AA12&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S12</f>
@@ -3986,37 +4002,37 @@
         <v>3</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13">
         <v>20</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="10">
         <v>11012</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M13" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O13" s="4">
         <v>12001</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q13" s="1">
         <v>101200</v>
@@ -4024,13 +4040,13 @@
       <c r="R13" s="1">
         <v>11012</v>
       </c>
-      <c r="S13" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T13" s="43" t="s">
+      <c r="S13" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U13" s="57">
+      <c r="T13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4038,21 +4054,21 @@
         <v>3</v>
       </c>
       <c r="W13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X13" s="4" t="str">
         <f>"In the ["&amp;W13&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S13</f>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y13" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB13" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4073,37 +4089,37 @@
         <v>4</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13">
         <v>20</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="10">
         <v>11014</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O14" s="4">
         <v>12001</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="1">
         <v>101400</v>
@@ -4111,13 +4127,13 @@
       <c r="R14" s="1">
         <v>11014</v>
       </c>
-      <c r="S14" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="43" t="s">
+      <c r="S14" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="57">
+      <c r="T14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U14" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4125,21 +4141,21 @@
         <v>4</v>
       </c>
       <c r="W14" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X14" s="4" t="str">
         <f>"In the ["&amp;W14&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S14</f>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y14" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z14" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB14" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4160,37 +4176,37 @@
         <v>5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13">
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="10">
         <v>11003</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S15</f>
         <v>在任意遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O15" s="4">
         <v>12001</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q15" s="1">
         <v>0</v>
@@ -4198,13 +4214,13 @@
       <c r="R15" s="1">
         <v>11003</v>
       </c>
-      <c r="S15" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T15" s="43" t="s">
+      <c r="S15" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U15" s="57">
+      <c r="T15" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U15" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4212,21 +4228,21 @@
         <v>5</v>
       </c>
       <c r="W15" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X15" s="4" t="str">
         <f>"In the ["&amp;W15&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S15</f>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y15" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4240,44 +4256,44 @@
       <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="59">
         <v>1200101</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13">
         <v>60</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="10">
         <v>11007</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" s="4" t="str">
         <f>"在["&amp;P16&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S16</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O16" s="4">
         <v>12001</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="1">
         <v>100700</v>
@@ -4285,13 +4301,13 @@
       <c r="R16" s="1">
         <v>11007</v>
       </c>
-      <c r="S16" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T16" s="43" t="s">
+      <c r="S16" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U16" s="57">
+      <c r="T16" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4299,21 +4315,21 @@
         <v>1</v>
       </c>
       <c r="W16" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X16" s="4" t="str">
         <f t="shared" ref="X16:X35" si="9">"In the ["&amp;W16&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S16</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y16" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z16" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA16" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB16" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4327,44 +4343,44 @@
       <c r="B17" s="12">
         <v>1</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="59">
         <v>1200101</v>
       </c>
       <c r="D17" s="12">
         <v>2</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13">
         <v>60</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I17" s="10">
         <v>11003</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M17" s="4" t="str">
         <f>"在["&amp;P17&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S17</f>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="4">
         <v>12001</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="1">
         <v>100300</v>
@@ -4372,13 +4388,13 @@
       <c r="R17" s="1">
         <v>11003</v>
       </c>
-      <c r="S17" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T17" s="43" t="s">
+      <c r="S17" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U17" s="57">
+      <c r="T17" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4386,21 +4402,21 @@
         <v>2</v>
       </c>
       <c r="W17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X17" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y17" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z17" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB17" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4414,44 +4430,44 @@
       <c r="B18" s="12">
         <v>1</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="59">
         <v>1200101</v>
       </c>
       <c r="D18" s="12">
         <v>3</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13">
         <v>60</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I18" s="10">
         <v>11012</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M18" s="4" t="str">
         <f>"在["&amp;P18&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S18</f>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O18" s="4">
         <v>12001</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="1">
         <v>101200</v>
@@ -4459,13 +4475,13 @@
       <c r="R18" s="1">
         <v>11012</v>
       </c>
-      <c r="S18" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T18" s="43" t="s">
+      <c r="S18" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U18" s="57">
+      <c r="T18" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4473,21 +4489,21 @@
         <v>3</v>
       </c>
       <c r="W18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X18" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y18" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z18" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB18" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4501,44 +4517,44 @@
       <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <v>1200101</v>
       </c>
       <c r="D19" s="12">
         <v>4</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13">
         <v>60</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="10">
         <v>11014</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M19" s="4" t="str">
         <f>"在["&amp;P19&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S19</f>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O19" s="4">
         <v>12001</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="1">
         <v>101400</v>
@@ -4546,13 +4562,13 @@
       <c r="R19" s="1">
         <v>11014</v>
       </c>
-      <c r="S19" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T19" s="43" t="s">
+      <c r="S19" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U19" s="57">
+      <c r="T19" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4560,21 +4576,21 @@
         <v>4</v>
       </c>
       <c r="W19" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X19" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y19" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z19" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB19" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4588,44 +4604,44 @@
       <c r="B20" s="12">
         <v>1</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="59">
         <v>1200101</v>
       </c>
       <c r="D20" s="12">
         <v>5</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13">
         <v>60</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="10">
         <v>11003</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M20" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S20</f>
         <v>在任意遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O20" s="4">
         <v>12001</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -4633,13 +4649,13 @@
       <c r="R20" s="1">
         <v>11003</v>
       </c>
-      <c r="S20" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T20" s="43" t="s">
+      <c r="S20" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U20" s="57">
+      <c r="T20" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U20" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4647,21 +4663,21 @@
         <v>5</v>
       </c>
       <c r="W20" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X20" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y20" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z20" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA20" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB20" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4675,44 +4691,44 @@
       <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="60">
         <v>1200102</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13">
         <v>130</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I21" s="10">
         <v>11007</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M21" s="4" t="str">
         <f t="shared" ref="M21:M29" si="10">"在["&amp;P21&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S21</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O21" s="4">
         <v>12001</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="1">
         <v>100700</v>
@@ -4720,13 +4736,13 @@
       <c r="R21" s="1">
         <v>11007</v>
       </c>
-      <c r="S21" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T21" s="43" t="s">
+      <c r="S21" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U21" s="57">
+      <c r="T21" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U21" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4734,21 +4750,21 @@
         <v>1</v>
       </c>
       <c r="W21" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X21" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y21" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z21" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA21" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB21" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4762,44 +4778,44 @@
       <c r="B22" s="12">
         <v>1</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="60">
         <v>1200102</v>
       </c>
       <c r="D22" s="12">
         <v>2</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13">
         <v>130</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I22" s="10">
         <v>11003</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M22" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O22" s="4">
         <v>12001</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q22" s="1">
         <v>100300</v>
@@ -4807,13 +4823,13 @@
       <c r="R22" s="1">
         <v>11003</v>
       </c>
-      <c r="S22" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T22" s="43" t="s">
+      <c r="S22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U22" s="57">
+      <c r="T22" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U22" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4821,21 +4837,21 @@
         <v>2</v>
       </c>
       <c r="W22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X22" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y22" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z22" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB22" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4849,44 +4865,44 @@
       <c r="B23" s="12">
         <v>1</v>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="60">
         <v>1200102</v>
       </c>
       <c r="D23" s="12">
         <v>3</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13">
         <v>130</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I23" s="10">
         <v>11012</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M23" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O23" s="4">
         <v>12001</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q23" s="1">
         <v>101200</v>
@@ -4894,13 +4910,13 @@
       <c r="R23" s="1">
         <v>11012</v>
       </c>
-      <c r="S23" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T23" s="43" t="s">
+      <c r="S23" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U23" s="57">
+      <c r="T23" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U23" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4908,21 +4924,21 @@
         <v>3</v>
       </c>
       <c r="W23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X23" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y23" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z23" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB23" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4936,44 +4952,44 @@
       <c r="B24" s="12">
         <v>1</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="60">
         <v>1200102</v>
       </c>
       <c r="D24" s="12">
         <v>4</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13">
         <v>130</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I24" s="10">
         <v>11014</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M24" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O24" s="4">
         <v>12001</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="1">
         <v>101400</v>
@@ -4981,13 +4997,13 @@
       <c r="R24" s="1">
         <v>11014</v>
       </c>
-      <c r="S24" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T24" s="43" t="s">
+      <c r="S24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U24" s="57">
+      <c r="T24" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U24" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4995,21 +5011,21 @@
         <v>4</v>
       </c>
       <c r="W24" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X24" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y24" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z24" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB24" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5023,44 +5039,44 @@
       <c r="B25" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25" s="60">
         <v>1200102</v>
       </c>
       <c r="D25" s="12">
         <v>5</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13">
         <v>130</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" s="10">
         <v>11003</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M25" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S25</f>
         <v>在任意遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O25" s="4">
         <v>12001</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
@@ -5068,13 +5084,13 @@
       <c r="R25" s="1">
         <v>11003</v>
       </c>
-      <c r="S25" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T25" s="43" t="s">
+      <c r="S25" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U25" s="57">
+      <c r="T25" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U25" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -5082,21 +5098,21 @@
         <v>5</v>
       </c>
       <c r="W25" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X25" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y25" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z25" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA25" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB25" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5117,51 +5133,51 @@
         <v>1</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F26" s="36"/>
       <c r="G26" s="13">
         <v>490</v>
       </c>
-      <c r="H26" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="46">
+      <c r="H26" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="47">
         <v>11007</v>
       </c>
-      <c r="J26" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47" t="s">
-        <v>114</v>
+      <c r="J26" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48" t="s">
+        <v>115</v>
       </c>
       <c r="M26" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N26" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O26" s="36">
         <v>12001</v>
       </c>
-      <c r="P26" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="48">
+      <c r="P26" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q26" s="49">
         <v>100700</v>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="49">
         <v>11007</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T26" s="49" t="s">
+      <c r="S26" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U26" s="50">
+      <c r="T26" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5169,21 +5185,21 @@
         <v>1</v>
       </c>
       <c r="W26" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X26" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y26" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z26" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA26" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB26" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5204,51 +5220,51 @@
         <v>2</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="13">
         <v>490</v>
       </c>
-      <c r="H27" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="46">
+      <c r="H27" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="47">
         <v>11003</v>
       </c>
-      <c r="J27" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47" t="s">
-        <v>118</v>
+      <c r="J27" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48" t="s">
+        <v>119</v>
       </c>
       <c r="M27" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N27" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O27" s="36">
         <v>12001</v>
       </c>
-      <c r="P27" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="48">
+      <c r="P27" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q27" s="49">
         <v>100300</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="49">
         <v>11003</v>
       </c>
-      <c r="S27" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T27" s="49" t="s">
+      <c r="S27" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U27" s="50">
+      <c r="T27" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U27" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5256,21 +5272,21 @@
         <v>2</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X27" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y27" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z27" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB27" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5291,51 +5307,51 @@
         <v>3</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="36"/>
       <c r="G28" s="13">
         <v>490</v>
       </c>
-      <c r="H28" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="46">
+      <c r="H28" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="47">
         <v>11012</v>
       </c>
-      <c r="J28" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47" t="s">
-        <v>120</v>
+      <c r="J28" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48" t="s">
+        <v>121</v>
       </c>
       <c r="M28" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N28" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O28" s="36">
         <v>12001</v>
       </c>
-      <c r="P28" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="48">
+      <c r="P28" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="49">
         <v>101200</v>
       </c>
-      <c r="R28" s="48">
+      <c r="R28" s="49">
         <v>11012</v>
       </c>
-      <c r="S28" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T28" s="49" t="s">
+      <c r="S28" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U28" s="50">
+      <c r="T28" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U28" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5343,21 +5359,21 @@
         <v>3</v>
       </c>
       <c r="W28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X28" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y28" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z28" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB28" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5378,51 +5394,51 @@
         <v>4</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="36"/>
       <c r="G29" s="13">
         <v>490</v>
       </c>
-      <c r="H29" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="46">
+      <c r="H29" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="47">
         <v>11014</v>
       </c>
-      <c r="J29" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47" t="s">
-        <v>122</v>
+      <c r="J29" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48" t="s">
+        <v>123</v>
       </c>
       <c r="M29" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N29" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O29" s="36">
         <v>12001</v>
       </c>
-      <c r="P29" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q29" s="48">
+      <c r="P29" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q29" s="49">
         <v>101400</v>
       </c>
-      <c r="R29" s="48">
+      <c r="R29" s="49">
         <v>11014</v>
       </c>
-      <c r="S29" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T29" s="49" t="s">
+      <c r="S29" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U29" s="50">
+      <c r="T29" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U29" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5430,21 +5446,21 @@
         <v>4</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X29" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y29" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA29" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB29" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5465,51 +5481,51 @@
         <v>5</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="36"/>
       <c r="G30" s="13">
         <v>490</v>
       </c>
-      <c r="H30" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="46">
+      <c r="H30" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="47">
         <v>11003</v>
       </c>
-      <c r="J30" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47" t="s">
-        <v>124</v>
+      <c r="J30" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48" t="s">
+        <v>125</v>
       </c>
       <c r="M30" s="36" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S30</f>
         <v>在任意遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N30" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O30" s="36">
         <v>12001</v>
       </c>
-      <c r="P30" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q30" s="48">
+      <c r="P30" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q30" s="49">
         <v>0</v>
       </c>
-      <c r="R30" s="48">
+      <c r="R30" s="49">
         <v>11003</v>
       </c>
-      <c r="S30" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T30" s="49" t="s">
+      <c r="S30" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U30" s="50">
+      <c r="T30" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U30" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5517,21 +5533,21 @@
         <v>5</v>
       </c>
       <c r="W30" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X30" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y30" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z30" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA30" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB30" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5551,52 +5567,52 @@
       <c r="D31" s="37">
         <v>1</v>
       </c>
-      <c r="E31" s="51" t="s">
-        <v>125</v>
+      <c r="E31" s="52" t="s">
+        <v>126</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="13">
         <v>1210</v>
       </c>
-      <c r="H31" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="52">
+      <c r="H31" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="53">
         <v>11007</v>
       </c>
-      <c r="J31" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53" t="s">
-        <v>126</v>
+      <c r="J31" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54" t="s">
+        <v>127</v>
       </c>
       <c r="M31" s="37" t="str">
         <f t="shared" ref="M31:M34" si="11">"在["&amp;P31&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S31</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O31" s="37">
         <v>12001</v>
       </c>
-      <c r="P31" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q31" s="54">
+      <c r="P31" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q31" s="55">
         <v>100700</v>
       </c>
-      <c r="R31" s="54">
+      <c r="R31" s="55">
         <v>11007</v>
       </c>
-      <c r="S31" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T31" s="55" t="s">
+      <c r="S31" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U31" s="56">
+      <c r="T31" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U31" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5604,21 +5620,21 @@
         <v>1</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X31" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z31" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA31" s="37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB31" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5638,52 +5654,52 @@
       <c r="D32" s="37">
         <v>2</v>
       </c>
-      <c r="E32" s="51" t="s">
-        <v>129</v>
+      <c r="E32" s="52" t="s">
+        <v>130</v>
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="13">
         <v>1210</v>
       </c>
-      <c r="H32" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="52">
+      <c r="H32" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="53">
         <v>11003</v>
       </c>
-      <c r="J32" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53" t="s">
-        <v>130</v>
+      <c r="J32" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54" t="s">
+        <v>131</v>
       </c>
       <c r="M32" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O32" s="37">
         <v>12001</v>
       </c>
-      <c r="P32" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q32" s="54">
+      <c r="P32" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q32" s="55">
         <v>100300</v>
       </c>
-      <c r="R32" s="54">
+      <c r="R32" s="55">
         <v>11003</v>
       </c>
-      <c r="S32" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T32" s="55" t="s">
+      <c r="S32" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U32" s="56">
+      <c r="T32" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U32" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5691,21 +5707,21 @@
         <v>2</v>
       </c>
       <c r="W32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X32" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y32" s="37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z32" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB32" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5725,52 +5741,52 @@
       <c r="D33" s="37">
         <v>3</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>131</v>
+      <c r="E33" s="52" t="s">
+        <v>132</v>
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="13">
         <v>1210</v>
       </c>
-      <c r="H33" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="52">
+      <c r="H33" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="53">
         <v>11012</v>
       </c>
-      <c r="J33" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53" t="s">
-        <v>132</v>
+      <c r="J33" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54" t="s">
+        <v>133</v>
       </c>
       <c r="M33" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O33" s="37">
         <v>12001</v>
       </c>
-      <c r="P33" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="54">
+      <c r="P33" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="55">
         <v>101200</v>
       </c>
-      <c r="R33" s="54">
+      <c r="R33" s="55">
         <v>11012</v>
       </c>
-      <c r="S33" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T33" s="55" t="s">
+      <c r="S33" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U33" s="56">
+      <c r="T33" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U33" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5778,21 +5794,21 @@
         <v>3</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X33" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z33" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB33" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5812,52 +5828,52 @@
       <c r="D34" s="37">
         <v>4</v>
       </c>
-      <c r="E34" s="51" t="s">
-        <v>133</v>
+      <c r="E34" s="52" t="s">
+        <v>134</v>
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="13">
         <v>1210</v>
       </c>
-      <c r="H34" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="52">
+      <c r="H34" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="53">
         <v>11014</v>
       </c>
-      <c r="J34" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53" t="s">
-        <v>134</v>
+      <c r="J34" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54" t="s">
+        <v>135</v>
       </c>
       <c r="M34" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N34" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O34" s="37">
         <v>12001</v>
       </c>
-      <c r="P34" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34" s="54">
+      <c r="P34" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q34" s="55">
         <v>101400</v>
       </c>
-      <c r="R34" s="54">
+      <c r="R34" s="55">
         <v>11014</v>
       </c>
-      <c r="S34" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T34" s="55" t="s">
+      <c r="S34" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U34" s="56">
+      <c r="T34" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U34" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5865,21 +5881,21 @@
         <v>4</v>
       </c>
       <c r="W34" s="37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X34" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y34" s="37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA34" s="37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB34" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5899,52 +5915,52 @@
       <c r="D35" s="37">
         <v>5</v>
       </c>
-      <c r="E35" s="51" t="s">
-        <v>135</v>
+      <c r="E35" s="52" t="s">
+        <v>136</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="13">
         <v>1210</v>
       </c>
-      <c r="H35" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="52">
+      <c r="H35" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="53">
         <v>11003</v>
       </c>
-      <c r="J35" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53" t="s">
-        <v>136</v>
+      <c r="J35" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54" t="s">
+        <v>137</v>
       </c>
       <c r="M35" s="37" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S35</f>
         <v>在任意遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N35" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O35" s="37">
         <v>12001</v>
       </c>
-      <c r="P35" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q35" s="54">
+      <c r="P35" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" s="55">
         <v>0</v>
       </c>
-      <c r="R35" s="54">
+      <c r="R35" s="55">
         <v>11003</v>
       </c>
-      <c r="S35" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T35" s="55" t="s">
+      <c r="S35" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U35" s="56">
+      <c r="T35" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U35" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5952,21 +5968,21 @@
         <v>5</v>
       </c>
       <c r="W35" s="37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X35" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y35" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z35" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA35" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB35" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5987,37 +6003,37 @@
         <v>1</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="13">
         <v>120</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I36" s="10">
         <v>11007</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M36" s="4" t="str">
         <f t="shared" ref="M36:M39" si="12">"在["&amp;P36&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S36</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O36" s="4">
         <v>10003</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q36" s="1">
         <v>100700</v>
@@ -6025,13 +6041,13 @@
       <c r="R36" s="1">
         <v>11007</v>
       </c>
-      <c r="S36" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T36" s="43" t="s">
+      <c r="S36" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U36" s="60">
+      <c r="T36" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U36" s="61">
         <f t="shared" ref="U36:U40" si="13">S36*3%/29000*7*2</f>
         <v>120.206896551724</v>
       </c>
@@ -6039,21 +6055,21 @@
         <v>1</v>
       </c>
       <c r="W36" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X36" s="4" t="str">
         <f>"In the ["&amp;W36&amp;"] , total gold coins won have reached  "&amp;S36</f>
         <v>In the [Mahjong Hu] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y36" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z36" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y36&amp;"], tổng số vàng thắng được đạt "&amp;S36</f>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA36" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB36" s="4" t="str">
         <f>"No jogo ["&amp;AA36&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S36</f>
@@ -6074,37 +6090,37 @@
         <v>2</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13">
         <v>120</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I37" s="10">
         <v>11003</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M37" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="4">
         <v>10003</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q37" s="1">
         <v>100300</v>
@@ -6112,13 +6128,13 @@
       <c r="R37" s="1">
         <v>11003</v>
       </c>
-      <c r="S37" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T37" s="43" t="s">
+      <c r="S37" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U37" s="60">
+      <c r="T37" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U37" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6126,21 +6142,21 @@
         <v>2</v>
       </c>
       <c r="W37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X37" s="4" t="str">
         <f t="shared" ref="X37:X55" si="14">"In the ["&amp;W37&amp;"] , total gold coins won have reached  "&amp;S37</f>
         <v>In the [Super Star] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y37" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z37" s="4" t="str">
         <f t="shared" ref="Z37:Z55" si="15">"Trong trò chơi ["&amp;Y37&amp;"], tổng số vàng thắng được đạt "&amp;S37</f>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB37" s="4" t="str">
         <f t="shared" ref="AB37:AB55" si="16">"No jogo ["&amp;AA37&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S37</f>
@@ -6161,37 +6177,37 @@
         <v>3</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="13">
         <v>120</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I38" s="10">
         <v>11012</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M38" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="4">
         <v>10003</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q38" s="1">
         <v>101200</v>
@@ -6199,13 +6215,13 @@
       <c r="R38" s="1">
         <v>11012</v>
       </c>
-      <c r="S38" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T38" s="43" t="s">
+      <c r="S38" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U38" s="60">
+      <c r="T38" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U38" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6213,21 +6229,21 @@
         <v>3</v>
       </c>
       <c r="W38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X38" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y38" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z38" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB38" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6248,37 +6264,37 @@
         <v>4</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="13">
         <v>120</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="10">
         <v>11014</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M39" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="4">
         <v>10003</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="1">
         <v>101400</v>
@@ -6286,13 +6302,13 @@
       <c r="R39" s="1">
         <v>11014</v>
       </c>
-      <c r="S39" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T39" s="43" t="s">
+      <c r="S39" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U39" s="60">
+      <c r="T39" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6300,21 +6316,21 @@
         <v>4</v>
       </c>
       <c r="W39" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X39" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y39" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z39" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA39" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB39" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6335,37 +6351,37 @@
         <v>5</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="13">
         <v>120</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I40" s="10">
         <v>11003</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M40" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S40</f>
         <v>在任意遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O40" s="4">
         <v>10003</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="1">
         <v>0</v>
@@ -6373,13 +6389,13 @@
       <c r="R40" s="1">
         <v>11003</v>
       </c>
-      <c r="S40" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T40" s="43" t="s">
+      <c r="S40" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U40" s="60">
+      <c r="T40" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U40" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6387,21 +6403,21 @@
         <v>5</v>
       </c>
       <c r="W40" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X40" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y40" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z40" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA40" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB40" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6422,37 +6438,37 @@
         <v>1</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="13">
         <v>260</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I41" s="10">
         <v>11007</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M41" s="4" t="str">
         <f t="shared" ref="M41:M44" si="17">"在["&amp;P41&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S41</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="4">
         <v>10003</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q41" s="1">
         <v>100700</v>
@@ -6460,13 +6476,13 @@
       <c r="R41" s="1">
         <v>11007</v>
       </c>
-      <c r="S41" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T41" s="43" t="s">
+      <c r="S41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U41" s="60">
+      <c r="T41" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U41" s="61">
         <f t="shared" ref="U41:U45" si="18">S41*3%/29000*7*2</f>
         <v>260.689655172414</v>
       </c>
@@ -6474,21 +6490,21 @@
         <v>1</v>
       </c>
       <c r="W41" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X41" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y41" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z41" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA41" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB41" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6509,37 +6525,37 @@
         <v>2</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
         <v>260</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>11003</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M42" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42" s="4">
         <v>10003</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q42" s="1">
         <v>100300</v>
@@ -6547,13 +6563,13 @@
       <c r="R42" s="1">
         <v>11003</v>
       </c>
-      <c r="S42" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T42" s="43" t="s">
+      <c r="S42" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U42" s="60">
+      <c r="T42" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U42" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6561,21 +6577,21 @@
         <v>2</v>
       </c>
       <c r="W42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X42" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y42" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z42" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB42" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6596,37 +6612,37 @@
         <v>3</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
         <v>260</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>11012</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M43" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O43" s="4">
         <v>10003</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q43" s="1">
         <v>101200</v>
@@ -6634,13 +6650,13 @@
       <c r="R43" s="1">
         <v>11012</v>
       </c>
-      <c r="S43" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T43" s="43" t="s">
+      <c r="S43" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U43" s="60">
+      <c r="T43" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U43" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6648,21 +6664,21 @@
         <v>3</v>
       </c>
       <c r="W43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X43" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y43" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z43" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB43" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6683,37 +6699,37 @@
         <v>4</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
         <v>260</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>11014</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M44" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44" s="4">
         <v>10003</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="1">
         <v>101400</v>
@@ -6721,13 +6737,13 @@
       <c r="R44" s="1">
         <v>11014</v>
       </c>
-      <c r="S44" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T44" s="43" t="s">
+      <c r="S44" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U44" s="60">
+      <c r="T44" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U44" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6735,21 +6751,21 @@
         <v>4</v>
       </c>
       <c r="W44" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X44" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y44" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z44" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA44" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB44" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6770,37 +6786,37 @@
         <v>5</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
         <v>260</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>11003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M45" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S45</f>
         <v>在任意遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O45" s="4">
         <v>10003</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="1">
         <v>0</v>
@@ -6808,13 +6824,13 @@
       <c r="R45" s="1">
         <v>11003</v>
       </c>
-      <c r="S45" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T45" s="43" t="s">
+      <c r="S45" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U45" s="60">
+      <c r="T45" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U45" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6822,21 +6838,21 @@
         <v>5</v>
       </c>
       <c r="W45" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X45" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y45" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z45" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA45" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB45" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6857,37 +6873,37 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
         <v>350</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>11007</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M46" s="4" t="str">
         <f t="shared" ref="M46:M49" si="19">"在["&amp;P46&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S46</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O46" s="4">
         <v>10003</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q46" s="1">
         <v>100700</v>
@@ -6895,13 +6911,13 @@
       <c r="R46" s="1">
         <v>11007</v>
       </c>
-      <c r="S46" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T46" s="43" t="s">
+      <c r="S46" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U46" s="60">
+      <c r="T46" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U46" s="61">
         <f t="shared" ref="U46:U55" si="20">S46*3%/29000*7*2</f>
         <v>350.48275862069</v>
       </c>
@@ -6909,21 +6925,21 @@
         <v>1</v>
       </c>
       <c r="W46" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X46" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z46" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA46" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB46" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6944,37 +6960,37 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
         <v>350</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>11003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M47" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O47" s="4">
         <v>10003</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q47" s="1">
         <v>100300</v>
@@ -6982,13 +6998,13 @@
       <c r="R47" s="1">
         <v>11003</v>
       </c>
-      <c r="S47" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" s="43" t="s">
+      <c r="S47" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U47" s="60">
+      <c r="T47" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U47" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -6996,21 +7012,21 @@
         <v>2</v>
       </c>
       <c r="W47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X47" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y47" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z47" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB47" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7031,37 +7047,37 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
         <v>350</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>11012</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M48" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O48" s="4">
         <v>10003</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q48" s="1">
         <v>101200</v>
@@ -7069,13 +7085,13 @@
       <c r="R48" s="1">
         <v>11012</v>
       </c>
-      <c r="S48" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T48" s="43" t="s">
+      <c r="S48" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U48" s="60">
+      <c r="T48" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U48" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7083,21 +7099,21 @@
         <v>3</v>
       </c>
       <c r="W48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X48" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y48" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z48" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB48" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7118,37 +7134,37 @@
         <v>4</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="13">
         <v>350</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I49" s="10">
         <v>11014</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M49" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O49" s="4">
         <v>10003</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="1">
         <v>101400</v>
@@ -7156,13 +7172,13 @@
       <c r="R49" s="1">
         <v>11014</v>
       </c>
-      <c r="S49" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T49" s="43" t="s">
+      <c r="S49" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U49" s="60">
+      <c r="T49" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U49" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7170,21 +7186,21 @@
         <v>4</v>
       </c>
       <c r="W49" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X49" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y49" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z49" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA49" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB49" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7205,37 +7221,37 @@
         <v>5</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13">
         <v>350</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I50" s="10">
         <v>11003</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M50" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S50</f>
         <v>在任意遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O50" s="4">
         <v>10003</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q50" s="1">
         <v>0</v>
@@ -7243,13 +7259,13 @@
       <c r="R50" s="1">
         <v>11003</v>
       </c>
-      <c r="S50" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T50" s="43" t="s">
+      <c r="S50" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U50" s="60">
+      <c r="T50" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U50" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7257,21 +7273,21 @@
         <v>5</v>
       </c>
       <c r="W50" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X50" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y50" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z50" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA50" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB50" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7292,51 +7308,51 @@
         <v>1</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F51" s="36"/>
       <c r="G51" s="13">
         <v>1200</v>
       </c>
-      <c r="H51" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="46">
+      <c r="H51" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="47">
         <v>11007</v>
       </c>
-      <c r="J51" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47" t="s">
-        <v>173</v>
+      <c r="J51" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48" t="s">
+        <v>174</v>
       </c>
       <c r="M51" s="36" t="str">
         <f t="shared" ref="M51:M54" si="21">"在["&amp;P51&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S51</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N51" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51" s="36">
         <v>10003</v>
       </c>
-      <c r="P51" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q51" s="48">
+      <c r="P51" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q51" s="49">
         <v>100700</v>
       </c>
-      <c r="R51" s="48">
+      <c r="R51" s="49">
         <v>11007</v>
       </c>
-      <c r="S51" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T51" s="49" t="s">
+      <c r="S51" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U51" s="50">
+      <c r="T51" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U51" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7344,21 +7360,21 @@
         <v>1</v>
       </c>
       <c r="W51" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X51" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y51" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z51" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA51" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB51" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7379,51 +7395,51 @@
         <v>2</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="13">
         <v>1200</v>
       </c>
-      <c r="H52" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="46">
+      <c r="H52" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="47">
         <v>11003</v>
       </c>
-      <c r="J52" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K52" s="47"/>
-      <c r="L52" s="47" t="s">
-        <v>177</v>
+      <c r="J52" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52" s="48"/>
+      <c r="L52" s="48" t="s">
+        <v>178</v>
       </c>
       <c r="M52" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N52" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O52" s="36">
         <v>10003</v>
       </c>
-      <c r="P52" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q52" s="48">
+      <c r="P52" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q52" s="49">
         <v>100300</v>
       </c>
-      <c r="R52" s="48">
+      <c r="R52" s="49">
         <v>11003</v>
       </c>
-      <c r="S52" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T52" s="49" t="s">
+      <c r="S52" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U52" s="50">
+      <c r="T52" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U52" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7431,21 +7447,21 @@
         <v>2</v>
       </c>
       <c r="W52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X52" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y52" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z52" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB52" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7466,51 +7482,51 @@
         <v>3</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F53" s="36"/>
       <c r="G53" s="13">
         <v>1200</v>
       </c>
-      <c r="H53" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="46">
+      <c r="H53" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="47">
         <v>11012</v>
       </c>
-      <c r="J53" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47" t="s">
-        <v>179</v>
+      <c r="J53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K53" s="48"/>
+      <c r="L53" s="48" t="s">
+        <v>180</v>
       </c>
       <c r="M53" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N53" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O53" s="36">
         <v>10003</v>
       </c>
-      <c r="P53" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q53" s="48">
+      <c r="P53" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="49">
         <v>101200</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="49">
         <v>11012</v>
       </c>
-      <c r="S53" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T53" s="49" t="s">
+      <c r="S53" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U53" s="50">
+      <c r="T53" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U53" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7518,21 +7534,21 @@
         <v>3</v>
       </c>
       <c r="W53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X53" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y53" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z53" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB53" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7553,51 +7569,51 @@
         <v>4</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="13">
         <v>1200</v>
       </c>
-      <c r="H54" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="46">
+      <c r="H54" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="47">
         <v>11014</v>
       </c>
-      <c r="J54" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47" t="s">
-        <v>181</v>
+      <c r="J54" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="48"/>
+      <c r="L54" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="M54" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N54" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O54" s="36">
         <v>10003</v>
       </c>
-      <c r="P54" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q54" s="48">
+      <c r="P54" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q54" s="49">
         <v>101400</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="49">
         <v>11014</v>
       </c>
-      <c r="S54" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T54" s="49" t="s">
+      <c r="S54" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U54" s="50">
+      <c r="T54" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U54" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7605,21 +7621,21 @@
         <v>4</v>
       </c>
       <c r="W54" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X54" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y54" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z54" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA54" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB54" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7640,51 +7656,51 @@
         <v>5</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="13">
         <v>1200</v>
       </c>
-      <c r="H55" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="46">
+      <c r="H55" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="47">
         <v>11003</v>
       </c>
-      <c r="J55" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="K55" s="47"/>
-      <c r="L55" s="47" t="s">
-        <v>183</v>
+      <c r="J55" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="48"/>
+      <c r="L55" s="48" t="s">
+        <v>184</v>
       </c>
       <c r="M55" s="36" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S55</f>
         <v>在任意遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N55" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O55" s="36">
         <v>10003</v>
       </c>
-      <c r="P55" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q55" s="48">
+      <c r="P55" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q55" s="49">
         <v>0</v>
       </c>
-      <c r="R55" s="48">
+      <c r="R55" s="49">
         <v>11003</v>
       </c>
-      <c r="S55" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T55" s="49" t="s">
+      <c r="S55" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U55" s="50">
+      <c r="T55" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U55" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7692,21 +7708,21 @@
         <v>5</v>
       </c>
       <c r="W55" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X55" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y55" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z55" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA55" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB55" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7727,37 +7743,37 @@
         <v>1</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="13">
         <v>5</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I56" s="10">
         <v>11007</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M56" s="4" t="str">
         <f>"在["&amp;P56&amp;"]電子遊戲中，累積旋轉 "&amp;S56&amp;"次"</f>
         <v>在[麻将胡了]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="4">
         <v>10001</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q56" s="1">
         <v>100700</v>
@@ -7765,11 +7781,11 @@
       <c r="R56" s="1">
         <v>11007</v>
       </c>
-      <c r="S56" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T56" s="43" t="s">
-        <v>187</v>
+      <c r="S56" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T56" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U56" s="4">
         <f t="shared" ref="U56:U60" si="22">S56/100</f>
@@ -7779,21 +7795,21 @@
         <v>1</v>
       </c>
       <c r="W56" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X56" s="4" t="str">
         <f>"In the game ["&amp;W56&amp;"] , "&amp;S56&amp;" spins have been accumulated."</f>
         <v>In the game [Mahjong Hu] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y56" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z56" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y56&amp;"], tích lũy quay "&amp;T56&amp;" lần."</f>
         <v>Trong trò chơi [Mạt chược], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA56" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB56" s="4" t="str">
         <f>"No jogo ["&amp;W56&amp;"], foram acumuladas "&amp;T56&amp;" rodadas."</f>
@@ -7814,37 +7830,37 @@
         <v>2</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="13">
         <v>5</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" s="10">
         <v>11003</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M57" s="4" t="str">
         <f>"在["&amp;P57&amp;"]電子遊戲中，累積旋轉 "&amp;S57&amp;"次"</f>
         <v>在[超级明星]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="4">
         <v>10001</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q57" s="1">
         <v>100300</v>
@@ -7852,11 +7868,11 @@
       <c r="R57" s="1">
         <v>11003</v>
       </c>
-      <c r="S57" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T57" s="43" t="s">
-        <v>187</v>
+      <c r="S57" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T57" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U57" s="4">
         <f t="shared" si="22"/>
@@ -7866,21 +7882,21 @@
         <v>2</v>
       </c>
       <c r="W57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X57" s="4" t="str">
         <f>"In the game ["&amp;W57&amp;"] , "&amp;S57&amp;" spins have been accumulated."</f>
         <v>In the game [Super Star] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y57" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z57" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y57&amp;"], tích lũy quay "&amp;T57&amp;" lần."</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB57" s="4" t="str">
         <f>"No jogo ["&amp;W57&amp;"], foram acumuladas "&amp;T57&amp;" rodadas."</f>
@@ -7901,37 +7917,37 @@
         <v>3</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="13">
         <v>5</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I58" s="10">
         <v>11012</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M58" s="4" t="str">
         <f>"在["&amp;P58&amp;"]電子遊戲中，累積旋轉 "&amp;S58&amp;"次"</f>
         <v>在[财神]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O58" s="4">
         <v>10001</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q58" s="1">
         <v>101200</v>
@@ -7939,11 +7955,11 @@
       <c r="R58" s="1">
         <v>11012</v>
       </c>
-      <c r="S58" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T58" s="43" t="s">
-        <v>187</v>
+      <c r="S58" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T58" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U58" s="4">
         <f t="shared" si="22"/>
@@ -7953,21 +7969,21 @@
         <v>3</v>
       </c>
       <c r="W58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X58" s="4" t="str">
         <f>"In the game ["&amp;W58&amp;"] , "&amp;S58&amp;" spins have been accumulated."</f>
         <v>In the game [God of Wealth] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y58" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z58" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y58&amp;"], tích lũy quay "&amp;T58&amp;" lần."</f>
         <v>Trong trò chơi [Thần Tài], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB58" s="4" t="str">
         <f>"No jogo ["&amp;W58&amp;"], foram acumuladas "&amp;T58&amp;" rodadas."</f>
@@ -7988,37 +8004,37 @@
         <v>4</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>11014</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M59" s="4" t="str">
         <f>"在["&amp;P59&amp;"]電子遊戲中，累積旋轉 "&amp;S59&amp;"次"</f>
         <v>在[埃及艳后]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O59" s="4">
         <v>10001</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q59" s="1">
         <v>101400</v>
@@ -8026,11 +8042,11 @@
       <c r="R59" s="1">
         <v>11014</v>
       </c>
-      <c r="S59" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T59" s="43" t="s">
-        <v>187</v>
+      <c r="S59" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T59" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U59" s="4">
         <f t="shared" si="22"/>
@@ -8040,21 +8056,21 @@
         <v>4</v>
       </c>
       <c r="W59" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X59" s="4" t="str">
         <f>"In the game ["&amp;W59&amp;"] , "&amp;S59&amp;" spins have been accumulated."</f>
         <v>In the game [Cleopatra] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y59" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z59" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y59&amp;"], tích lũy quay "&amp;T59&amp;" lần."</f>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA59" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB59" s="4" t="str">
         <f>"No jogo ["&amp;W59&amp;"], foram acumuladas "&amp;T59&amp;" rodadas."</f>
@@ -8075,31 +8091,31 @@
         <v>5</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>5</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>11003</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M60" s="4" t="str">
         <f>"在任意電子遊戲中，累積旋轉 "&amp;S60&amp;"次"</f>
         <v>在任意電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="4">
         <v>10001</v>
@@ -8111,11 +8127,11 @@
       <c r="R60" s="1">
         <v>11003</v>
       </c>
-      <c r="S60" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T60" s="43" t="s">
-        <v>187</v>
+      <c r="S60" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T60" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U60" s="4">
         <f t="shared" si="22"/>
@@ -8125,21 +8141,21 @@
         <v>5</v>
       </c>
       <c r="W60" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X60" s="4" t="str">
         <f>"In the game ["&amp;W60&amp;"] , "&amp;S60&amp;" spins have been accumulated."</f>
         <v>In the game [any game] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y60" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z60" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y60&amp;"], tích lũy quay "&amp;T60&amp;" lần."</f>
         <v>Trong trò chơi [bất kỳ], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA60" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB60" s="4" t="str">
         <f>"No jogo ["&amp;W60&amp;"], foram acumuladas "&amp;T60&amp;" rodadas."</f>
@@ -8181,16 +8197,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J5" s="19">
         <v>502</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -8201,32 +8217,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -8234,37 +8250,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F7" s="18">
         <v>100100</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J7" s="18">
         <v>2</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N7" s="18">
         <v>1022501</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -8272,37 +8288,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="18">
         <v>100300</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J8" s="18">
         <v>3</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N8" s="18">
         <v>1022502</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -8310,37 +8326,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" s="18">
         <v>100700</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J9" s="18">
         <v>4</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N9" s="18">
         <v>1010301</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -8348,37 +8364,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="18">
         <v>101200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="18">
         <v>5</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N10" s="18">
         <v>1010302</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -8386,37 +8402,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F11" s="18">
         <v>101400</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J11" s="18">
         <v>6</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N11" s="18">
         <v>1010303</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -8424,37 +8440,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="18">
         <v>200100</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="25">
         <v>12</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N12" s="18">
         <v>1010311</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -8462,19 +8478,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13" s="18">
         <v>200101</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -8483,10 +8499,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -8494,19 +8510,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F14" s="18">
         <v>200300</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -8515,10 +8531,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -8526,28 +8542,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" s="18">
         <v>200400</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N15" s="18">
         <v>1010314</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -8555,28 +8571,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F16" s="18">
         <v>200500</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N16" s="18">
         <v>1010315</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -8584,19 +8600,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F17" s="18">
         <v>200600</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -8604,19 +8620,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F18" s="18">
         <v>200700</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -8624,22 +8640,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="18">
         <v>200800</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -8647,28 +8663,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F20" s="18">
         <v>200900</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -8676,28 +8692,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F21" s="18">
         <v>201000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N21" s="18">
         <v>1022501</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -8705,28 +8721,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F22" s="18">
         <v>300100</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N22" s="18">
         <v>1022502</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -8734,19 +8750,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N23" s="18">
         <v>1980000</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -8754,10 +8770,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -8765,10 +8781,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -8776,10 +8792,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -8787,10 +8803,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -8798,10 +8814,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -8809,10 +8825,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -8820,10 +8836,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -8831,10 +8847,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -8842,10 +8858,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -8853,10 +8869,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:22">
@@ -8871,7 +8887,7 @@
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28" t="s">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>4</v>
@@ -8898,19 +8914,19 @@
         <v>11</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:22">
@@ -8925,25 +8941,25 @@
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L39" s="33" t="s">
         <v>13</v>
@@ -8951,38 +8967,38 @@
     </row>
     <row r="40" s="3" customFormat="1" spans="1:22">
       <c r="A40" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L40" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:22">
@@ -9014,36 +9030,36 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
         <v>3</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>3002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
         <v>70008</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O42" s="4">
         <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -9079,36 +9095,36 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
         <v>8</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>3002</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O43" s="4">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>0.25</v>
@@ -9144,36 +9160,36 @@
         <v>2</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
         <v>25</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>3002</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O44" s="4">
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>0.25</v>
@@ -9208,30 +9224,30 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
         <v>20</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>2003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O45" s="4">
         <v>2</v>
@@ -9270,30 +9286,30 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
         <v>1</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>2003</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -9332,30 +9348,30 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
         <v>5</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>2003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -9394,30 +9410,30 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
         <v>10</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>2003</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O48" s="4">
         <v>1</v>
@@ -9461,7 +9477,7 @@
         <v>70001</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -9471,7 +9487,7 @@
         <v>70002</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -9481,7 +9497,7 @@
         <v>70003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -9491,7 +9507,7 @@
         <v>70004</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -9501,10 +9517,10 @@
         <v>70005</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L5" s="10">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9516,10 +9532,10 @@
         <v>70006</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L6" s="10">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9531,10 +9547,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>317</v>
       </c>
       <c r="L7" s="10">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9546,10 +9562,10 @@
         <v>70008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L8" s="10">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9561,10 +9577,10 @@
         <v>70009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" s="10">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9576,10 +9592,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L10" s="10">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9591,10 +9607,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L11" s="10">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9606,10 +9622,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L12" s="10">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9621,10 +9637,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L13" s="10">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9636,10 +9652,10 @@
         <v>70104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" s="10">
         <f>_xlfn.XLOOKUP(K14,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9651,10 +9667,10 @@
         <v>70301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="10">
         <f>_xlfn.XLOOKUP(K15,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9666,10 +9682,10 @@
         <v>70302</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L16" s="10">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9681,10 +9697,10 @@
         <v>70303</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L17" s="10">
         <f>_xlfn.XLOOKUP(K17,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9696,10 +9712,10 @@
         <v>70304</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L18" s="10">
         <f>_xlfn.XLOOKUP(K18,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9711,10 +9727,10 @@
         <v>70305</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L19" s="10">
         <f>_xlfn.XLOOKUP(K19,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9726,10 +9742,10 @@
         <v>70306</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L20" s="10">
         <f>_xlfn.XLOOKUP(K20,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9741,10 +9757,10 @@
         <v>70307</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L21" s="10">
         <f>_xlfn.XLOOKUP(K21,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9756,10 +9772,10 @@
         <v>70308</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L22" s="10">
         <f>_xlfn.XLOOKUP(K22,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9771,10 +9787,10 @@
         <v>70309</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L23" s="10">
         <f>_xlfn.XLOOKUP(K23,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9786,10 +9802,10 @@
         <v>70310</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L24" s="10">
         <f>_xlfn.XLOOKUP(K24,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9801,10 +9817,10 @@
         <v>70311</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L25" s="10">
         <f>_xlfn.XLOOKUP(K25,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9816,10 +9832,10 @@
         <v>70312</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L26" s="10">
         <f>_xlfn.XLOOKUP(K26,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9831,10 +9847,10 @@
         <v>70381</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L27" s="10">
         <f>_xlfn.XLOOKUP(K27,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9846,10 +9862,10 @@
         <v>70382</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L28" s="10">
         <f>_xlfn.XLOOKUP(K28,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9861,10 +9877,10 @@
         <v>70383</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L29" s="10">
         <f>_xlfn.XLOOKUP(K29,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9876,10 +9892,10 @@
         <v>70391</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L30" s="10">
         <f>_xlfn.XLOOKUP(K30,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9891,10 +9907,10 @@
         <v>70392</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L31" s="10">
         <f>_xlfn.XLOOKUP(K31,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9906,10 +9922,10 @@
         <v>70393</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L32" s="10">
         <f>_xlfn.XLOOKUP(K32,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9921,10 +9937,10 @@
         <v>71101</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L33" s="10">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9936,10 +9952,10 @@
         <v>71102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L34" s="10">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9951,10 +9967,10 @@
         <v>71103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L35" s="10">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9966,10 +9982,10 @@
         <v>71201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L36" s="10">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9981,10 +9997,10 @@
         <v>71202</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L37" s="10">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9996,10 +10012,10 @@
         <v>72011</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L38" s="10">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10011,10 +10027,10 @@
         <v>72012</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L39" s="10">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10026,10 +10042,10 @@
         <v>72101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L40" s="10">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10041,10 +10057,10 @@
         <v>72102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L41" s="10">
         <f>_xlfn.XLOOKUP(K41,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10053,7 +10069,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="K42" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L42" s="10">
         <f>_xlfn.XLOOKUP(K42,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10062,7 +10078,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="K43" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L43" s="10">
         <f>_xlfn.XLOOKUP(K43,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10071,7 +10087,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="K44" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L44" s="10">
         <f>_xlfn.XLOOKUP(K44,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10080,7 +10096,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="K45" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L45" s="10">
         <f>_xlfn.XLOOKUP(K45,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10172,30 +10188,30 @@
         <v>1</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>2001</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8">
         <v>70007</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
@@ -10231,30 +10247,30 @@
         <v>1</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>10</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>2001</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="O60" s="3">
         <v>7000</v>
@@ -10292,30 +10308,30 @@
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13">
         <v>100</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I61" s="10">
         <v>2001</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O61" s="3">
         <v>70000</v>
@@ -10353,30 +10369,30 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="13">
         <v>1000</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I62" s="10">
         <v>2001</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O62" s="3">
         <v>700000</v>
@@ -10413,29 +10429,29 @@
         <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="15">
         <v>10</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I63" s="11">
         <v>2002</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L63" s="16">
         <v>70007</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P63" s="4"/>
     </row>
@@ -10454,29 +10470,29 @@
         <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F65" s="14"/>
       <c r="G65" s="15">
         <v>20</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I65" s="11">
         <v>1001</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L65" s="16">
         <v>70001</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V65" s="4">
         <f>ROUND(MAX(S65/100,T65/100,U65),0)</f>
@@ -10498,29 +10514,29 @@
         <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="15">
         <v>100</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I66" s="11">
         <v>2001</v>
       </c>
       <c r="J66" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="K66" s="16" t="s">
         <v>361</v>
-      </c>
-      <c r="K66" s="16" t="s">
-        <v>359</v>
       </c>
       <c r="L66" s="16">
         <v>70002</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:22">
@@ -10538,29 +10554,29 @@
         <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="15">
         <v>10</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I67" s="11">
         <v>2002</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L67" s="16">
         <v>70003</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:22">
@@ -10578,29 +10594,29 @@
         <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F68" s="14"/>
       <c r="G68" s="15">
         <v>40</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I68" s="11">
         <v>2003</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L68" s="16">
         <v>70004</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:22">
@@ -10618,29 +10634,29 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="15">
         <v>10</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I69" s="11">
         <v>1001</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L69" s="16">
         <v>70005</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N69" s="17"/>
     </row>
@@ -10659,29 +10675,29 @@
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="15">
         <v>20</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I70" s="11">
         <v>2001</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L70" s="16">
         <v>70006</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N70" s="17"/>
     </row>
@@ -10700,29 +10716,29 @@
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="15">
         <v>5</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I71" s="11">
         <v>2003</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L71" s="16">
         <v>70008</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N71" s="17"/>
     </row>
@@ -10741,29 +10757,29 @@
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="15">
         <v>1</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I72" s="11">
         <v>1001</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L72" s="16">
         <v>70009</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N72" s="17"/>
     </row>
@@ -10782,29 +10798,29 @@
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="15">
         <v>5</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I73" s="11">
         <v>2001</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L73" s="16">
         <v>70010</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -10831,384 +10847,384 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1">
         <v>100100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1">
         <v>100300</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>100700</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1">
         <v>101200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="1">
         <v>101400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B7" s="1">
         <v>101700</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B8" s="1">
         <v>102100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B9" s="1">
         <v>102200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1">
         <v>102300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1">
         <v>102400</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1">
         <v>102500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B13" s="1">
         <v>200100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B14" s="1">
         <v>200101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B15" s="1">
         <v>200300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B16" s="1">
         <v>200400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B17" s="1">
         <v>200500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B18" s="1">
         <v>200600</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B19" s="1">
         <v>200700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B20" s="1">
         <v>200800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B21" s="1">
         <v>200900</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B22" s="1">
         <v>300100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B23" s="1">
         <v>300200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B24" s="1">
         <v>500000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1">
         <v>500001</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B26" s="1">
         <v>500002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B27" s="1">
         <v>500003</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B28" s="1">
         <v>500004</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B29" s="1">
         <v>500005</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1">
         <v>500006</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1">
         <v>500007</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1">
         <v>600000</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="1">
         <v>600001</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B34" s="1">
         <v>600002</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1">
         <v>600003</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>29</v>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>29</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="13">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>29</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="13">
-        <v>950</v>
+        <v>843</v>
       </c>
       <c r="H9" s="46" t="s">
         <v>29</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="13">
-        <v>1440</v>
+        <v>1278</v>
       </c>
       <c r="H10" s="52" t="s">
         <v>29</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>29</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>29</v>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>29</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>29</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>29</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>29</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>29</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>29</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>29</v>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>29</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>29</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>29</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>29</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>29</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>29</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F26" s="36"/>
       <c r="G26" s="13">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="H26" s="46" t="s">
         <v>29</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="13">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="H27" s="46" t="s">
         <v>29</v>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="F28" s="36"/>
       <c r="G28" s="13">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="H28" s="46" t="s">
         <v>29</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="F29" s="36"/>
       <c r="G29" s="13">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="H29" s="46" t="s">
         <v>29</v>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="F30" s="36"/>
       <c r="G30" s="13">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="H30" s="46" t="s">
         <v>29</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="13">
-        <v>1210</v>
+        <v>1073</v>
       </c>
       <c r="H31" s="52" t="s">
         <v>29</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="13">
-        <v>1210</v>
+        <v>1073</v>
       </c>
       <c r="H32" s="52" t="s">
         <v>29</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="13">
-        <v>1210</v>
+        <v>1073</v>
       </c>
       <c r="H33" s="52" t="s">
         <v>29</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="13">
-        <v>1210</v>
+        <v>1073</v>
       </c>
       <c r="H34" s="52" t="s">
         <v>29</v>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="13">
-        <v>1210</v>
+        <v>1073</v>
       </c>
       <c r="H35" s="52" t="s">
         <v>29</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>29</v>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>29</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>29</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>29</v>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>29</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>29</v>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>29</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>29</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>29</v>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>29</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>29</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>29</v>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>29</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>29</v>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>29</v>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="F51" s="36"/>
       <c r="G51" s="13">
-        <v>1200</v>
+        <v>1060</v>
       </c>
       <c r="H51" s="46" t="s">
         <v>29</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="13">
-        <v>1200</v>
+        <v>1060</v>
       </c>
       <c r="H52" s="46" t="s">
         <v>29</v>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="F53" s="36"/>
       <c r="G53" s="13">
-        <v>1200</v>
+        <v>1060</v>
       </c>
       <c r="H53" s="46" t="s">
         <v>29</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="13">
-        <v>1200</v>
+        <v>1060</v>
       </c>
       <c r="H54" s="46" t="s">
         <v>29</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="13">
-        <v>1200</v>
+        <v>1060</v>
       </c>
       <c r="H55" s="46" t="s">
         <v>29</v>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -101,7 +101,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置 condition.xlsx 文件中的ID</t>
+配置 condition.xlsx 文件中的ID
+充值类型的单位是分，比如要求充值9.99美元，需要填 999</t>
         </r>
       </text>
     </comment>
@@ -459,7 +460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="425">
   <si>
     <t>任务ID</t>
   </si>
@@ -470,7 +471,7 @@
     <t>任务组</t>
   </si>
   <si>
-    <t>任务条件</t>
+    <t>任务条件（充值货币单位是分，服务端会除以100）</t>
   </si>
   <si>
     <t>道具奖励</t>
@@ -503,6 +504,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
@@ -542,7 +546,7 @@
     <t>language</t>
   </si>
   <si>
-    <t>11002_300000_0</t>
+    <t>11002_30000000_0</t>
   </si>
   <si>
     <t>itemicon_1022504.png</t>
@@ -563,7 +567,7 @@
     <t>300000</t>
   </si>
   <si>
-    <t>11002_1400000_0</t>
+    <t>11002_140000000_0</t>
   </si>
   <si>
     <t>70002</t>
@@ -575,7 +579,7 @@
     <t>1400000</t>
   </si>
   <si>
-    <t>11002_8300000_0</t>
+    <t>11002_830000000_0</t>
   </si>
   <si>
     <t>70003</t>
@@ -587,7 +591,7 @@
     <t>8300000</t>
   </si>
   <si>
-    <t>11002_32000000_0</t>
+    <t>11002_3200000000_0</t>
   </si>
   <si>
     <t>70004</t>
@@ -599,7 +603,7 @@
     <t>32000000</t>
   </si>
   <si>
-    <t>11002_132000000_0</t>
+    <t>11002_13200000000_0</t>
   </si>
   <si>
     <t>70005</t>
@@ -611,7 +615,7 @@
     <t>132000000</t>
   </si>
   <si>
-    <t>11002_200000000_0</t>
+    <t>11002_20000000000_0</t>
   </si>
   <si>
     <t>70006</t>
@@ -1349,6 +1353,9 @@
   </si>
   <si>
     <t>德州-房间</t>
+  </si>
+  <si>
+    <t>任务条件</t>
   </si>
   <si>
     <t>价值转化</t>
@@ -1980,7 +1987,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2056,6 +2063,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2378,7 +2391,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2402,16 +2415,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2420,89 +2433,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2632,6 +2645,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2680,7 +2696,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -3269,22 +3285,22 @@
         <v>14</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>13</v>
@@ -3292,38 +3308,38 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="28"/>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -3353,32 +3369,32 @@
       <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>27</v>
+      <c r="E5" s="43" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="10">
         <v>2003</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="4" t="str">
         <f t="shared" ref="M5:M10" si="0">"累積充值達到 "&amp;S5&amp;" ₫"</f>
         <v>累積充值達到 300,000 ₫</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1">
         <v>11002</v>
@@ -3388,13 +3404,13 @@
       <c r="R5" s="1">
         <v>2003</v>
       </c>
-      <c r="S5" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="T5" s="43" t="s">
+      <c r="S5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="44">
+      <c r="T5" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="45">
         <f t="shared" ref="U5:U10" si="1">S5/29000*7*3%</f>
         <v>2.17241379310345</v>
       </c>
@@ -3430,32 +3446,32 @@
       <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>34</v>
+      <c r="E6" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="10">
         <v>2003</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 1,400,000 ₫</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="1">
         <v>11002</v>
@@ -3465,13 +3481,13 @@
       <c r="R6" s="1">
         <v>2003</v>
       </c>
-      <c r="S6" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="43" t="s">
+      <c r="S6" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="44">
+      <c r="T6" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="U6" s="45">
         <f t="shared" si="1"/>
         <v>10.1379310344828</v>
       </c>
@@ -3507,32 +3523,32 @@
       <c r="D7" s="12">
         <v>1</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>38</v>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10">
         <v>2003</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 8,300,000 ₫</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" s="1">
         <v>11002</v>
@@ -3542,13 +3558,13 @@
       <c r="R7" s="1">
         <v>2003</v>
       </c>
-      <c r="S7" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T7" s="43" t="s">
+      <c r="S7" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="44">
+      <c r="T7" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" s="45">
         <f t="shared" si="1"/>
         <v>60.1034482758621</v>
       </c>
@@ -3584,32 +3600,32 @@
       <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>42</v>
+      <c r="E8" s="43" t="s">
+        <v>43</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="13">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="10">
         <v>2003</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 32,000,000 ₫</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O8" s="1">
         <v>11002</v>
@@ -3619,13 +3635,13 @@
       <c r="R8" s="1">
         <v>2003</v>
       </c>
-      <c r="S8" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="43" t="s">
+      <c r="S8" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="44">
+      <c r="T8" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="45">
         <f t="shared" si="1"/>
         <v>231.724137931035</v>
       </c>
@@ -3661,48 +3677,48 @@
       <c r="D9" s="36">
         <v>1</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>46</v>
+      <c r="E9" s="43" t="s">
+        <v>47</v>
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="13">
-        <v>950</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="46">
+        <v>843</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="47">
         <v>2003</v>
       </c>
-      <c r="J9" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="47"/>
+      <c r="J9" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="48"/>
       <c r="L9" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" s="36" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 132,000,000 ₫</v>
       </c>
-      <c r="N9" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="48">
+      <c r="N9" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="49">
         <v>11002</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48">
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49">
         <v>2003</v>
       </c>
-      <c r="S9" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="49" t="s">
+      <c r="S9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="50">
+      <c r="T9" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="51">
         <f t="shared" si="1"/>
         <v>955.862068965517</v>
       </c>
@@ -3736,48 +3752,48 @@
       <c r="D10" s="37">
         <v>1</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>50</v>
+      <c r="E10" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="13">
-        <v>1440</v>
-      </c>
-      <c r="H10" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="52">
+        <v>1278</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="53">
         <v>2003</v>
       </c>
-      <c r="J10" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="53"/>
+      <c r="J10" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="54"/>
       <c r="L10" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M10" s="37" t="str">
         <f t="shared" si="0"/>
         <v>累積充值達到 200,000,000 ₫</v>
       </c>
-      <c r="N10" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="54">
+      <c r="N10" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="55">
         <v>11002</v>
       </c>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54">
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55">
         <v>2003</v>
       </c>
-      <c r="S10" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="T10" s="55" t="s">
+      <c r="S10" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="U10" s="56">
+      <c r="T10" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="U10" s="57">
         <f t="shared" si="1"/>
         <v>1448.27586206897</v>
       </c>
@@ -3812,37 +3828,37 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I11" s="10">
         <v>11007</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M11" s="4" t="str">
         <f t="shared" ref="M11:M14" si="5">"在["&amp;P11&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S11</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O11" s="4">
         <v>12001</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="1">
         <v>100700</v>
@@ -3850,13 +3866,13 @@
       <c r="R11" s="1">
         <v>11007</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T11" s="43" t="s">
+      <c r="S11" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U11" s="57">
+      <c r="T11" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11" s="58">
         <f t="shared" ref="U11:U35" si="6">S11*3%/29000*7</f>
         <v>24.6206896551724</v>
       </c>
@@ -3864,21 +3880,21 @@
         <v>1</v>
       </c>
       <c r="W11" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X11" s="4" t="str">
         <f>"In the ["&amp;W11&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S11</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y11" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z11" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y11&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S11</f>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA11" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB11" s="4" t="str">
         <f>"No videogame ["&amp;AA11&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S11</f>
@@ -3899,37 +3915,37 @@
         <v>2</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="10">
         <v>11003</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M12" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O12" s="4">
         <v>12001</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q12" s="1">
         <v>100300</v>
@@ -3937,13 +3953,13 @@
       <c r="R12" s="1">
         <v>11003</v>
       </c>
-      <c r="S12" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T12" s="43" t="s">
+      <c r="S12" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U12" s="57">
+      <c r="T12" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -3951,21 +3967,21 @@
         <v>2</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X12" s="4" t="str">
         <f>"In the ["&amp;W12&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S12</f>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y12" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z12" s="4" t="str">
         <f t="shared" ref="Z12:Z35" si="7">"Trong trò chơi ["&amp;Y12&amp;"], tích lũy đặt cược hợp lệ tiền vàng đạt "&amp;S12</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA12" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB12" s="4" t="str">
         <f t="shared" ref="AB12:AB35" si="8">"No videogame ["&amp;AA12&amp;"], as apostas válidas acumuladas em Moedas de Ouro atingem "&amp;S12</f>
@@ -3986,37 +4002,37 @@
         <v>3</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="10">
         <v>11012</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M13" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O13" s="4">
         <v>12001</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q13" s="1">
         <v>101200</v>
@@ -4024,13 +4040,13 @@
       <c r="R13" s="1">
         <v>11012</v>
       </c>
-      <c r="S13" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T13" s="43" t="s">
+      <c r="S13" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U13" s="57">
+      <c r="T13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4038,21 +4054,21 @@
         <v>3</v>
       </c>
       <c r="W13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X13" s="4" t="str">
         <f>"In the ["&amp;W13&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S13</f>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y13" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB13" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4073,37 +4089,37 @@
         <v>4</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="10">
         <v>11014</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="4" t="str">
         <f t="shared" si="5"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O14" s="4">
         <v>12001</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="1">
         <v>101400</v>
@@ -4111,13 +4127,13 @@
       <c r="R14" s="1">
         <v>11014</v>
       </c>
-      <c r="S14" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="43" t="s">
+      <c r="S14" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="57">
+      <c r="T14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U14" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4125,21 +4141,21 @@
         <v>4</v>
       </c>
       <c r="W14" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X14" s="4" t="str">
         <f>"In the ["&amp;W14&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S14</f>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y14" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z14" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB14" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4160,37 +4176,37 @@
         <v>5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="10">
         <v>11003</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S15</f>
         <v>在任意遊戲中，金币有效下注累積達到 3,400,000</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O15" s="4">
         <v>12001</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q15" s="1">
         <v>0</v>
@@ -4198,13 +4214,13 @@
       <c r="R15" s="1">
         <v>11003</v>
       </c>
-      <c r="S15" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="T15" s="43" t="s">
+      <c r="S15" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="U15" s="57">
+      <c r="T15" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U15" s="58">
         <f t="shared" si="6"/>
         <v>24.6206896551724</v>
       </c>
@@ -4212,21 +4228,21 @@
         <v>5</v>
       </c>
       <c r="W15" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X15" s="4" t="str">
         <f>"In the ["&amp;W15&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S15</f>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 3,400,000</v>
       </c>
       <c r="Y15" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 3,400,000</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4240,44 +4256,44 @@
       <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="59">
         <v>1200101</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="10">
         <v>11007</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" s="4" t="str">
         <f>"在["&amp;P16&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S16</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O16" s="4">
         <v>12001</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="1">
         <v>100700</v>
@@ -4285,13 +4301,13 @@
       <c r="R16" s="1">
         <v>11007</v>
       </c>
-      <c r="S16" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T16" s="43" t="s">
+      <c r="S16" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U16" s="57">
+      <c r="T16" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4299,21 +4315,21 @@
         <v>1</v>
       </c>
       <c r="W16" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X16" s="4" t="str">
         <f t="shared" ref="X16:X35" si="9">"In the ["&amp;W16&amp;"] video game, the accumulated valid Gold Coin bets reach "&amp;S16</f>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y16" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z16" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA16" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB16" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4327,44 +4343,44 @@
       <c r="B17" s="12">
         <v>1</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="59">
         <v>1200101</v>
       </c>
       <c r="D17" s="12">
         <v>2</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I17" s="10">
         <v>11003</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M17" s="4" t="str">
         <f>"在["&amp;P17&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S17</f>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="4">
         <v>12001</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="1">
         <v>100300</v>
@@ -4372,13 +4388,13 @@
       <c r="R17" s="1">
         <v>11003</v>
       </c>
-      <c r="S17" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T17" s="43" t="s">
+      <c r="S17" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U17" s="57">
+      <c r="T17" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4386,21 +4402,21 @@
         <v>2</v>
       </c>
       <c r="W17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X17" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y17" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z17" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA17" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB17" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4414,44 +4430,44 @@
       <c r="B18" s="12">
         <v>1</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="59">
         <v>1200101</v>
       </c>
       <c r="D18" s="12">
         <v>3</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I18" s="10">
         <v>11012</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M18" s="4" t="str">
         <f>"在["&amp;P18&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S18</f>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O18" s="4">
         <v>12001</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="1">
         <v>101200</v>
@@ -4459,13 +4475,13 @@
       <c r="R18" s="1">
         <v>11012</v>
       </c>
-      <c r="S18" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T18" s="43" t="s">
+      <c r="S18" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U18" s="57">
+      <c r="T18" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4473,21 +4489,21 @@
         <v>3</v>
       </c>
       <c r="W18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X18" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y18" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z18" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA18" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB18" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4501,44 +4517,44 @@
       <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <v>1200101</v>
       </c>
       <c r="D19" s="12">
         <v>4</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="10">
         <v>11014</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M19" s="4" t="str">
         <f>"在["&amp;P19&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S19</f>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O19" s="4">
         <v>12001</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="1">
         <v>101400</v>
@@ -4546,13 +4562,13 @@
       <c r="R19" s="1">
         <v>11014</v>
       </c>
-      <c r="S19" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T19" s="43" t="s">
+      <c r="S19" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U19" s="57">
+      <c r="T19" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4560,21 +4576,21 @@
         <v>4</v>
       </c>
       <c r="W19" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X19" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y19" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z19" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB19" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4588,44 +4604,44 @@
       <c r="B20" s="12">
         <v>1</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="59">
         <v>1200101</v>
       </c>
       <c r="D20" s="12">
         <v>5</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="10">
         <v>11003</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M20" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S20</f>
         <v>在任意遊戲中，金币有效下注累積達到 8,300,000</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O20" s="4">
         <v>12001</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -4633,13 +4649,13 @@
       <c r="R20" s="1">
         <v>11003</v>
       </c>
-      <c r="S20" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T20" s="43" t="s">
+      <c r="S20" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U20" s="57">
+      <c r="T20" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U20" s="58">
         <f t="shared" si="6"/>
         <v>60.1034482758621</v>
       </c>
@@ -4647,21 +4663,21 @@
         <v>5</v>
       </c>
       <c r="W20" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X20" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 8,300,000</v>
       </c>
       <c r="Y20" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z20" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 8,300,000</v>
       </c>
       <c r="AA20" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB20" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4675,44 +4691,44 @@
       <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="60">
         <v>1200102</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I21" s="10">
         <v>11007</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M21" s="4" t="str">
         <f t="shared" ref="M21:M29" si="10">"在["&amp;P21&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S21</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O21" s="4">
         <v>12001</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="1">
         <v>100700</v>
@@ -4720,13 +4736,13 @@
       <c r="R21" s="1">
         <v>11007</v>
       </c>
-      <c r="S21" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T21" s="43" t="s">
+      <c r="S21" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U21" s="57">
+      <c r="T21" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U21" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4734,21 +4750,21 @@
         <v>1</v>
       </c>
       <c r="W21" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X21" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y21" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z21" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA21" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB21" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4762,44 +4778,44 @@
       <c r="B22" s="12">
         <v>1</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="60">
         <v>1200102</v>
       </c>
       <c r="D22" s="12">
         <v>2</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I22" s="10">
         <v>11003</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M22" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O22" s="4">
         <v>12001</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q22" s="1">
         <v>100300</v>
@@ -4807,13 +4823,13 @@
       <c r="R22" s="1">
         <v>11003</v>
       </c>
-      <c r="S22" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T22" s="43" t="s">
+      <c r="S22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U22" s="57">
+      <c r="T22" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U22" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4821,21 +4837,21 @@
         <v>2</v>
       </c>
       <c r="W22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X22" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y22" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z22" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA22" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB22" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4849,44 +4865,44 @@
       <c r="B23" s="12">
         <v>1</v>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="60">
         <v>1200102</v>
       </c>
       <c r="D23" s="12">
         <v>3</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I23" s="10">
         <v>11012</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M23" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O23" s="4">
         <v>12001</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q23" s="1">
         <v>101200</v>
@@ -4894,13 +4910,13 @@
       <c r="R23" s="1">
         <v>11012</v>
       </c>
-      <c r="S23" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T23" s="43" t="s">
+      <c r="S23" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U23" s="57">
+      <c r="T23" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U23" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4908,21 +4924,21 @@
         <v>3</v>
       </c>
       <c r="W23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X23" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y23" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z23" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA23" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB23" s="4" t="str">
         <f t="shared" si="8"/>
@@ -4936,44 +4952,44 @@
       <c r="B24" s="12">
         <v>1</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="60">
         <v>1200102</v>
       </c>
       <c r="D24" s="12">
         <v>4</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I24" s="10">
         <v>11014</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M24" s="4" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O24" s="4">
         <v>12001</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="1">
         <v>101400</v>
@@ -4981,13 +4997,13 @@
       <c r="R24" s="1">
         <v>11014</v>
       </c>
-      <c r="S24" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T24" s="43" t="s">
+      <c r="S24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U24" s="57">
+      <c r="T24" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U24" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -4995,21 +5011,21 @@
         <v>4</v>
       </c>
       <c r="W24" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X24" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y24" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z24" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB24" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5023,44 +5039,44 @@
       <c r="B25" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25" s="60">
         <v>1200102</v>
       </c>
       <c r="D25" s="12">
         <v>5</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" s="10">
         <v>11003</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M25" s="4" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S25</f>
         <v>在任意遊戲中，金币有效下注累積達到 18,000,000</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O25" s="4">
         <v>12001</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
@@ -5068,13 +5084,13 @@
       <c r="R25" s="1">
         <v>11003</v>
       </c>
-      <c r="S25" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T25" s="43" t="s">
+      <c r="S25" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U25" s="57">
+      <c r="T25" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U25" s="58">
         <f t="shared" si="6"/>
         <v>130.344827586207</v>
       </c>
@@ -5082,21 +5098,21 @@
         <v>5</v>
       </c>
       <c r="W25" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X25" s="4" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 18,000,000</v>
       </c>
       <c r="Y25" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z25" s="4" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 18,000,000</v>
       </c>
       <c r="AA25" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB25" s="4" t="str">
         <f t="shared" si="8"/>
@@ -5117,51 +5133,51 @@
         <v>1</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F26" s="36"/>
       <c r="G26" s="13">
-        <v>490</v>
-      </c>
-      <c r="H26" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="46">
+        <v>435</v>
+      </c>
+      <c r="H26" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="47">
         <v>11007</v>
       </c>
-      <c r="J26" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47" t="s">
-        <v>114</v>
+      <c r="J26" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48" t="s">
+        <v>115</v>
       </c>
       <c r="M26" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N26" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O26" s="36">
         <v>12001</v>
       </c>
-      <c r="P26" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="48">
+      <c r="P26" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q26" s="49">
         <v>100700</v>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="49">
         <v>11007</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T26" s="49" t="s">
+      <c r="S26" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U26" s="50">
+      <c r="T26" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5169,21 +5185,21 @@
         <v>1</v>
       </c>
       <c r="W26" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X26" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y26" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z26" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA26" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB26" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5204,51 +5220,51 @@
         <v>2</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="13">
-        <v>490</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="46">
+        <v>435</v>
+      </c>
+      <c r="H27" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="47">
         <v>11003</v>
       </c>
-      <c r="J27" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47" t="s">
-        <v>118</v>
+      <c r="J27" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48" t="s">
+        <v>119</v>
       </c>
       <c r="M27" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N27" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O27" s="36">
         <v>12001</v>
       </c>
-      <c r="P27" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="48">
+      <c r="P27" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q27" s="49">
         <v>100300</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="49">
         <v>11003</v>
       </c>
-      <c r="S27" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T27" s="49" t="s">
+      <c r="S27" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U27" s="50">
+      <c r="T27" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U27" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5256,21 +5272,21 @@
         <v>2</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X27" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y27" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z27" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA27" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB27" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5291,51 +5307,51 @@
         <v>3</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="36"/>
       <c r="G28" s="13">
-        <v>490</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="46">
+        <v>435</v>
+      </c>
+      <c r="H28" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="47">
         <v>11012</v>
       </c>
-      <c r="J28" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47" t="s">
-        <v>120</v>
+      <c r="J28" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48" t="s">
+        <v>121</v>
       </c>
       <c r="M28" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N28" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O28" s="36">
         <v>12001</v>
       </c>
-      <c r="P28" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="48">
+      <c r="P28" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="49">
         <v>101200</v>
       </c>
-      <c r="R28" s="48">
+      <c r="R28" s="49">
         <v>11012</v>
       </c>
-      <c r="S28" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T28" s="49" t="s">
+      <c r="S28" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U28" s="50">
+      <c r="T28" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U28" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5343,21 +5359,21 @@
         <v>3</v>
       </c>
       <c r="W28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X28" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y28" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z28" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA28" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB28" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5378,51 +5394,51 @@
         <v>4</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="36"/>
       <c r="G29" s="13">
-        <v>490</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="46">
+        <v>435</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="47">
         <v>11014</v>
       </c>
-      <c r="J29" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47" t="s">
-        <v>122</v>
+      <c r="J29" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48" t="s">
+        <v>123</v>
       </c>
       <c r="M29" s="36" t="str">
         <f t="shared" si="10"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N29" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O29" s="36">
         <v>12001</v>
       </c>
-      <c r="P29" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q29" s="48">
+      <c r="P29" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q29" s="49">
         <v>101400</v>
       </c>
-      <c r="R29" s="48">
+      <c r="R29" s="49">
         <v>11014</v>
       </c>
-      <c r="S29" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T29" s="49" t="s">
+      <c r="S29" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U29" s="50">
+      <c r="T29" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U29" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5430,21 +5446,21 @@
         <v>4</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X29" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y29" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA29" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB29" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5465,51 +5481,51 @@
         <v>5</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="36"/>
       <c r="G30" s="13">
-        <v>490</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="46">
+        <v>435</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="47">
         <v>11003</v>
       </c>
-      <c r="J30" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47" t="s">
-        <v>124</v>
+      <c r="J30" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48" t="s">
+        <v>125</v>
       </c>
       <c r="M30" s="36" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S30</f>
         <v>在任意遊戲中，金币有效下注累積達到 68,000,000</v>
       </c>
       <c r="N30" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O30" s="36">
         <v>12001</v>
       </c>
-      <c r="P30" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q30" s="48">
+      <c r="P30" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q30" s="49">
         <v>0</v>
       </c>
-      <c r="R30" s="48">
+      <c r="R30" s="49">
         <v>11003</v>
       </c>
-      <c r="S30" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="T30" s="49" t="s">
+      <c r="S30" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="U30" s="50">
+      <c r="T30" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="U30" s="51">
         <f t="shared" si="6"/>
         <v>492.413793103448</v>
       </c>
@@ -5517,21 +5533,21 @@
         <v>5</v>
       </c>
       <c r="W30" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X30" s="36" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 68,000,000</v>
       </c>
       <c r="Y30" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z30" s="36" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 68,000,000</v>
       </c>
       <c r="AA30" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB30" s="36" t="str">
         <f t="shared" si="8"/>
@@ -5551,52 +5567,52 @@
       <c r="D31" s="37">
         <v>1</v>
       </c>
-      <c r="E31" s="51" t="s">
-        <v>125</v>
+      <c r="E31" s="52" t="s">
+        <v>126</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="13">
-        <v>1210</v>
-      </c>
-      <c r="H31" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="52">
+        <v>1073</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="53">
         <v>11007</v>
       </c>
-      <c r="J31" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53" t="s">
-        <v>126</v>
+      <c r="J31" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54" t="s">
+        <v>127</v>
       </c>
       <c r="M31" s="37" t="str">
         <f t="shared" ref="M31:M34" si="11">"在["&amp;P31&amp;"]電子遊戲中，金币有效下注累積達到 "&amp;S31</f>
         <v>在[麻将胡了]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O31" s="37">
         <v>12001</v>
       </c>
-      <c r="P31" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q31" s="54">
+      <c r="P31" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q31" s="55">
         <v>100700</v>
       </c>
-      <c r="R31" s="54">
+      <c r="R31" s="55">
         <v>11007</v>
       </c>
-      <c r="S31" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T31" s="55" t="s">
+      <c r="S31" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U31" s="56">
+      <c r="T31" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U31" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5604,21 +5620,21 @@
         <v>1</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X31" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Mahjong Hu] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z31" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Mạt chược], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA31" s="37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB31" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5638,52 +5654,52 @@
       <c r="D32" s="37">
         <v>2</v>
       </c>
-      <c r="E32" s="51" t="s">
-        <v>129</v>
+      <c r="E32" s="52" t="s">
+        <v>130</v>
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="13">
-        <v>1210</v>
-      </c>
-      <c r="H32" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="52">
+        <v>1073</v>
+      </c>
+      <c r="H32" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="53">
         <v>11003</v>
       </c>
-      <c r="J32" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53" t="s">
-        <v>130</v>
+      <c r="J32" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54" t="s">
+        <v>131</v>
       </c>
       <c r="M32" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[超级明星]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O32" s="37">
         <v>12001</v>
       </c>
-      <c r="P32" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q32" s="54">
+      <c r="P32" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q32" s="55">
         <v>100300</v>
       </c>
-      <c r="R32" s="54">
+      <c r="R32" s="55">
         <v>11003</v>
       </c>
-      <c r="S32" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T32" s="55" t="s">
+      <c r="S32" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U32" s="56">
+      <c r="T32" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U32" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5691,21 +5707,21 @@
         <v>2</v>
       </c>
       <c r="W32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X32" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Super Star] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y32" s="37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z32" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Siêu Sao], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA32" s="37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB32" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5725,52 +5741,52 @@
       <c r="D33" s="37">
         <v>3</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>131</v>
+      <c r="E33" s="52" t="s">
+        <v>132</v>
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="13">
-        <v>1210</v>
-      </c>
-      <c r="H33" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="52">
+        <v>1073</v>
+      </c>
+      <c r="H33" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="53">
         <v>11012</v>
       </c>
-      <c r="J33" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53" t="s">
-        <v>132</v>
+      <c r="J33" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54" t="s">
+        <v>133</v>
       </c>
       <c r="M33" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[财神]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O33" s="37">
         <v>12001</v>
       </c>
-      <c r="P33" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="54">
+      <c r="P33" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="55">
         <v>101200</v>
       </c>
-      <c r="R33" s="54">
+      <c r="R33" s="55">
         <v>11012</v>
       </c>
-      <c r="S33" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T33" s="55" t="s">
+      <c r="S33" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U33" s="56">
+      <c r="T33" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U33" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5778,21 +5794,21 @@
         <v>3</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X33" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [God of Wealth] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z33" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Thần Tài], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA33" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB33" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5812,52 +5828,52 @@
       <c r="D34" s="37">
         <v>4</v>
       </c>
-      <c r="E34" s="51" t="s">
-        <v>133</v>
+      <c r="E34" s="52" t="s">
+        <v>134</v>
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="13">
-        <v>1210</v>
-      </c>
-      <c r="H34" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="52">
+        <v>1073</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="53">
         <v>11014</v>
       </c>
-      <c r="J34" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53" t="s">
-        <v>134</v>
+      <c r="J34" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54" t="s">
+        <v>135</v>
       </c>
       <c r="M34" s="37" t="str">
         <f t="shared" si="11"/>
         <v>在[埃及艳后]電子遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N34" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O34" s="37">
         <v>12001</v>
       </c>
-      <c r="P34" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34" s="54">
+      <c r="P34" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q34" s="55">
         <v>101400</v>
       </c>
-      <c r="R34" s="54">
+      <c r="R34" s="55">
         <v>11014</v>
       </c>
-      <c r="S34" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T34" s="55" t="s">
+      <c r="S34" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U34" s="56">
+      <c r="T34" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U34" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5865,21 +5881,21 @@
         <v>4</v>
       </c>
       <c r="W34" s="37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X34" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [Cleopatra] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y34" s="37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA34" s="37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB34" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5899,52 +5915,52 @@
       <c r="D35" s="37">
         <v>5</v>
       </c>
-      <c r="E35" s="51" t="s">
-        <v>135</v>
+      <c r="E35" s="52" t="s">
+        <v>136</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="13">
-        <v>1210</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="52">
+        <v>1073</v>
+      </c>
+      <c r="H35" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="53">
         <v>11003</v>
       </c>
-      <c r="J35" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53" t="s">
-        <v>136</v>
+      <c r="J35" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54" t="s">
+        <v>137</v>
       </c>
       <c r="M35" s="37" t="str">
         <f>"在任意遊戲中，金币有效下注累積達到 "&amp;S35</f>
         <v>在任意遊戲中，金币有效下注累積達到 168,000,000</v>
       </c>
       <c r="N35" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O35" s="37">
         <v>12001</v>
       </c>
-      <c r="P35" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q35" s="54">
+      <c r="P35" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" s="55">
         <v>0</v>
       </c>
-      <c r="R35" s="54">
+      <c r="R35" s="55">
         <v>11003</v>
       </c>
-      <c r="S35" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="T35" s="55" t="s">
+      <c r="S35" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="U35" s="56">
+      <c r="T35" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="U35" s="57">
         <f t="shared" si="6"/>
         <v>1216.55172413793</v>
       </c>
@@ -5952,21 +5968,21 @@
         <v>5</v>
       </c>
       <c r="W35" s="37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X35" s="37" t="str">
         <f t="shared" si="9"/>
         <v>In the [any game] video game, the accumulated valid Gold Coin bets reach 168,000,000</v>
       </c>
       <c r="Y35" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z35" s="37" t="str">
         <f t="shared" si="7"/>
         <v>Trong trò chơi [bất kỳ], tích lũy đặt cược hợp lệ tiền vàng đạt 168,000,000</v>
       </c>
       <c r="AA35" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB35" s="37" t="str">
         <f t="shared" si="8"/>
@@ -5987,37 +6003,37 @@
         <v>1</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I36" s="10">
         <v>11007</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M36" s="4" t="str">
         <f t="shared" ref="M36:M39" si="12">"在["&amp;P36&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S36</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O36" s="4">
         <v>10003</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q36" s="1">
         <v>100700</v>
@@ -6025,13 +6041,13 @@
       <c r="R36" s="1">
         <v>11007</v>
       </c>
-      <c r="S36" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T36" s="43" t="s">
+      <c r="S36" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U36" s="60">
+      <c r="T36" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U36" s="61">
         <f t="shared" ref="U36:U40" si="13">S36*3%/29000*7*2</f>
         <v>120.206896551724</v>
       </c>
@@ -6039,21 +6055,21 @@
         <v>1</v>
       </c>
       <c r="W36" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X36" s="4" t="str">
         <f>"In the ["&amp;W36&amp;"] , total gold coins won have reached  "&amp;S36</f>
         <v>In the [Mahjong Hu] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y36" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z36" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y36&amp;"], tổng số vàng thắng được đạt "&amp;S36</f>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA36" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB36" s="4" t="str">
         <f>"No jogo ["&amp;AA36&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S36</f>
@@ -6074,37 +6090,37 @@
         <v>2</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I37" s="10">
         <v>11003</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M37" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="4">
         <v>10003</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q37" s="1">
         <v>100300</v>
@@ -6112,13 +6128,13 @@
       <c r="R37" s="1">
         <v>11003</v>
       </c>
-      <c r="S37" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T37" s="43" t="s">
+      <c r="S37" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U37" s="60">
+      <c r="T37" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U37" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6126,21 +6142,21 @@
         <v>2</v>
       </c>
       <c r="W37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X37" s="4" t="str">
         <f t="shared" ref="X37:X55" si="14">"In the ["&amp;W37&amp;"] , total gold coins won have reached  "&amp;S37</f>
         <v>In the [Super Star] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y37" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z37" s="4" t="str">
         <f t="shared" ref="Z37:Z55" si="15">"Trong trò chơi ["&amp;Y37&amp;"], tổng số vàng thắng được đạt "&amp;S37</f>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA37" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB37" s="4" t="str">
         <f t="shared" ref="AB37:AB55" si="16">"No jogo ["&amp;AA37&amp;"], o total de moedas de ouro ganhas atingiu "&amp;S37</f>
@@ -6161,37 +6177,37 @@
         <v>3</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I38" s="10">
         <v>11012</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M38" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="4">
         <v>10003</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q38" s="1">
         <v>101200</v>
@@ -6199,13 +6215,13 @@
       <c r="R38" s="1">
         <v>11012</v>
       </c>
-      <c r="S38" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T38" s="43" t="s">
+      <c r="S38" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U38" s="60">
+      <c r="T38" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U38" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6213,21 +6229,21 @@
         <v>3</v>
       </c>
       <c r="W38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X38" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y38" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z38" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA38" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB38" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6248,37 +6264,37 @@
         <v>4</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="10">
         <v>11014</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M39" s="4" t="str">
         <f t="shared" si="12"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="4">
         <v>10003</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="1">
         <v>101400</v>
@@ -6286,13 +6302,13 @@
       <c r="R39" s="1">
         <v>11014</v>
       </c>
-      <c r="S39" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T39" s="43" t="s">
+      <c r="S39" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U39" s="60">
+      <c r="T39" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6300,21 +6316,21 @@
         <v>4</v>
       </c>
       <c r="W39" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X39" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y39" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z39" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA39" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB39" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6335,37 +6351,37 @@
         <v>5</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="13">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I40" s="10">
         <v>11003</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M40" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S40</f>
         <v>在任意遊戲中，金币累積贏獎達到 8,300,000</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O40" s="4">
         <v>10003</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="1">
         <v>0</v>
@@ -6373,13 +6389,13 @@
       <c r="R40" s="1">
         <v>11003</v>
       </c>
-      <c r="S40" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="T40" s="43" t="s">
+      <c r="S40" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="U40" s="60">
+      <c r="T40" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U40" s="61">
         <f t="shared" si="13"/>
         <v>120.206896551724</v>
       </c>
@@ -6387,21 +6403,21 @@
         <v>5</v>
       </c>
       <c r="W40" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X40" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  8,300,000</v>
       </c>
       <c r="Y40" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z40" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 8,300,000</v>
       </c>
       <c r="AA40" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB40" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6422,37 +6438,37 @@
         <v>1</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I41" s="10">
         <v>11007</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M41" s="4" t="str">
         <f t="shared" ref="M41:M44" si="17">"在["&amp;P41&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S41</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="4">
         <v>10003</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q41" s="1">
         <v>100700</v>
@@ -6460,13 +6476,13 @@
       <c r="R41" s="1">
         <v>11007</v>
       </c>
-      <c r="S41" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T41" s="43" t="s">
+      <c r="S41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U41" s="60">
+      <c r="T41" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U41" s="61">
         <f t="shared" ref="U41:U45" si="18">S41*3%/29000*7*2</f>
         <v>260.689655172414</v>
       </c>
@@ -6474,21 +6490,21 @@
         <v>1</v>
       </c>
       <c r="W41" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X41" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y41" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z41" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA41" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB41" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6509,37 +6525,37 @@
         <v>2</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>11003</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M42" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42" s="4">
         <v>10003</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q42" s="1">
         <v>100300</v>
@@ -6547,13 +6563,13 @@
       <c r="R42" s="1">
         <v>11003</v>
       </c>
-      <c r="S42" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T42" s="43" t="s">
+      <c r="S42" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U42" s="60">
+      <c r="T42" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U42" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6561,21 +6577,21 @@
         <v>2</v>
       </c>
       <c r="W42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X42" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y42" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z42" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA42" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB42" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6596,37 +6612,37 @@
         <v>3</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>11012</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M43" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O43" s="4">
         <v>10003</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q43" s="1">
         <v>101200</v>
@@ -6634,13 +6650,13 @@
       <c r="R43" s="1">
         <v>11012</v>
       </c>
-      <c r="S43" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T43" s="43" t="s">
+      <c r="S43" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U43" s="60">
+      <c r="T43" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U43" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6648,21 +6664,21 @@
         <v>3</v>
       </c>
       <c r="W43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X43" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y43" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z43" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA43" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB43" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6683,37 +6699,37 @@
         <v>4</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>11014</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M44" s="4" t="str">
         <f t="shared" si="17"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44" s="4">
         <v>10003</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="1">
         <v>101400</v>
@@ -6721,13 +6737,13 @@
       <c r="R44" s="1">
         <v>11014</v>
       </c>
-      <c r="S44" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T44" s="43" t="s">
+      <c r="S44" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U44" s="60">
+      <c r="T44" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U44" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6735,21 +6751,21 @@
         <v>4</v>
       </c>
       <c r="W44" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X44" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y44" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z44" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA44" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB44" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6770,37 +6786,37 @@
         <v>5</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>11003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M45" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S45</f>
         <v>在任意遊戲中，金币累積贏獎達到 18,000,000</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O45" s="4">
         <v>10003</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="1">
         <v>0</v>
@@ -6808,13 +6824,13 @@
       <c r="R45" s="1">
         <v>11003</v>
       </c>
-      <c r="S45" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="T45" s="43" t="s">
+      <c r="S45" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="U45" s="60">
+      <c r="T45" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="U45" s="61">
         <f t="shared" si="18"/>
         <v>260.689655172414</v>
       </c>
@@ -6822,21 +6838,21 @@
         <v>5</v>
       </c>
       <c r="W45" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X45" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  18,000,000</v>
       </c>
       <c r="Y45" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z45" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 18,000,000</v>
       </c>
       <c r="AA45" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB45" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6857,37 +6873,37 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>11007</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M46" s="4" t="str">
         <f t="shared" ref="M46:M49" si="19">"在["&amp;P46&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S46</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O46" s="4">
         <v>10003</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q46" s="1">
         <v>100700</v>
@@ -6895,13 +6911,13 @@
       <c r="R46" s="1">
         <v>11007</v>
       </c>
-      <c r="S46" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T46" s="43" t="s">
+      <c r="S46" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U46" s="60">
+      <c r="T46" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U46" s="61">
         <f t="shared" ref="U46:U55" si="20">S46*3%/29000*7*2</f>
         <v>350.48275862069</v>
       </c>
@@ -6909,21 +6925,21 @@
         <v>1</v>
       </c>
       <c r="W46" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X46" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z46" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA46" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB46" s="4" t="str">
         <f t="shared" si="16"/>
@@ -6944,37 +6960,37 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>11003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M47" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O47" s="4">
         <v>10003</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q47" s="1">
         <v>100300</v>
@@ -6982,13 +6998,13 @@
       <c r="R47" s="1">
         <v>11003</v>
       </c>
-      <c r="S47" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" s="43" t="s">
+      <c r="S47" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U47" s="60">
+      <c r="T47" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U47" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -6996,21 +7012,21 @@
         <v>2</v>
       </c>
       <c r="W47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X47" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y47" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z47" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA47" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB47" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7031,37 +7047,37 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>11012</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M48" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O48" s="4">
         <v>10003</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q48" s="1">
         <v>101200</v>
@@ -7069,13 +7085,13 @@
       <c r="R48" s="1">
         <v>11012</v>
       </c>
-      <c r="S48" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T48" s="43" t="s">
+      <c r="S48" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U48" s="60">
+      <c r="T48" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U48" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7083,21 +7099,21 @@
         <v>3</v>
       </c>
       <c r="W48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X48" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y48" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z48" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA48" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB48" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7118,37 +7134,37 @@
         <v>4</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I49" s="10">
         <v>11014</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M49" s="4" t="str">
         <f t="shared" si="19"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O49" s="4">
         <v>10003</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="1">
         <v>101400</v>
@@ -7156,13 +7172,13 @@
       <c r="R49" s="1">
         <v>11014</v>
       </c>
-      <c r="S49" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T49" s="43" t="s">
+      <c r="S49" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U49" s="60">
+      <c r="T49" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U49" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7170,21 +7186,21 @@
         <v>4</v>
       </c>
       <c r="W49" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X49" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y49" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z49" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA49" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB49" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7205,37 +7221,37 @@
         <v>5</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I50" s="10">
         <v>11003</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M50" s="4" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S50</f>
         <v>在任意遊戲中，金币累積贏獎達到 24,200,000</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O50" s="4">
         <v>10003</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q50" s="1">
         <v>0</v>
@@ -7243,13 +7259,13 @@
       <c r="R50" s="1">
         <v>11003</v>
       </c>
-      <c r="S50" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="T50" s="43" t="s">
+      <c r="S50" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="U50" s="60">
+      <c r="T50" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U50" s="61">
         <f t="shared" si="20"/>
         <v>350.48275862069</v>
       </c>
@@ -7257,21 +7273,21 @@
         <v>5</v>
       </c>
       <c r="W50" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X50" s="4" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  24,200,000</v>
       </c>
       <c r="Y50" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z50" s="4" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 24,200,000</v>
       </c>
       <c r="AA50" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB50" s="4" t="str">
         <f t="shared" si="16"/>
@@ -7292,51 +7308,51 @@
         <v>1</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F51" s="36"/>
       <c r="G51" s="13">
-        <v>1200</v>
-      </c>
-      <c r="H51" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="46">
+        <v>1060</v>
+      </c>
+      <c r="H51" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="47">
         <v>11007</v>
       </c>
-      <c r="J51" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47" t="s">
-        <v>173</v>
+      <c r="J51" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48" t="s">
+        <v>174</v>
       </c>
       <c r="M51" s="36" t="str">
         <f t="shared" ref="M51:M54" si="21">"在["&amp;P51&amp;"]電子遊戲中，金币累積贏獎達到 "&amp;S51</f>
         <v>在[麻将胡了]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N51" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51" s="36">
         <v>10003</v>
       </c>
-      <c r="P51" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q51" s="48">
+      <c r="P51" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q51" s="49">
         <v>100700</v>
       </c>
-      <c r="R51" s="48">
+      <c r="R51" s="49">
         <v>11007</v>
       </c>
-      <c r="S51" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T51" s="49" t="s">
+      <c r="S51" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U51" s="50">
+      <c r="T51" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U51" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7344,21 +7360,21 @@
         <v>1</v>
       </c>
       <c r="W51" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X51" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Mahjong Hu] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y51" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z51" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Mạt chược], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA51" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB51" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7379,51 +7395,51 @@
         <v>2</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="13">
-        <v>1200</v>
-      </c>
-      <c r="H52" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="46">
+        <v>1060</v>
+      </c>
+      <c r="H52" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="47">
         <v>11003</v>
       </c>
-      <c r="J52" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="K52" s="47"/>
-      <c r="L52" s="47" t="s">
-        <v>177</v>
+      <c r="J52" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52" s="48"/>
+      <c r="L52" s="48" t="s">
+        <v>178</v>
       </c>
       <c r="M52" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[超级明星]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N52" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O52" s="36">
         <v>10003</v>
       </c>
-      <c r="P52" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q52" s="48">
+      <c r="P52" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q52" s="49">
         <v>100300</v>
       </c>
-      <c r="R52" s="48">
+      <c r="R52" s="49">
         <v>11003</v>
       </c>
-      <c r="S52" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T52" s="49" t="s">
+      <c r="S52" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U52" s="50">
+      <c r="T52" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U52" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7431,21 +7447,21 @@
         <v>2</v>
       </c>
       <c r="W52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X52" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Super Star] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y52" s="36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z52" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Siêu Sao], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA52" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB52" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7466,51 +7482,51 @@
         <v>3</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F53" s="36"/>
       <c r="G53" s="13">
-        <v>1200</v>
-      </c>
-      <c r="H53" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="46">
+        <v>1060</v>
+      </c>
+      <c r="H53" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="47">
         <v>11012</v>
       </c>
-      <c r="J53" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47" t="s">
-        <v>179</v>
+      <c r="J53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="K53" s="48"/>
+      <c r="L53" s="48" t="s">
+        <v>180</v>
       </c>
       <c r="M53" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[财神]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N53" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O53" s="36">
         <v>10003</v>
       </c>
-      <c r="P53" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q53" s="48">
+      <c r="P53" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="49">
         <v>101200</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="49">
         <v>11012</v>
       </c>
-      <c r="S53" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T53" s="49" t="s">
+      <c r="S53" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U53" s="50">
+      <c r="T53" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U53" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7518,21 +7534,21 @@
         <v>3</v>
       </c>
       <c r="W53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X53" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [God of Wealth] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y53" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z53" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Thần Tài], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA53" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB53" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7553,51 +7569,51 @@
         <v>4</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="13">
-        <v>1200</v>
-      </c>
-      <c r="H54" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="46">
+        <v>1060</v>
+      </c>
+      <c r="H54" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="47">
         <v>11014</v>
       </c>
-      <c r="J54" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47" t="s">
-        <v>181</v>
+      <c r="J54" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="48"/>
+      <c r="L54" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="M54" s="36" t="str">
         <f t="shared" si="21"/>
         <v>在[埃及艳后]電子遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N54" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O54" s="36">
         <v>10003</v>
       </c>
-      <c r="P54" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q54" s="48">
+      <c r="P54" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q54" s="49">
         <v>101400</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="49">
         <v>11014</v>
       </c>
-      <c r="S54" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T54" s="49" t="s">
+      <c r="S54" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U54" s="50">
+      <c r="T54" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U54" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7605,21 +7621,21 @@
         <v>4</v>
       </c>
       <c r="W54" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X54" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [Cleopatra] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y54" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z54" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA54" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB54" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7640,51 +7656,51 @@
         <v>5</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="13">
-        <v>1200</v>
-      </c>
-      <c r="H55" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="46">
+        <v>1060</v>
+      </c>
+      <c r="H55" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="47">
         <v>11003</v>
       </c>
-      <c r="J55" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="K55" s="47"/>
-      <c r="L55" s="47" t="s">
-        <v>183</v>
+      <c r="J55" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="48"/>
+      <c r="L55" s="48" t="s">
+        <v>184</v>
       </c>
       <c r="M55" s="36" t="str">
         <f>"在任意遊戲中，金币累積贏獎達到 "&amp;S55</f>
         <v>在任意遊戲中，金币累積贏獎達到 83,000,000</v>
       </c>
       <c r="N55" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O55" s="36">
         <v>10003</v>
       </c>
-      <c r="P55" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q55" s="48">
+      <c r="P55" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q55" s="49">
         <v>0</v>
       </c>
-      <c r="R55" s="48">
+      <c r="R55" s="49">
         <v>11003</v>
       </c>
-      <c r="S55" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="T55" s="49" t="s">
+      <c r="S55" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="U55" s="50">
+      <c r="T55" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="U55" s="51">
         <f t="shared" si="20"/>
         <v>1202.06896551724</v>
       </c>
@@ -7692,21 +7708,21 @@
         <v>5</v>
       </c>
       <c r="W55" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X55" s="36" t="str">
         <f t="shared" si="14"/>
         <v>In the [any game] , total gold coins won have reached  83,000,000</v>
       </c>
       <c r="Y55" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z55" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Trong trò chơi [bất kỳ], tổng số vàng thắng được đạt 83,000,000</v>
       </c>
       <c r="AA55" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB55" s="36" t="str">
         <f t="shared" si="16"/>
@@ -7727,37 +7743,37 @@
         <v>1</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="13">
         <v>5</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I56" s="10">
         <v>11007</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M56" s="4" t="str">
         <f>"在["&amp;P56&amp;"]電子遊戲中，累積旋轉 "&amp;S56&amp;"次"</f>
         <v>在[麻将胡了]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="4">
         <v>10001</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q56" s="1">
         <v>100700</v>
@@ -7765,11 +7781,11 @@
       <c r="R56" s="1">
         <v>11007</v>
       </c>
-      <c r="S56" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T56" s="43" t="s">
-        <v>187</v>
+      <c r="S56" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T56" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U56" s="4">
         <f t="shared" ref="U56:U60" si="22">S56/100</f>
@@ -7779,21 +7795,21 @@
         <v>1</v>
       </c>
       <c r="W56" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X56" s="4" t="str">
         <f>"In the game ["&amp;W56&amp;"] , "&amp;S56&amp;" spins have been accumulated."</f>
         <v>In the game [Mahjong Hu] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y56" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z56" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y56&amp;"], tích lũy quay "&amp;T56&amp;" lần."</f>
         <v>Trong trò chơi [Mạt chược], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA56" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB56" s="4" t="str">
         <f>"No jogo ["&amp;W56&amp;"], foram acumuladas "&amp;T56&amp;" rodadas."</f>
@@ -7814,37 +7830,37 @@
         <v>2</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="13">
         <v>5</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" s="10">
         <v>11003</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M57" s="4" t="str">
         <f>"在["&amp;P57&amp;"]電子遊戲中，累積旋轉 "&amp;S57&amp;"次"</f>
         <v>在[超级明星]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="4">
         <v>10001</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q57" s="1">
         <v>100300</v>
@@ -7852,11 +7868,11 @@
       <c r="R57" s="1">
         <v>11003</v>
       </c>
-      <c r="S57" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T57" s="43" t="s">
-        <v>187</v>
+      <c r="S57" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T57" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U57" s="4">
         <f t="shared" si="22"/>
@@ -7866,21 +7882,21 @@
         <v>2</v>
       </c>
       <c r="W57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X57" s="4" t="str">
         <f>"In the game ["&amp;W57&amp;"] , "&amp;S57&amp;" spins have been accumulated."</f>
         <v>In the game [Super Star] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y57" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z57" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y57&amp;"], tích lũy quay "&amp;T57&amp;" lần."</f>
         <v>Trong trò chơi [Siêu Sao], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA57" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB57" s="4" t="str">
         <f>"No jogo ["&amp;W57&amp;"], foram acumuladas "&amp;T57&amp;" rodadas."</f>
@@ -7901,37 +7917,37 @@
         <v>3</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="13">
         <v>5</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I58" s="10">
         <v>11012</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M58" s="4" t="str">
         <f>"在["&amp;P58&amp;"]電子遊戲中，累積旋轉 "&amp;S58&amp;"次"</f>
         <v>在[财神]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O58" s="4">
         <v>10001</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q58" s="1">
         <v>101200</v>
@@ -7939,11 +7955,11 @@
       <c r="R58" s="1">
         <v>11012</v>
       </c>
-      <c r="S58" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T58" s="43" t="s">
-        <v>187</v>
+      <c r="S58" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T58" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U58" s="4">
         <f t="shared" si="22"/>
@@ -7953,21 +7969,21 @@
         <v>3</v>
       </c>
       <c r="W58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X58" s="4" t="str">
         <f>"In the game ["&amp;W58&amp;"] , "&amp;S58&amp;" spins have been accumulated."</f>
         <v>In the game [God of Wealth] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y58" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z58" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y58&amp;"], tích lũy quay "&amp;T58&amp;" lần."</f>
         <v>Trong trò chơi [Thần Tài], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA58" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB58" s="4" t="str">
         <f>"No jogo ["&amp;W58&amp;"], foram acumuladas "&amp;T58&amp;" rodadas."</f>
@@ -7988,37 +8004,37 @@
         <v>4</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>11014</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M59" s="4" t="str">
         <f>"在["&amp;P59&amp;"]電子遊戲中，累積旋轉 "&amp;S59&amp;"次"</f>
         <v>在[埃及艳后]電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O59" s="4">
         <v>10001</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q59" s="1">
         <v>101400</v>
@@ -8026,11 +8042,11 @@
       <c r="R59" s="1">
         <v>11014</v>
       </c>
-      <c r="S59" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T59" s="43" t="s">
-        <v>187</v>
+      <c r="S59" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T59" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U59" s="4">
         <f t="shared" si="22"/>
@@ -8040,21 +8056,21 @@
         <v>4</v>
       </c>
       <c r="W59" s="41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X59" s="4" t="str">
         <f>"In the game ["&amp;W59&amp;"] , "&amp;S59&amp;" spins have been accumulated."</f>
         <v>In the game [Cleopatra] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y59" s="41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z59" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y59&amp;"], tích lũy quay "&amp;T59&amp;" lần."</f>
         <v>Trong trò chơi [Nữ hoàng Ai Cập], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA59" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB59" s="4" t="str">
         <f>"No jogo ["&amp;W59&amp;"], foram acumuladas "&amp;T59&amp;" rodadas."</f>
@@ -8075,31 +8091,31 @@
         <v>5</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>5</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>11003</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M60" s="4" t="str">
         <f>"在任意電子遊戲中，累積旋轉 "&amp;S60&amp;"次"</f>
         <v>在任意電子遊戲中，累積旋轉 500次</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="4">
         <v>10001</v>
@@ -8111,11 +8127,11 @@
       <c r="R60" s="1">
         <v>11003</v>
       </c>
-      <c r="S60" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="T60" s="43" t="s">
-        <v>187</v>
+      <c r="S60" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="T60" s="44" t="s">
+        <v>188</v>
       </c>
       <c r="U60" s="4">
         <f t="shared" si="22"/>
@@ -8125,21 +8141,21 @@
         <v>5</v>
       </c>
       <c r="W60" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X60" s="4" t="str">
         <f>"In the game ["&amp;W60&amp;"] , "&amp;S60&amp;" spins have been accumulated."</f>
         <v>In the game [any game] , 500 spins have been accumulated.</v>
       </c>
       <c r="Y60" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z60" s="4" t="str">
         <f>"Trong trò chơi ["&amp;Y60&amp;"], tích lũy quay "&amp;T60&amp;" lần."</f>
         <v>Trong trò chơi [bất kỳ], tích lũy quay 500 lần.</v>
       </c>
       <c r="AA60" s="41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB60" s="4" t="str">
         <f>"No jogo ["&amp;W60&amp;"], foram acumuladas "&amp;T60&amp;" rodadas."</f>
@@ -8181,16 +8197,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J5" s="19">
         <v>502</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -8201,32 +8217,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -8234,37 +8250,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F7" s="18">
         <v>100100</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J7" s="18">
         <v>2</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N7" s="18">
         <v>1022501</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -8272,37 +8288,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="18">
         <v>100300</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J8" s="18">
         <v>3</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N8" s="18">
         <v>1022502</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -8310,37 +8326,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" s="18">
         <v>100700</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J9" s="18">
         <v>4</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N9" s="18">
         <v>1010301</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -8348,37 +8364,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="18">
         <v>101200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="18">
         <v>5</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N10" s="18">
         <v>1010302</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -8386,37 +8402,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F11" s="18">
         <v>101400</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J11" s="18">
         <v>6</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N11" s="18">
         <v>1010303</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -8424,37 +8440,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="18">
         <v>200100</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="25">
         <v>12</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N12" s="18">
         <v>1010311</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -8462,19 +8478,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13" s="18">
         <v>200101</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -8483,10 +8499,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -8494,19 +8510,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F14" s="18">
         <v>200300</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -8515,10 +8531,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -8526,28 +8542,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" s="18">
         <v>200400</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N15" s="18">
         <v>1010314</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -8555,28 +8571,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F16" s="18">
         <v>200500</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N16" s="18">
         <v>1010315</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -8584,19 +8600,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F17" s="18">
         <v>200600</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -8604,19 +8620,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F18" s="18">
         <v>200700</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -8624,22 +8640,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="18">
         <v>200800</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -8647,28 +8663,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F20" s="18">
         <v>200900</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -8676,28 +8692,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F21" s="18">
         <v>201000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N21" s="18">
         <v>1022501</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -8705,28 +8721,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F22" s="18">
         <v>300100</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N22" s="18">
         <v>1022502</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -8734,19 +8750,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N23" s="18">
         <v>1980000</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -8754,10 +8770,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -8765,10 +8781,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -8776,10 +8792,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -8787,10 +8803,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -8798,10 +8814,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -8809,10 +8825,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -8820,10 +8836,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -8831,10 +8847,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -8842,10 +8858,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -8853,10 +8869,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:22">
@@ -8871,7 +8887,7 @@
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28" t="s">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>4</v>
@@ -8898,19 +8914,19 @@
         <v>11</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:22">
@@ -8925,25 +8941,25 @@
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L39" s="33" t="s">
         <v>13</v>
@@ -8951,38 +8967,38 @@
     </row>
     <row r="40" s="3" customFormat="1" spans="1:22">
       <c r="A40" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L40" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:22">
@@ -9014,36 +9030,36 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
         <v>3</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I42" s="10">
         <v>3002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
         <v>70008</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O42" s="4">
         <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -9079,36 +9095,36 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
         <v>8</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I43" s="10">
         <v>3002</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O43" s="4">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>0.25</v>
@@ -9144,36 +9160,36 @@
         <v>2</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
         <v>25</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10">
         <v>3002</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O44" s="4">
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>0.25</v>
@@ -9208,30 +9224,30 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
         <v>20</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10">
         <v>2003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O45" s="4">
         <v>2</v>
@@ -9270,30 +9286,30 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
         <v>1</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10">
         <v>2003</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -9332,30 +9348,30 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
         <v>5</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="10">
         <v>2003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -9394,30 +9410,30 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
         <v>10</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="10">
         <v>2003</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O48" s="4">
         <v>1</v>
@@ -9461,7 +9477,7 @@
         <v>70001</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -9471,7 +9487,7 @@
         <v>70002</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -9481,7 +9497,7 @@
         <v>70003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -9491,7 +9507,7 @@
         <v>70004</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -9501,10 +9517,10 @@
         <v>70005</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L5" s="10">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9516,10 +9532,10 @@
         <v>70006</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L6" s="10">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9531,10 +9547,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>317</v>
       </c>
       <c r="L7" s="10">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9546,10 +9562,10 @@
         <v>70008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L8" s="10">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9561,10 +9577,10 @@
         <v>70009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" s="10">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9576,10 +9592,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L10" s="10">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9591,10 +9607,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L11" s="10">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9606,10 +9622,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L12" s="10">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9621,10 +9637,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L13" s="10">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9636,10 +9652,10 @@
         <v>70104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" s="10">
         <f>_xlfn.XLOOKUP(K14,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9651,10 +9667,10 @@
         <v>70301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="10">
         <f>_xlfn.XLOOKUP(K15,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9666,10 +9682,10 @@
         <v>70302</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L16" s="10">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9681,10 +9697,10 @@
         <v>70303</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L17" s="10">
         <f>_xlfn.XLOOKUP(K17,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9696,10 +9712,10 @@
         <v>70304</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L18" s="10">
         <f>_xlfn.XLOOKUP(K18,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9711,10 +9727,10 @@
         <v>70305</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L19" s="10">
         <f>_xlfn.XLOOKUP(K19,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9726,10 +9742,10 @@
         <v>70306</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L20" s="10">
         <f>_xlfn.XLOOKUP(K20,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9741,10 +9757,10 @@
         <v>70307</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L21" s="10">
         <f>_xlfn.XLOOKUP(K21,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9756,10 +9772,10 @@
         <v>70308</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L22" s="10">
         <f>_xlfn.XLOOKUP(K22,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9771,10 +9787,10 @@
         <v>70309</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L23" s="10">
         <f>_xlfn.XLOOKUP(K23,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9786,10 +9802,10 @@
         <v>70310</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L24" s="10">
         <f>_xlfn.XLOOKUP(K24,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9801,10 +9817,10 @@
         <v>70311</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L25" s="10">
         <f>_xlfn.XLOOKUP(K25,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9816,10 +9832,10 @@
         <v>70312</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L26" s="10">
         <f>_xlfn.XLOOKUP(K26,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9831,10 +9847,10 @@
         <v>70381</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L27" s="10">
         <f>_xlfn.XLOOKUP(K27,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9846,10 +9862,10 @@
         <v>70382</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L28" s="10">
         <f>_xlfn.XLOOKUP(K28,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9861,10 +9877,10 @@
         <v>70383</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L29" s="10">
         <f>_xlfn.XLOOKUP(K29,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9876,10 +9892,10 @@
         <v>70391</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L30" s="10">
         <f>_xlfn.XLOOKUP(K30,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9891,10 +9907,10 @@
         <v>70392</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L31" s="10">
         <f>_xlfn.XLOOKUP(K31,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9906,10 +9922,10 @@
         <v>70393</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L32" s="10">
         <f>_xlfn.XLOOKUP(K32,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9921,10 +9937,10 @@
         <v>71101</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L33" s="10">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9936,10 +9952,10 @@
         <v>71102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L34" s="10">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9951,10 +9967,10 @@
         <v>71103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L35" s="10">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9966,10 +9982,10 @@
         <v>71201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L36" s="10">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9981,10 +9997,10 @@
         <v>71202</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L37" s="10">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -9996,10 +10012,10 @@
         <v>72011</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L38" s="10">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10011,10 +10027,10 @@
         <v>72012</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L39" s="10">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10026,10 +10042,10 @@
         <v>72101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L40" s="10">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10041,10 +10057,10 @@
         <v>72102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L41" s="10">
         <f>_xlfn.XLOOKUP(K41,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10053,7 +10069,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="K42" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L42" s="10">
         <f>_xlfn.XLOOKUP(K42,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10062,7 +10078,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="K43" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L43" s="10">
         <f>_xlfn.XLOOKUP(K43,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10071,7 +10087,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="K44" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L44" s="10">
         <f>_xlfn.XLOOKUP(K44,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10080,7 +10096,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="K45" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L45" s="10">
         <f>_xlfn.XLOOKUP(K45,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -10172,30 +10188,30 @@
         <v>1</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
         <v>5</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="10">
         <v>2001</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8">
         <v>70007</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
@@ -10231,30 +10247,30 @@
         <v>1</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
         <v>10</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I60" s="10">
         <v>2001</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="O60" s="3">
         <v>7000</v>
@@ -10292,30 +10308,30 @@
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13">
         <v>100</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I61" s="10">
         <v>2001</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O61" s="3">
         <v>70000</v>
@@ -10353,30 +10369,30 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="13">
         <v>1000</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I62" s="10">
         <v>2001</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O62" s="3">
         <v>700000</v>
@@ -10413,29 +10429,29 @@
         <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="15">
         <v>10</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I63" s="11">
         <v>2002</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L63" s="16">
         <v>70007</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P63" s="4"/>
     </row>
@@ -10454,29 +10470,29 @@
         <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F65" s="14"/>
       <c r="G65" s="15">
         <v>20</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I65" s="11">
         <v>1001</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L65" s="16">
         <v>70001</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V65" s="4">
         <f>ROUND(MAX(S65/100,T65/100,U65),0)</f>
@@ -10498,29 +10514,29 @@
         <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="15">
         <v>100</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I66" s="11">
         <v>2001</v>
       </c>
       <c r="J66" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="K66" s="16" t="s">
         <v>361</v>
-      </c>
-      <c r="K66" s="16" t="s">
-        <v>359</v>
       </c>
       <c r="L66" s="16">
         <v>70002</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:22">
@@ -10538,29 +10554,29 @@
         <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="15">
         <v>10</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I67" s="11">
         <v>2002</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L67" s="16">
         <v>70003</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:22">
@@ -10578,29 +10594,29 @@
         <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F68" s="14"/>
       <c r="G68" s="15">
         <v>40</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I68" s="11">
         <v>2003</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L68" s="16">
         <v>70004</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:22">
@@ -10618,29 +10634,29 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="15">
         <v>10</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I69" s="11">
         <v>1001</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L69" s="16">
         <v>70005</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N69" s="17"/>
     </row>
@@ -10659,29 +10675,29 @@
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="15">
         <v>20</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I70" s="11">
         <v>2001</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L70" s="16">
         <v>70006</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N70" s="17"/>
     </row>
@@ -10700,29 +10716,29 @@
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="15">
         <v>5</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I71" s="11">
         <v>2003</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L71" s="16">
         <v>70008</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N71" s="17"/>
     </row>
@@ -10741,29 +10757,29 @@
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="15">
         <v>1</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I72" s="11">
         <v>1001</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L72" s="16">
         <v>70009</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N72" s="17"/>
     </row>
@@ -10782,29 +10798,29 @@
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="15">
         <v>5</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I73" s="11">
         <v>2001</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L73" s="16">
         <v>70010</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -10831,384 +10847,384 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="1">
         <v>100100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1">
         <v>100300</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>100700</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1">
         <v>101200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="1">
         <v>101400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B7" s="1">
         <v>101700</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B8" s="1">
         <v>102100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B9" s="1">
         <v>102200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1">
         <v>102300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1">
         <v>102400</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1">
         <v>102500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B13" s="1">
         <v>200100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B14" s="1">
         <v>200101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B15" s="1">
         <v>200300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B16" s="1">
         <v>200400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B17" s="1">
         <v>200500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B18" s="1">
         <v>200600</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B19" s="1">
         <v>200700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B20" s="1">
         <v>200800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B21" s="1">
         <v>200900</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B22" s="1">
         <v>300100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B23" s="1">
         <v>300200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B24" s="1">
         <v>500000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1">
         <v>500001</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B26" s="1">
         <v>500002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B27" s="1">
         <v>500003</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B28" s="1">
         <v>500004</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B29" s="1">
         <v>500005</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1">
         <v>500006</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1">
         <v>500007</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1">
         <v>600000</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="1">
         <v>600001</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B34" s="1">
         <v>600002</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1">
         <v>600003</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/task.xlsx
+++ b/slots/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="909">
   <si>
     <t>任务ID</t>
   </si>
@@ -684,7 +684,7 @@
     <t>12001_100700_144000</t>
   </si>
   <si>
-    <t>tesk_100700.png</t>
+    <t>task_100700.png</t>
   </si>
   <si>
     <t>71001</t>
@@ -723,7 +723,7 @@
     <t>12001_100300_144000</t>
   </si>
   <si>
-    <t>tesk_100300.png</t>
+    <t>task_100300.png</t>
   </si>
   <si>
     <t>71002</t>
@@ -753,7 +753,7 @@
     <t>12001_101200_144000</t>
   </si>
   <si>
-    <t>tesk_101200.png</t>
+    <t>task_101200.png</t>
   </si>
   <si>
     <t>71003</t>
@@ -783,7 +783,7 @@
     <t>12001_101400_144000</t>
   </si>
   <si>
-    <t>tesk_101400.png</t>
+    <t>task_101400.png</t>
   </si>
   <si>
     <t>71004</t>
@@ -816,7 +816,7 @@
     <t>12001_0_144000</t>
   </si>
   <si>
-    <t>tesk_500007.png</t>
+    <t>task_500007.png</t>
   </si>
   <si>
     <t>71005</t>
@@ -852,7 +852,7 @@
     <t>12001_101700_144000</t>
   </si>
   <si>
-    <t>tesk_101700.png</t>
+    <t>task_101700.png</t>
   </si>
   <si>
     <t>71006</t>
@@ -885,7 +885,7 @@
     <t>12001_102100_144000</t>
   </si>
   <si>
-    <t>tesk_102100.png</t>
+    <t>task_102100.png</t>
   </si>
   <si>
     <t>71007</t>
@@ -918,7 +918,7 @@
     <t>12001_102200_144000</t>
   </si>
   <si>
-    <t>tesk_102200.png</t>
+    <t>task_102200.png</t>
   </si>
   <si>
     <t>71008</t>
@@ -948,7 +948,7 @@
     <t>12001_102300_144000</t>
   </si>
   <si>
-    <t>tesk_102300.png</t>
+    <t>task_102300.png</t>
   </si>
   <si>
     <t>71009</t>
@@ -981,7 +981,7 @@
     <t>12001_102400_144000</t>
   </si>
   <si>
-    <t>tesk_102400.png</t>
+    <t>task_102400.png</t>
   </si>
   <si>
     <t>71010</t>
@@ -1350,9 +1350,6 @@
     <t>12001_100700_4277000</t>
   </si>
   <si>
-    <t>task_100700.png</t>
-  </si>
-  <si>
     <t>71301</t>
   </si>
   <si>
@@ -1374,9 +1371,6 @@
     <t>12001_100300_4277000</t>
   </si>
   <si>
-    <t>task_100300.png</t>
-  </si>
-  <si>
     <t>71302</t>
   </si>
   <si>
@@ -1395,9 +1389,6 @@
     <t>12001_101200_4277000</t>
   </si>
   <si>
-    <t>task_101200.png</t>
-  </si>
-  <si>
     <t>71303</t>
   </si>
   <si>
@@ -1416,9 +1407,6 @@
     <t>12001_101400_4277000</t>
   </si>
   <si>
-    <t>task_101400.png</t>
-  </si>
-  <si>
     <t>71304</t>
   </si>
   <si>
@@ -1437,9 +1425,6 @@
     <t>12001_0_4277000</t>
   </si>
   <si>
-    <t>task_500007.png</t>
-  </si>
-  <si>
     <t>71305</t>
   </si>
   <si>
@@ -3097,21 +3082,6 @@
   </si>
   <si>
     <t>task_100100.png</t>
-  </si>
-  <si>
-    <t>task_101700.png</t>
-  </si>
-  <si>
-    <t>task_102100.png</t>
-  </si>
-  <si>
-    <t>task_102200.png</t>
-  </si>
-  <si>
-    <t>task_102300.png</t>
-  </si>
-  <si>
-    <t>task_102400.png</t>
   </si>
   <si>
     <t>寒冰王座</t>
@@ -4220,14 +4190,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7794,14 +7757,14 @@
         <v>11007</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>77</v>
@@ -7822,7 +7785,7 @@
         <v>4277000</v>
       </c>
       <c r="T41" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U41" s="61">
         <v>713</v>
@@ -7834,19 +7797,19 @@
         <v>80</v>
       </c>
       <c r="X41" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y41" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z41" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA41" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB41" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:28">
@@ -7863,7 +7826,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
@@ -7876,14 +7839,14 @@
         <v>11003</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N42" s="4" t="s">
         <v>77</v>
@@ -7904,7 +7867,7 @@
         <v>4277000</v>
       </c>
       <c r="T42" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U42" s="61">
         <v>713</v>
@@ -7916,19 +7879,19 @@
         <v>91</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Y42" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z42" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AA42" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:28">
@@ -7945,7 +7908,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
@@ -7958,14 +7921,14 @@
         <v>11012</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>77</v>
@@ -7986,7 +7949,7 @@
         <v>4277000</v>
       </c>
       <c r="T43" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U43" s="61">
         <v>713</v>
@@ -7998,19 +7961,19 @@
         <v>101</v>
       </c>
       <c r="X43" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Y43" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AA43" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:28">
@@ -8027,7 +7990,7 @@
         <v>4</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
@@ -8040,14 +8003,14 @@
         <v>11014</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N44" s="4" t="s">
         <v>77</v>
@@ -8068,7 +8031,7 @@
         <v>4277000</v>
       </c>
       <c r="T44" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U44" s="61">
         <v>713</v>
@@ -8080,19 +8043,19 @@
         <v>111</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Y44" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AA44" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" s="4" customFormat="1" spans="1:28">
@@ -8109,7 +8072,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
@@ -8122,14 +8085,14 @@
         <v>11003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>325</v>
+        <v>118</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N45" s="4" t="s">
         <v>121</v>
@@ -8150,7 +8113,7 @@
         <v>4277000</v>
       </c>
       <c r="T45" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U45" s="61">
         <v>713</v>
@@ -8162,19 +8125,19 @@
         <v>123</v>
       </c>
       <c r="X45" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="Y45" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AA45" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" s="4" customFormat="1" spans="1:28">
@@ -8191,7 +8154,7 @@
         <v>6</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
@@ -8211,7 +8174,7 @@
         <v>71306</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>121</v>
@@ -8232,7 +8195,7 @@
         <v>4277000</v>
       </c>
       <c r="T46" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U46" s="61">
         <v>713</v>
@@ -8244,19 +8207,19 @@
         <v>134</v>
       </c>
       <c r="X46" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="Y46" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AA46" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:28">
@@ -8273,7 +8236,7 @@
         <v>7</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
@@ -8293,7 +8256,7 @@
         <v>71307</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>121</v>
@@ -8314,7 +8277,7 @@
         <v>4277000</v>
       </c>
       <c r="T47" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U47" s="61">
         <v>713</v>
@@ -8326,19 +8289,19 @@
         <v>145</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="Y47" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AA47" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" s="4" customFormat="1" spans="1:28">
@@ -8355,7 +8318,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
@@ -8375,7 +8338,7 @@
         <v>71308</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>121</v>
@@ -8396,7 +8359,7 @@
         <v>4277000</v>
       </c>
       <c r="T48" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U48" s="61">
         <v>713</v>
@@ -8408,19 +8371,19 @@
         <v>156</v>
       </c>
       <c r="X48" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="Y48" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z48" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AA48" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" s="4" customFormat="1" spans="1:28">
@@ -8437,7 +8400,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="13">
@@ -8457,7 +8420,7 @@
         <v>71309</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>121</v>
@@ -8478,7 +8441,7 @@
         <v>4277000</v>
       </c>
       <c r="T49" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U49" s="61">
         <v>713</v>
@@ -8490,19 +8453,19 @@
         <v>166</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="Y49" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z49" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AA49" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" s="4" customFormat="1" spans="1:28">
@@ -8519,7 +8482,7 @@
         <v>10</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13">
@@ -8539,7 +8502,7 @@
         <v>71310</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>121</v>
@@ -8560,7 +8523,7 @@
         <v>4277000</v>
       </c>
       <c r="T50" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U50" s="61">
         <v>713</v>
@@ -8572,19 +8535,19 @@
         <v>177</v>
       </c>
       <c r="X50" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="Y50" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z50" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AA50" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" s="36" customFormat="1" spans="1:28">
@@ -8601,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F51" s="36"/>
       <c r="G51" s="13">
@@ -8614,14 +8577,14 @@
         <v>11007</v>
       </c>
       <c r="J51" s="47" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="K51" s="48"/>
       <c r="L51" s="48" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M51" s="36" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="N51" s="36" t="s">
         <v>77</v>
@@ -8642,7 +8605,7 @@
         <v>7128000</v>
       </c>
       <c r="T51" s="63" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U51" s="51">
         <v>1188</v>
@@ -8654,19 +8617,19 @@
         <v>80</v>
       </c>
       <c r="X51" s="36" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="Y51" s="36" t="s">
         <v>82</v>
       </c>
       <c r="Z51" s="36" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AA51" s="36" t="s">
         <v>84</v>
       </c>
       <c r="AB51" s="36" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" s="36" customFormat="1" spans="1:28">
@@ -8683,7 +8646,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F52" s="36"/>
       <c r="G52" s="13">
@@ -8696,14 +8659,14 @@
         <v>11003</v>
       </c>
       <c r="J52" s="47" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="K52" s="48"/>
       <c r="L52" s="48" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M52" s="36" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N52" s="36" t="s">
         <v>77</v>
@@ -8724,7 +8687,7 @@
         <v>7128000</v>
       </c>
       <c r="T52" s="63" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U52" s="51">
         <v>1188</v>
@@ -8736,19 +8699,19 @@
         <v>91</v>
       </c>
       <c r="X52" s="36" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="Y52" s="36" t="s">
         <v>93</v>
       </c>
       <c r="Z52" s="36" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AA52" s="36" t="s">
         <v>91</v>
       </c>
       <c r="AB52" s="36" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" s="36" customFormat="1" spans="1:28">
@@ -8765,7 +8728,7 @@
         <v>3</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F53" s="36"/>
       <c r="G53" s="13">
@@ -8778,14 +8741,14 @@
         <v>11012</v>
       </c>
       <c r="J53" s="47" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="K53" s="48"/>
       <c r="L53" s="48" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M53" s="36" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="N53" s="36" t="s">
         <v>77</v>
@@ -8806,7 +8769,7 @@
         <v>7128000</v>
       </c>
       <c r="T53" s="63" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U53" s="51">
         <v>1188</v>
@@ -8818,19 +8781,19 @@
         <v>101</v>
       </c>
       <c r="X53" s="36" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Y53" s="36" t="s">
         <v>103</v>
       </c>
       <c r="Z53" s="36" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AA53" s="36" t="s">
         <v>101</v>
       </c>
       <c r="AB53" s="36" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="54" s="36" customFormat="1" spans="1:28">
@@ -8847,7 +8810,7 @@
         <v>4</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="13">
@@ -8860,14 +8823,14 @@
         <v>11014</v>
       </c>
       <c r="J54" s="47" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="K54" s="48"/>
       <c r="L54" s="48" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="M54" s="36" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="N54" s="36" t="s">
         <v>77</v>
@@ -8888,7 +8851,7 @@
         <v>7128000</v>
       </c>
       <c r="T54" s="63" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U54" s="51">
         <v>1188</v>
@@ -8900,19 +8863,19 @@
         <v>111</v>
       </c>
       <c r="X54" s="36" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="Y54" s="36" t="s">
         <v>113</v>
       </c>
       <c r="Z54" s="36" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AA54" s="36" t="s">
         <v>115</v>
       </c>
       <c r="AB54" s="36" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" s="36" customFormat="1" spans="1:28">
@@ -8929,7 +8892,7 @@
         <v>5</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="13">
@@ -8942,14 +8905,14 @@
         <v>11003</v>
       </c>
       <c r="J55" s="47" t="s">
-        <v>325</v>
+        <v>118</v>
       </c>
       <c r="K55" s="48"/>
       <c r="L55" s="48" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="M55" s="36" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="N55" s="36" t="s">
         <v>121</v>
@@ -8970,7 +8933,7 @@
         <v>7128000</v>
       </c>
       <c r="T55" s="63" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U55" s="51">
         <v>1188</v>
@@ -8982,19 +8945,19 @@
         <v>123</v>
       </c>
       <c r="X55" s="36" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="Y55" s="36" t="s">
         <v>125</v>
       </c>
       <c r="Z55" s="36" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AA55" s="36" t="s">
         <v>127</v>
       </c>
       <c r="AB55" s="36" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" s="4" customFormat="1" spans="1:28">
@@ -9011,7 +8974,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="13">
@@ -9031,7 +8994,7 @@
         <v>71406</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="N56" s="4" t="s">
         <v>121</v>
@@ -9052,7 +9015,7 @@
         <v>7128000</v>
       </c>
       <c r="T56" s="62" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U56" s="4">
         <v>1188</v>
@@ -9064,19 +9027,19 @@
         <v>134</v>
       </c>
       <c r="X56" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="Y56" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z56" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA56" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB56" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" s="4" customFormat="1" spans="1:28">
@@ -9093,7 +9056,7 @@
         <v>7</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="13">
@@ -9113,7 +9076,7 @@
         <v>71407</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>121</v>
@@ -9134,7 +9097,7 @@
         <v>7128000</v>
       </c>
       <c r="T57" s="62" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U57" s="4">
         <v>1188</v>
@@ -9146,19 +9109,19 @@
         <v>145</v>
       </c>
       <c r="X57" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="Y57" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z57" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AA57" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB57" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" s="4" customFormat="1" spans="1:28">
@@ -9175,7 +9138,7 @@
         <v>8</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="13">
@@ -9195,7 +9158,7 @@
         <v>71408</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="N58" s="4" t="s">
         <v>121</v>
@@ -9216,7 +9179,7 @@
         <v>7128000</v>
       </c>
       <c r="T58" s="62" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U58" s="4">
         <v>1188</v>
@@ -9228,19 +9191,19 @@
         <v>156</v>
       </c>
       <c r="X58" s="4" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Y58" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z58" s="4" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA58" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB58" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" s="4" customFormat="1" spans="1:28">
@@ -9257,7 +9220,7 @@
         <v>9</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
@@ -9277,7 +9240,7 @@
         <v>71409</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>121</v>
@@ -9298,7 +9261,7 @@
         <v>7128000</v>
       </c>
       <c r="T59" s="62" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U59" s="4">
         <v>1188</v>
@@ -9310,19 +9273,19 @@
         <v>166</v>
       </c>
       <c r="X59" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="Y59" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z59" s="4" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA59" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB59" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" s="4" customFormat="1" spans="1:28">
@@ -9339,7 +9302,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
@@ -9359,7 +9322,7 @@
         <v>71410</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>121</v>
@@ -9380,7 +9343,7 @@
         <v>7128000</v>
       </c>
       <c r="T60" s="62" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U60" s="4">
         <v>1188</v>
@@ -9392,19 +9355,19 @@
         <v>177</v>
       </c>
       <c r="X60" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Y60" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z60" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AA60" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB60" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -9421,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G61" s="3">
         <v>67</v>
@@ -9433,16 +9396,16 @@
         <v>11007</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L61" s="39" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O61" s="3">
         <v>10003</v>
@@ -9460,7 +9423,7 @@
         <v>400000</v>
       </c>
       <c r="T61" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U61" s="3">
         <v>67</v>
@@ -9472,19 +9435,19 @@
         <v>80</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="Y61" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z61" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AA61" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB61" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -9501,7 +9464,7 @@
         <v>2</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G62" s="3">
         <v>67</v>
@@ -9513,16 +9476,16 @@
         <v>11003</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="L62" s="39" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O62" s="3">
         <v>10003</v>
@@ -9540,7 +9503,7 @@
         <v>400000</v>
       </c>
       <c r="T62" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U62" s="3">
         <v>67</v>
@@ -9552,19 +9515,19 @@
         <v>91</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Y62" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AA62" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB62" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -9581,7 +9544,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G63" s="3">
         <v>67</v>
@@ -9593,16 +9556,16 @@
         <v>11012</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="L63" s="39" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O63" s="3">
         <v>10003</v>
@@ -9620,7 +9583,7 @@
         <v>400000</v>
       </c>
       <c r="T63" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U63" s="3">
         <v>67</v>
@@ -9632,19 +9595,19 @@
         <v>101</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="Y63" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AA63" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB63" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -9661,7 +9624,7 @@
         <v>4</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G64" s="3">
         <v>67</v>
@@ -9673,16 +9636,16 @@
         <v>11014</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L64" s="39" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O64" s="3">
         <v>10003</v>
@@ -9700,7 +9663,7 @@
         <v>400000</v>
       </c>
       <c r="T64" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U64" s="3">
         <v>67</v>
@@ -9712,19 +9675,19 @@
         <v>111</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Y64" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z64" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AA64" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB64" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="65" spans="1:28">
@@ -9741,7 +9704,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G65" s="3">
         <v>67</v>
@@ -9753,13 +9716,13 @@
         <v>11003</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L65" s="39" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>121</v>
@@ -9768,7 +9731,7 @@
         <v>10003</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Q65" s="3">
         <v>0</v>
@@ -9780,7 +9743,7 @@
         <v>400000</v>
       </c>
       <c r="T65" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U65" s="3">
         <v>67</v>
@@ -9792,19 +9755,19 @@
         <v>123</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="Y65" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z65" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AA65" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB65" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66" spans="1:28">
@@ -9821,7 +9784,7 @@
         <v>6</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G66" s="3">
         <v>67</v>
@@ -9839,10 +9802,10 @@
         <v>72006</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O66" s="3">
         <v>10003</v>
@@ -9860,7 +9823,7 @@
         <v>400000</v>
       </c>
       <c r="T66" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U66" s="3">
         <v>67</v>
@@ -9872,19 +9835,19 @@
         <v>134</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Y66" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z66" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AA66" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB66" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -9901,7 +9864,7 @@
         <v>7</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="G67" s="3">
         <v>67</v>
@@ -9919,10 +9882,10 @@
         <v>72007</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O67" s="3">
         <v>10003</v>
@@ -9940,7 +9903,7 @@
         <v>400000</v>
       </c>
       <c r="T67" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U67" s="3">
         <v>67</v>
@@ -9952,19 +9915,19 @@
         <v>145</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Y67" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z67" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AA67" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB67" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="68" spans="1:28">
@@ -9981,7 +9944,7 @@
         <v>8</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G68" s="3">
         <v>67</v>
@@ -9999,10 +9962,10 @@
         <v>72008</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O68" s="3">
         <v>10003</v>
@@ -10020,7 +9983,7 @@
         <v>400000</v>
       </c>
       <c r="T68" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U68" s="3">
         <v>67</v>
@@ -10032,19 +9995,19 @@
         <v>156</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="Y68" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z68" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AA68" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB68" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="69" spans="1:28">
@@ -10061,7 +10024,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G69" s="3">
         <v>67</v>
@@ -10079,10 +10042,10 @@
         <v>72009</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O69" s="3">
         <v>10003</v>
@@ -10100,7 +10063,7 @@
         <v>400000</v>
       </c>
       <c r="T69" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U69" s="3">
         <v>67</v>
@@ -10112,19 +10075,19 @@
         <v>166</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="Y69" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z69" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AA69" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB69" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -10141,7 +10104,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="G70" s="3">
         <v>67</v>
@@ -10159,10 +10122,10 @@
         <v>72010</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O70" s="3">
         <v>10003</v>
@@ -10180,7 +10143,7 @@
         <v>400000</v>
       </c>
       <c r="T70" s="65" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="U70" s="3">
         <v>67</v>
@@ -10192,19 +10155,19 @@
         <v>177</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="Y70" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z70" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AA70" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB70" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -10221,7 +10184,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G71" s="3">
         <v>133</v>
@@ -10233,16 +10196,16 @@
         <v>11007</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L71" s="39" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O71" s="3">
         <v>10003</v>
@@ -10260,7 +10223,7 @@
         <v>800000</v>
       </c>
       <c r="T71" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U71" s="3">
         <v>133</v>
@@ -10272,19 +10235,19 @@
         <v>80</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="Y71" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z71" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AA71" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB71" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" spans="1:28">
@@ -10301,7 +10264,7 @@
         <v>2</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G72" s="3">
         <v>133</v>
@@ -10313,16 +10276,16 @@
         <v>11003</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="L72" s="39" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O72" s="3">
         <v>10003</v>
@@ -10340,7 +10303,7 @@
         <v>800000</v>
       </c>
       <c r="T72" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U72" s="3">
         <v>133</v>
@@ -10352,19 +10315,19 @@
         <v>91</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="Y72" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z72" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AA72" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB72" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -10381,7 +10344,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G73" s="3">
         <v>133</v>
@@ -10393,16 +10356,16 @@
         <v>11012</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="L73" s="39" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O73" s="3">
         <v>10003</v>
@@ -10420,7 +10383,7 @@
         <v>800000</v>
       </c>
       <c r="T73" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U73" s="3">
         <v>133</v>
@@ -10432,19 +10395,19 @@
         <v>101</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="Y73" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z73" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="AA73" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB73" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" spans="1:28">
@@ -10461,7 +10424,7 @@
         <v>4</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G74" s="3">
         <v>133</v>
@@ -10473,16 +10436,16 @@
         <v>11014</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L74" s="39" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O74" s="3">
         <v>10003</v>
@@ -10500,7 +10463,7 @@
         <v>800000</v>
       </c>
       <c r="T74" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U74" s="3">
         <v>133</v>
@@ -10512,19 +10475,19 @@
         <v>111</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="Y74" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z74" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AA74" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB74" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="75" spans="1:28">
@@ -10541,7 +10504,7 @@
         <v>5</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G75" s="3">
         <v>133</v>
@@ -10553,13 +10516,13 @@
         <v>11003</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L75" s="39" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>121</v>
@@ -10568,7 +10531,7 @@
         <v>10003</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Q75" s="3">
         <v>0</v>
@@ -10580,7 +10543,7 @@
         <v>800000</v>
       </c>
       <c r="T75" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U75" s="3">
         <v>133</v>
@@ -10592,19 +10555,19 @@
         <v>123</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="Y75" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z75" s="3" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA75" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB75" s="3" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="76" spans="1:28">
@@ -10621,7 +10584,7 @@
         <v>6</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="G76" s="3">
         <v>133</v>
@@ -10639,10 +10602,10 @@
         <v>72206</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O76" s="3">
         <v>10003</v>
@@ -10660,7 +10623,7 @@
         <v>800000</v>
       </c>
       <c r="T76" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U76" s="3">
         <v>133</v>
@@ -10672,19 +10635,19 @@
         <v>134</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="Y76" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z76" s="3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="AA76" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB76" s="3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="77" spans="1:28">
@@ -10701,7 +10664,7 @@
         <v>7</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="G77" s="3">
         <v>133</v>
@@ -10719,10 +10682,10 @@
         <v>72207</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O77" s="3">
         <v>10003</v>
@@ -10740,7 +10703,7 @@
         <v>800000</v>
       </c>
       <c r="T77" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U77" s="3">
         <v>133</v>
@@ -10752,19 +10715,19 @@
         <v>145</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Y77" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z77" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AA77" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB77" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:28">
@@ -10781,7 +10744,7 @@
         <v>8</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="G78" s="3">
         <v>133</v>
@@ -10799,10 +10762,10 @@
         <v>72208</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O78" s="3">
         <v>10003</v>
@@ -10820,7 +10783,7 @@
         <v>800000</v>
       </c>
       <c r="T78" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U78" s="3">
         <v>133</v>
@@ -10832,19 +10795,19 @@
         <v>156</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="Y78" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z78" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AA78" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB78" s="3" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="79" spans="1:28">
@@ -10861,7 +10824,7 @@
         <v>9</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="G79" s="3">
         <v>133</v>
@@ -10879,10 +10842,10 @@
         <v>72209</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O79" s="3">
         <v>10003</v>
@@ -10900,7 +10863,7 @@
         <v>800000</v>
       </c>
       <c r="T79" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U79" s="3">
         <v>133</v>
@@ -10912,19 +10875,19 @@
         <v>166</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Y79" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z79" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AA79" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB79" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="80" spans="1:28">
@@ -10941,7 +10904,7 @@
         <v>10</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="G80" s="3">
         <v>133</v>
@@ -10959,10 +10922,10 @@
         <v>72210</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O80" s="3">
         <v>10003</v>
@@ -10980,7 +10943,7 @@
         <v>800000</v>
       </c>
       <c r="T80" s="65" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="U80" s="3">
         <v>133</v>
@@ -10992,19 +10955,19 @@
         <v>177</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Y80" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z80" s="3" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AA80" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB80" s="3" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:28">
@@ -11021,7 +10984,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="G81" s="3">
         <v>333</v>
@@ -11033,16 +10996,16 @@
         <v>11007</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L81" s="39" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O81" s="3">
         <v>10003</v>
@@ -11060,7 +11023,7 @@
         <v>2000000</v>
       </c>
       <c r="T81" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U81" s="3">
         <v>333</v>
@@ -11072,19 +11035,19 @@
         <v>80</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="Y81" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z81" s="3" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AA81" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB81" s="3" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82" spans="1:28">
@@ -11101,7 +11064,7 @@
         <v>2</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="G82" s="3">
         <v>333</v>
@@ -11113,16 +11076,16 @@
         <v>11003</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="L82" s="39" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O82" s="3">
         <v>10003</v>
@@ -11140,7 +11103,7 @@
         <v>2000000</v>
       </c>
       <c r="T82" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U82" s="3">
         <v>333</v>
@@ -11152,19 +11115,19 @@
         <v>91</v>
       </c>
       <c r="X82" s="3" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="Y82" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z82" s="3" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AA82" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB82" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="83" spans="1:28">
@@ -11181,7 +11144,7 @@
         <v>3</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="G83" s="3">
         <v>333</v>
@@ -11193,16 +11156,16 @@
         <v>11012</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="L83" s="39" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O83" s="3">
         <v>10003</v>
@@ -11220,7 +11183,7 @@
         <v>2000000</v>
       </c>
       <c r="T83" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U83" s="3">
         <v>333</v>
@@ -11232,19 +11195,19 @@
         <v>101</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="Y83" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z83" s="3" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AA83" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB83" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="84" spans="1:28">
@@ -11261,7 +11224,7 @@
         <v>4</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G84" s="3">
         <v>333</v>
@@ -11273,16 +11236,16 @@
         <v>11014</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L84" s="39" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O84" s="3">
         <v>10003</v>
@@ -11300,7 +11263,7 @@
         <v>2000000</v>
       </c>
       <c r="T84" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U84" s="3">
         <v>333</v>
@@ -11312,19 +11275,19 @@
         <v>111</v>
       </c>
       <c r="X84" s="3" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="Y84" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z84" s="3" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AA84" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB84" s="3" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="85" spans="1:28">
@@ -11341,7 +11304,7 @@
         <v>5</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G85" s="3">
         <v>333</v>
@@ -11353,13 +11316,13 @@
         <v>11003</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L85" s="39" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>121</v>
@@ -11368,7 +11331,7 @@
         <v>10003</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Q85" s="3">
         <v>0</v>
@@ -11380,7 +11343,7 @@
         <v>2000000</v>
       </c>
       <c r="T85" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U85" s="3">
         <v>333</v>
@@ -11392,19 +11355,19 @@
         <v>123</v>
       </c>
       <c r="X85" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="Y85" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z85" s="3" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AA85" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB85" s="3" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="86" spans="1:28">
@@ -11421,7 +11384,7 @@
         <v>6</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G86" s="3">
         <v>333</v>
@@ -11439,10 +11402,10 @@
         <v>72306</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O86" s="3">
         <v>10003</v>
@@ -11460,7 +11423,7 @@
         <v>2000000</v>
       </c>
       <c r="T86" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U86" s="3">
         <v>333</v>
@@ -11472,19 +11435,19 @@
         <v>134</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="Y86" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z86" s="3" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="AA86" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB86" s="3" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="87" spans="1:28">
@@ -11501,7 +11464,7 @@
         <v>7</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="G87" s="3">
         <v>333</v>
@@ -11519,10 +11482,10 @@
         <v>72307</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O87" s="3">
         <v>10003</v>
@@ -11540,7 +11503,7 @@
         <v>2000000</v>
       </c>
       <c r="T87" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U87" s="3">
         <v>333</v>
@@ -11552,19 +11515,19 @@
         <v>145</v>
       </c>
       <c r="X87" s="3" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="Y87" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z87" s="3" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AA87" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB87" s="3" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="88" spans="1:28">
@@ -11581,7 +11544,7 @@
         <v>8</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G88" s="3">
         <v>333</v>
@@ -11599,10 +11562,10 @@
         <v>72308</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O88" s="3">
         <v>10003</v>
@@ -11620,7 +11583,7 @@
         <v>2000000</v>
       </c>
       <c r="T88" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U88" s="3">
         <v>333</v>
@@ -11632,19 +11595,19 @@
         <v>156</v>
       </c>
       <c r="X88" s="3" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="Y88" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z88" s="3" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AA88" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB88" s="3" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="89" spans="1:28">
@@ -11661,7 +11624,7 @@
         <v>9</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G89" s="3">
         <v>333</v>
@@ -11679,10 +11642,10 @@
         <v>72309</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O89" s="3">
         <v>10003</v>
@@ -11700,7 +11663,7 @@
         <v>2000000</v>
       </c>
       <c r="T89" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U89" s="3">
         <v>333</v>
@@ -11712,19 +11675,19 @@
         <v>166</v>
       </c>
       <c r="X89" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="Y89" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z89" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="AA89" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB89" s="3" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:28">
@@ -11741,7 +11704,7 @@
         <v>10</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G90" s="3">
         <v>333</v>
@@ -11759,10 +11722,10 @@
         <v>72310</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O90" s="3">
         <v>10003</v>
@@ -11780,7 +11743,7 @@
         <v>2000000</v>
       </c>
       <c r="T90" s="65" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="U90" s="3">
         <v>333</v>
@@ -11792,19 +11755,19 @@
         <v>177</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="Y90" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AA90" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB90" s="3" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="91" spans="1:28">
@@ -11821,7 +11784,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G91" s="3">
         <v>667</v>
@@ -11833,16 +11796,16 @@
         <v>11007</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L91" s="39" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O91" s="3">
         <v>10003</v>
@@ -11860,7 +11823,7 @@
         <v>4000000</v>
       </c>
       <c r="T91" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U91" s="3">
         <v>667</v>
@@ -11872,19 +11835,19 @@
         <v>80</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="Y91" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z91" s="3" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="AA91" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB91" s="3" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92" spans="1:28">
@@ -11901,7 +11864,7 @@
         <v>2</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G92" s="3">
         <v>667</v>
@@ -11913,16 +11876,16 @@
         <v>11003</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="L92" s="39" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O92" s="3">
         <v>10003</v>
@@ -11940,7 +11903,7 @@
         <v>4000000</v>
       </c>
       <c r="T92" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U92" s="3">
         <v>667</v>
@@ -11952,19 +11915,19 @@
         <v>91</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="Y92" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z92" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AA92" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB92" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="93" spans="1:28">
@@ -11981,7 +11944,7 @@
         <v>3</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G93" s="3">
         <v>667</v>
@@ -11993,16 +11956,16 @@
         <v>11012</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="L93" s="39" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O93" s="3">
         <v>10003</v>
@@ -12020,7 +11983,7 @@
         <v>4000000</v>
       </c>
       <c r="T93" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U93" s="3">
         <v>667</v>
@@ -12032,19 +11995,19 @@
         <v>101</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="Y93" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z93" s="3" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AA93" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB93" s="3" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="94" spans="1:28">
@@ -12061,7 +12024,7 @@
         <v>4</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="G94" s="3">
         <v>667</v>
@@ -12073,16 +12036,16 @@
         <v>11014</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L94" s="39" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O94" s="3">
         <v>10003</v>
@@ -12100,7 +12063,7 @@
         <v>4000000</v>
       </c>
       <c r="T94" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U94" s="3">
         <v>667</v>
@@ -12112,19 +12075,19 @@
         <v>111</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="Y94" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z94" s="3" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="AA94" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB94" s="3" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="95" spans="1:28">
@@ -12141,7 +12104,7 @@
         <v>5</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G95" s="3">
         <v>667</v>
@@ -12153,13 +12116,13 @@
         <v>11003</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L95" s="39" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>121</v>
@@ -12168,7 +12131,7 @@
         <v>10003</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Q95" s="3">
         <v>0</v>
@@ -12180,7 +12143,7 @@
         <v>4000000</v>
       </c>
       <c r="T95" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U95" s="3">
         <v>667</v>
@@ -12192,19 +12155,19 @@
         <v>123</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="Y95" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z95" s="3" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AA95" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB95" s="3" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="96" spans="1:28">
@@ -12221,7 +12184,7 @@
         <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G96" s="3">
         <v>667</v>
@@ -12239,10 +12202,10 @@
         <v>72406</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O96" s="3">
         <v>10003</v>
@@ -12260,7 +12223,7 @@
         <v>4000000</v>
       </c>
       <c r="T96" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U96" s="3">
         <v>667</v>
@@ -12272,19 +12235,19 @@
         <v>134</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="Y96" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z96" s="3" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="AA96" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB96" s="3" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="97" spans="1:28">
@@ -12301,7 +12264,7 @@
         <v>7</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="G97" s="3">
         <v>667</v>
@@ -12319,10 +12282,10 @@
         <v>72407</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O97" s="3">
         <v>10003</v>
@@ -12340,7 +12303,7 @@
         <v>4000000</v>
       </c>
       <c r="T97" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U97" s="3">
         <v>667</v>
@@ -12352,19 +12315,19 @@
         <v>145</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="Y97" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z97" s="3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="AA97" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB97" s="3" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98" spans="1:28">
@@ -12381,7 +12344,7 @@
         <v>8</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G98" s="3">
         <v>667</v>
@@ -12399,10 +12362,10 @@
         <v>72408</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O98" s="3">
         <v>10003</v>
@@ -12420,7 +12383,7 @@
         <v>4000000</v>
       </c>
       <c r="T98" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U98" s="3">
         <v>667</v>
@@ -12432,19 +12395,19 @@
         <v>156</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="Y98" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z98" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="AA98" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB98" s="3" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="99" spans="1:28">
@@ -12461,7 +12424,7 @@
         <v>9</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G99" s="3">
         <v>667</v>
@@ -12479,10 +12442,10 @@
         <v>72409</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O99" s="3">
         <v>10003</v>
@@ -12500,7 +12463,7 @@
         <v>4000000</v>
       </c>
       <c r="T99" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U99" s="3">
         <v>667</v>
@@ -12512,19 +12475,19 @@
         <v>166</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="Y99" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z99" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="AA99" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB99" s="3" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
     <row r="100" spans="1:28">
@@ -12541,7 +12504,7 @@
         <v>10</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="G100" s="3">
         <v>667</v>
@@ -12559,10 +12522,10 @@
         <v>72410</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O100" s="3">
         <v>10003</v>
@@ -12580,7 +12543,7 @@
         <v>4000000</v>
       </c>
       <c r="T100" s="65" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="U100" s="3">
         <v>667</v>
@@ -12592,19 +12555,19 @@
         <v>177</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="Y100" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z100" s="3" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="AA100" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB100" s="3" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="101" spans="1:28">
@@ -12621,7 +12584,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G101" s="3">
         <v>300</v>
@@ -12633,16 +12596,16 @@
         <v>11007</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L101" s="39" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O101" s="3">
         <v>10001</v>
@@ -12660,7 +12623,7 @@
         <v>1000</v>
       </c>
       <c r="T101" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U101" s="3">
         <v>300</v>
@@ -12672,19 +12635,19 @@
         <v>80</v>
       </c>
       <c r="X101" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="Y101" s="41" t="s">
         <v>82</v>
       </c>
       <c r="Z101" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="AA101" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AB101" s="3" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="102" spans="1:28">
@@ -12701,7 +12664,7 @@
         <v>2</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="G102" s="3">
         <v>300</v>
@@ -12713,16 +12676,16 @@
         <v>11003</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="L102" s="39" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O102" s="3">
         <v>10001</v>
@@ -12740,7 +12703,7 @@
         <v>1000</v>
       </c>
       <c r="T102" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U102" s="3">
         <v>300</v>
@@ -12752,19 +12715,19 @@
         <v>91</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="Y102" s="41" t="s">
         <v>93</v>
       </c>
       <c r="Z102" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="AA102" s="41" t="s">
         <v>91</v>
       </c>
       <c r="AB102" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="103" spans="1:28">
@@ -12781,7 +12744,7 @@
         <v>3</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="G103" s="3">
         <v>300</v>
@@ -12793,16 +12756,16 @@
         <v>11012</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="L103" s="39" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O103" s="3">
         <v>10001</v>
@@ -12820,7 +12783,7 @@
         <v>1000</v>
       </c>
       <c r="T103" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U103" s="3">
         <v>300</v>
@@ -12832,19 +12795,19 @@
         <v>101</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="Y103" s="41" t="s">
         <v>103</v>
       </c>
       <c r="Z103" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="AA103" s="41" t="s">
         <v>101</v>
       </c>
       <c r="AB103" s="3" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="104" spans="1:28">
@@ -12861,7 +12824,7 @@
         <v>4</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G104" s="3">
         <v>300</v>
@@ -12873,16 +12836,16 @@
         <v>11014</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L104" s="39" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O104" s="3">
         <v>10001</v>
@@ -12900,7 +12863,7 @@
         <v>1000</v>
       </c>
       <c r="T104" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U104" s="3">
         <v>300</v>
@@ -12912,19 +12875,19 @@
         <v>111</v>
       </c>
       <c r="X104" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="Y104" s="41" t="s">
         <v>113</v>
       </c>
       <c r="Z104" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="AA104" s="41" t="s">
         <v>115</v>
       </c>
       <c r="AB104" s="3" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="105" spans="1:28">
@@ -12941,7 +12904,7 @@
         <v>5</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G105" s="3">
         <v>300</v>
@@ -12953,16 +12916,16 @@
         <v>11003</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="L105" s="39" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="O105" s="3">
         <v>10001</v>
@@ -12977,7 +12940,7 @@
         <v>1000</v>
       </c>
       <c r="T105" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U105" s="3">
         <v>300</v>
@@ -12989,19 +12952,19 @@
         <v>123</v>
       </c>
       <c r="X105" s="3" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="Y105" s="41" t="s">
         <v>125</v>
       </c>
       <c r="Z105" s="3" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="AA105" s="41" t="s">
         <v>127</v>
       </c>
       <c r="AB105" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="106" spans="1:28">
@@ -13018,7 +12981,7 @@
         <v>6</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="G106" s="3">
         <v>300</v>
@@ -13036,10 +12999,10 @@
         <v>73006</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O106" s="3">
         <v>12001</v>
@@ -13057,7 +13020,7 @@
         <v>1000</v>
       </c>
       <c r="T106" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U106" s="3">
         <v>300</v>
@@ -13069,19 +13032,19 @@
         <v>134</v>
       </c>
       <c r="X106" s="3" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="Y106" s="41" t="s">
         <v>136</v>
       </c>
       <c r="Z106" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="AA106" s="41" t="s">
         <v>138</v>
       </c>
       <c r="AB106" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="107" spans="1:28">
@@ -13098,7 +13061,7 @@
         <v>7</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="G107" s="3">
         <v>300</v>
@@ -13116,10 +13079,10 @@
         <v>73007</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O107" s="3">
         <v>12001</v>
@@ -13137,7 +13100,7 @@
         <v>1000</v>
       </c>
       <c r="T107" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U107" s="3">
         <v>300</v>
@@ -13149,19 +13112,19 @@
         <v>145</v>
       </c>
       <c r="X107" s="3" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="Y107" s="41" t="s">
         <v>147</v>
       </c>
       <c r="Z107" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="AA107" s="41" t="s">
         <v>149</v>
       </c>
       <c r="AB107" s="3" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="108" spans="1:28">
@@ -13178,7 +13141,7 @@
         <v>8</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="G108" s="3">
         <v>300</v>
@@ -13196,10 +13159,10 @@
         <v>73008</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O108" s="3">
         <v>12001</v>
@@ -13217,7 +13180,7 @@
         <v>1000</v>
       </c>
       <c r="T108" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U108" s="3">
         <v>300</v>
@@ -13229,19 +13192,19 @@
         <v>156</v>
       </c>
       <c r="X108" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="Y108" s="41" t="s">
         <v>158</v>
       </c>
       <c r="Z108" s="3" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="AA108" s="41" t="s">
         <v>156</v>
       </c>
       <c r="AB108" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="109" spans="1:28">
@@ -13258,7 +13221,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G109" s="3">
         <v>300</v>
@@ -13276,10 +13239,10 @@
         <v>73009</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O109" s="3">
         <v>12001</v>
@@ -13297,7 +13260,7 @@
         <v>1000</v>
       </c>
       <c r="T109" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U109" s="3">
         <v>300</v>
@@ -13309,19 +13272,19 @@
         <v>166</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="Y109" s="41" t="s">
         <v>168</v>
       </c>
       <c r="Z109" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="AA109" s="41" t="s">
         <v>170</v>
       </c>
       <c r="AB109" s="3" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="110" spans="1:28">
@@ -13338,7 +13301,7 @@
         <v>10</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G110" s="3">
         <v>300</v>
@@ -13356,10 +13319,10 @@
         <v>73010</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O110" s="3">
         <v>12001</v>
@@ -13377,7 +13340,7 @@
         <v>1000</v>
       </c>
       <c r="T110" s="65" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="U110" s="3">
         <v>300</v>
@@ -13389,19 +13352,19 @@
         <v>177</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="Y110" s="41" t="s">
         <v>179</v>
       </c>
       <c r="Z110" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="AA110" s="41" t="s">
         <v>181</v>
       </c>
       <c r="AB110" s="3" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -13409,7 +13372,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L$1:L$1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -13442,16 +13405,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="18" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="J5" s="19">
         <v>502</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -13462,32 +13425,32 @@
         <v>10</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="L6" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="N6" s="24" t="s">
         <v>701</v>
       </c>
-      <c r="N6" s="24" t="s">
-        <v>706</v>
-      </c>
       <c r="O6" s="24" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -13495,37 +13458,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="F7" s="18">
         <v>100100</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="J7" s="18">
         <v>2</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="N7" s="18">
         <v>1022501</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -13533,37 +13496,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="F8" s="18">
         <v>100300</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="J8" s="18">
         <v>3</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="N8" s="18">
         <v>1022502</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -13571,37 +13534,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F9" s="18">
         <v>100700</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="J9" s="18">
         <v>4</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="N9" s="18">
         <v>1010301</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -13609,37 +13572,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="F10" s="18">
         <v>101200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="J10" s="18">
         <v>5</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N10" s="18">
         <v>1010302</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -13647,37 +13610,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F11" s="18">
         <v>101400</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="J11" s="18">
         <v>6</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="N11" s="18">
         <v>1010303</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -13685,37 +13648,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="F12" s="18">
         <v>200100</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="J12" s="25">
         <v>12</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="N12" s="18">
         <v>1010311</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -13723,19 +13686,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F13" s="18">
         <v>200101</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -13744,10 +13707,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -13755,19 +13718,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="F14" s="18">
         <v>200300</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -13776,10 +13739,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -13787,28 +13750,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F15" s="18">
         <v>200400</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="N15" s="18">
         <v>1010314</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -13816,28 +13779,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="F16" s="18">
         <v>200500</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="N16" s="18">
         <v>1010315</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -13845,19 +13808,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F17" s="18">
         <v>200600</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -13865,19 +13828,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="F18" s="18">
         <v>200700</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -13885,22 +13848,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="F19" s="18">
         <v>200800</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -13908,28 +13871,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="F20" s="18">
         <v>200900</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -13937,28 +13900,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="F21" s="18">
         <v>201000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="N21" s="18">
         <v>1022501</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -13966,28 +13929,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="F22" s="18">
         <v>300100</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="N22" s="18">
         <v>1022502</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -13995,19 +13958,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="N23" s="18">
         <v>1980000</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -14015,10 +13978,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -14026,10 +13989,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -14037,10 +14000,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -14048,10 +14011,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -14059,10 +14022,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="18" t="s">
+        <v>773</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>778</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -14070,10 +14033,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -14081,10 +14044,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -14092,10 +14055,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -14103,10 +14066,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -14114,10 +14077,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:22">
@@ -14132,7 +14095,7 @@
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>4</v>
@@ -14159,19 +14122,19 @@
         <v>11</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:22">
@@ -14275,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
@@ -14288,23 +14251,23 @@
         <v>3002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
         <v>70008</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="O42" s="4">
         <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -14340,7 +14303,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
@@ -14353,23 +14316,23 @@
         <v>3002</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="O43" s="4">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="Q43">
         <v>0.25</v>
@@ -14405,7 +14368,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
@@ -14418,23 +14381,23 @@
         <v>3002</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="O44" s="4">
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="Q44">
         <v>0.25</v>
@@ -14469,7 +14432,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
@@ -14482,17 +14445,17 @@
         <v>2003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
         <v>31</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="O45" s="4">
         <v>2</v>
@@ -14531,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
@@ -14544,17 +14507,17 @@
         <v>2003</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
         <v>184</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -14593,7 +14556,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
@@ -14606,17 +14569,17 @@
         <v>2003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
         <v>191</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -14655,7 +14618,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
@@ -14668,17 +14631,17 @@
         <v>2003</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
         <v>197</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="O48" s="4">
         <v>1</v>
@@ -14722,7 +14685,7 @@
         <v>70001</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -14732,7 +14695,7 @@
         <v>70002</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -14742,7 +14705,7 @@
         <v>70003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -14752,7 +14715,7 @@
         <v>70004</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -14762,10 +14725,10 @@
         <v>70005</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L5" s="10">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14777,10 +14740,10 @@
         <v>70006</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L6" s="10">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14792,10 +14755,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L7" s="10">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14807,10 +14770,10 @@
         <v>70008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L8" s="10">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14822,10 +14785,10 @@
         <v>70009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L9" s="10">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14837,10 +14800,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L10" s="10">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14852,10 +14815,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L11" s="10">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14867,10 +14830,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="L12" s="10">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14882,10 +14845,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="L13" s="10">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14897,7 +14860,7 @@
         <v>70104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>78</v>
@@ -14912,7 +14875,7 @@
         <v>70301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>90</v>
@@ -14927,10 +14890,10 @@
         <v>70302</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="L16" s="10">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -14942,7 +14905,7 @@
         <v>70303</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>90</v>
@@ -14957,7 +14920,7 @@
         <v>70304</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>90</v>
@@ -14972,7 +14935,7 @@
         <v>70305</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>90</v>
@@ -14987,7 +14950,7 @@
         <v>70306</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>78</v>
@@ -15002,7 +14965,7 @@
         <v>70307</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>78</v>
@@ -15017,7 +14980,7 @@
         <v>70308</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>78</v>
@@ -15032,7 +14995,7 @@
         <v>70309</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>100</v>
@@ -15047,7 +15010,7 @@
         <v>70310</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>100</v>
@@ -15062,7 +15025,7 @@
         <v>70311</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>100</v>
@@ -15077,7 +15040,7 @@
         <v>70312</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>110</v>
@@ -15092,7 +15055,7 @@
         <v>70381</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>110</v>
@@ -15107,7 +15070,7 @@
         <v>70382</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="K28" s="10" t="s">
         <v>110</v>
@@ -15122,7 +15085,7 @@
         <v>70383</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>100</v>
@@ -15137,7 +15100,7 @@
         <v>70391</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="K30" s="10" t="s">
         <v>100</v>
@@ -15152,7 +15115,7 @@
         <v>70392</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>100</v>
@@ -15167,7 +15130,7 @@
         <v>70393</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>100</v>
@@ -15182,10 +15145,10 @@
         <v>71101</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="L33" s="10">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15197,10 +15160,10 @@
         <v>71102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="L34" s="10">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15212,10 +15175,10 @@
         <v>71103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="L35" s="10">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15227,10 +15190,10 @@
         <v>71201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="L36" s="10">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15242,10 +15205,10 @@
         <v>71202</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L37" s="10">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15257,10 +15220,10 @@
         <v>72011</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L38" s="10">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15272,10 +15235,10 @@
         <v>72012</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L39" s="10">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15287,10 +15250,10 @@
         <v>72101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="L40" s="10">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -15302,7 +15265,7 @@
         <v>72102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>90</v>
@@ -15433,7 +15396,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
@@ -15446,17 +15409,17 @@
         <v>2001</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8">
         <v>70007</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
@@ -15492,7 +15455,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
@@ -15505,17 +15468,17 @@
         <v>2001</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="O60" s="3">
         <v>7000</v>
@@ -15553,7 +15516,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13">
@@ -15566,17 +15529,17 @@
         <v>2001</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="O61" s="3">
         <v>70000</v>
@@ -15614,7 +15577,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="13">
@@ -15627,17 +15590,17 @@
         <v>2001</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="O62" s="3">
         <v>700000</v>
@@ -15674,7 +15637,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="15">
@@ -15687,16 +15650,16 @@
         <v>2002</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L63" s="16">
         <v>70007</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="P63" s="4"/>
     </row>
@@ -15715,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F65" s="14"/>
       <c r="G65" s="15">
@@ -15728,16 +15691,16 @@
         <v>1001</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="L65" s="16">
         <v>70001</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="V65" s="4">
         <f>ROUND(MAX(S65/100,T65/100,U65),0)</f>
@@ -15759,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="15">
@@ -15772,16 +15735,16 @@
         <v>2001</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L66" s="16">
         <v>70002</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:22">
@@ -15799,7 +15762,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="15">
@@ -15812,16 +15775,16 @@
         <v>2002</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L67" s="16">
         <v>70003</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:22">
@@ -15839,7 +15802,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F68" s="14"/>
       <c r="G68" s="15">
@@ -15852,16 +15815,16 @@
         <v>2003</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L68" s="16">
         <v>70004</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:22">
@@ -15879,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="15">
@@ -15892,16 +15855,16 @@
         <v>1001</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L69" s="16">
         <v>70005</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="N69" s="17"/>
     </row>
@@ -15920,7 +15883,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F70" s="14"/>
       <c r="G70" s="15">
@@ -15933,16 +15896,16 @@
         <v>2001</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L70" s="16">
         <v>70006</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="N70" s="17"/>
     </row>
@@ -15961,7 +15924,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="15">
@@ -15974,16 +15937,16 @@
         <v>2003</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L71" s="16">
         <v>70008</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="N71" s="17"/>
     </row>
@@ -16002,7 +15965,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="15">
@@ -16015,16 +15978,16 @@
         <v>1001</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L72" s="16">
         <v>70009</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="N72" s="17"/>
     </row>
@@ -16043,7 +16006,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="15">
@@ -16056,16 +16019,16 @@
         <v>2001</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="L73" s="16">
         <v>70010</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -16095,18 +16058,18 @@
         <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B2" s="1">
         <v>100100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -16117,7 +16080,7 @@
         <v>100300</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -16128,7 +16091,7 @@
         <v>100700</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -16139,7 +16102,7 @@
         <v>101200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -16150,7 +16113,7 @@
         <v>101400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -16161,7 +16124,7 @@
         <v>101700</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>879</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -16172,7 +16135,7 @@
         <v>102100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>880</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -16183,7 +16146,7 @@
         <v>102200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>881</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -16194,7 +16157,7 @@
         <v>102300</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>882</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -16205,150 +16168,150 @@
         <v>102400</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>883</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="B12" s="1">
         <v>102500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="B13" s="1">
         <v>200100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="B14" s="1">
         <v>200101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="B15" s="1">
         <v>200300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="B16" s="1">
         <v>200400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="B17" s="1">
         <v>200500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="B18" s="1">
         <v>200600</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="B19" s="1">
         <v>200700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="B20" s="1">
         <v>200800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="B21" s="1">
         <v>200900</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="B22" s="1">
         <v>300100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="B23" s="1">
         <v>300200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B24" s="1">
         <v>500000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -16364,57 +16327,57 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B26" s="1">
         <v>500002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B27" s="1">
         <v>500003</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="B28" s="1">
         <v>500004</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="B29" s="1">
         <v>500005</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B30" s="1">
         <v>500006</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -16425,51 +16388,51 @@
         <v>500007</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>325</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B32" s="1">
         <v>600000</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B33" s="1">
         <v>600001</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B34" s="1">
         <v>600002</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B35" s="1">
         <v>600003</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
